--- a/Score_Class_2026.xlsx
+++ b/Score_Class_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Phisan\Consultancy\2569-KU_MapProjection\Admin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9A9C2AA-D29C-4A48-8D09-C1F5781FCC8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CADF2D12-1106-4911-9AA3-4C7F38FE111D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10746" yWindow="0" windowWidth="11154" windowHeight="12192" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Exercise" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="308">
   <si>
     <t>รายงานแสดงจำนวนนิสิต จำแนกตามหมู่เรียน ภาคต้น ปีการศึกษา 2569</t>
   </si>
@@ -952,13 +952,22 @@
   </si>
   <si>
     <t>Ex.5 Guassian vs Mercator</t>
+  </si>
+  <si>
+    <t>Ex.6 Tissot Indicator</t>
+  </si>
+  <si>
+    <t>06-10/8/1969</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <numFmts count="1">
+    <numFmt numFmtId="187" formatCode="B1d\-mmm\-yy"/>
+  </numFmts>
+  <fonts count="7">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -992,6 +1001,12 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1" tint="4.9989318521683403E-2"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -1065,7 +1080,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1108,7 +1123,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1119,15 +1133,24 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
+    <xf numFmtId="187" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1165,7 +1188,7 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>1313180</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>1422060</xdr:rowOff>
+      <xdr:rowOff>1420790</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1367,50 +1390,50 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:20" ht="16" customHeight="1">
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
-      <c r="K2" s="27"/>
-      <c r="L2" s="27"/>
-      <c r="M2" s="27"/>
-      <c r="N2" s="27"/>
-      <c r="O2" s="27"/>
-      <c r="P2" s="27"/>
-      <c r="Q2" s="27"/>
-      <c r="R2" s="27"/>
-      <c r="S2" s="27"/>
-      <c r="T2" s="27"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="29"/>
+      <c r="N2" s="29"/>
+      <c r="O2" s="29"/>
+      <c r="P2" s="29"/>
+      <c r="Q2" s="29"/>
+      <c r="R2" s="29"/>
+      <c r="S2" s="29"/>
+      <c r="T2" s="29"/>
     </row>
     <row r="3" spans="2:20" ht="18.3" customHeight="1">
-      <c r="B3" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27"/>
-      <c r="J3" s="27"/>
-      <c r="K3" s="27"/>
-      <c r="L3" s="27"/>
-      <c r="M3" s="27"/>
-      <c r="N3" s="27"/>
-      <c r="O3" s="27"/>
-      <c r="P3" s="27"/>
-      <c r="Q3" s="27"/>
-      <c r="R3" s="27"/>
-      <c r="S3" s="27"/>
-      <c r="T3" s="27"/>
+      <c r="B3" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
+      <c r="J3" s="29"/>
+      <c r="K3" s="29"/>
+      <c r="L3" s="29"/>
+      <c r="M3" s="29"/>
+      <c r="N3" s="29"/>
+      <c r="O3" s="29"/>
+      <c r="P3" s="29"/>
+      <c r="Q3" s="29"/>
+      <c r="R3" s="29"/>
+      <c r="S3" s="29"/>
+      <c r="T3" s="29"/>
     </row>
     <row r="4" spans="2:20" ht="26.1" customHeight="1">
       <c r="B4" s="1" t="s">
@@ -1419,16 +1442,16 @@
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="M4" s="28" t="s">
+      <c r="M4" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="N4" s="28"/>
-      <c r="O4" s="28"/>
-      <c r="P4" s="28"/>
-      <c r="Q4" s="28"/>
-      <c r="R4" s="28"/>
-      <c r="S4" s="28"/>
-      <c r="T4" s="28"/>
+      <c r="N4" s="30"/>
+      <c r="O4" s="30"/>
+      <c r="P4" s="30"/>
+      <c r="Q4" s="30"/>
+      <c r="R4" s="30"/>
+      <c r="S4" s="30"/>
+      <c r="T4" s="30"/>
     </row>
     <row r="5" spans="2:20" ht="18">
       <c r="E5" s="1" t="s">
@@ -1460,8 +1483,10 @@
       <c r="O6" s="13" t="s">
         <v>305</v>
       </c>
-      <c r="P6" s="10"/>
-      <c r="Q6" s="10"/>
+      <c r="P6" s="13" t="s">
+        <v>306</v>
+      </c>
+      <c r="Q6" s="13"/>
       <c r="R6" s="10"/>
       <c r="S6" s="10"/>
       <c r="T6" s="10"/>
@@ -2573,7 +2598,7 @@
         <v>163</v>
       </c>
       <c r="L30" s="17">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="M30" s="9">
         <v>10</v>
@@ -3348,7 +3373,9 @@
       <c r="M46" s="9">
         <v>10</v>
       </c>
-      <c r="N46" s="11"/>
+      <c r="N46" s="11">
+        <v>7</v>
+      </c>
       <c r="O46" s="9">
         <v>8</v>
       </c>
@@ -3638,7 +3665,7 @@
         <v>12</v>
       </c>
       <c r="M52" s="9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N52" s="11">
         <v>10</v>
@@ -3726,9 +3753,9 @@
     <col min="1" max="1" width="6.94921875" customWidth="1"/>
     <col min="2" max="2" width="16.19921875" customWidth="1"/>
     <col min="3" max="3" width="31.046875" customWidth="1"/>
-    <col min="4" max="4" width="3.796875" style="19" customWidth="1"/>
+    <col min="4" max="4" width="3.796875" style="18" customWidth="1"/>
     <col min="5" max="5" width="3.796875" customWidth="1"/>
-    <col min="6" max="6" width="3.796875" style="18" customWidth="1"/>
+    <col min="6" max="6" width="3.796875" style="26" customWidth="1"/>
     <col min="7" max="14" width="3.796875" customWidth="1"/>
     <col min="15" max="15" width="8.796875" customWidth="1"/>
     <col min="16" max="26" width="4.6484375" customWidth="1"/>
@@ -3741,21 +3768,23 @@
       <c r="C6" s="10" t="s">
         <v>302</v>
       </c>
-      <c r="D6" s="24" t="s">
+      <c r="D6" s="22" t="s">
         <v>303</v>
       </c>
-      <c r="E6" s="25" t="s">
+      <c r="E6" s="23" t="s">
         <v>304</v>
       </c>
-      <c r="F6" s="26"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="25"/>
-      <c r="I6" s="25"/>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="L6" s="25"/>
-      <c r="M6" s="25"/>
-      <c r="N6" s="25"/>
+      <c r="F6" s="24" t="s">
+        <v>307</v>
+      </c>
+      <c r="G6" s="23"/>
+      <c r="H6" s="23"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="23"/>
+      <c r="K6" s="23"/>
+      <c r="L6" s="23"/>
+      <c r="M6" s="23"/>
+      <c r="N6" s="23"/>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="9" t="str">
@@ -3770,17 +3799,17 @@
         <f>Exercise!D7</f>
         <v>ชื่อ-นามสกุล</v>
       </c>
-      <c r="D7" s="23"/>
-      <c r="E7" s="23"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="23"/>
-      <c r="I7" s="23"/>
-      <c r="J7" s="23"/>
-      <c r="K7" s="23"/>
-      <c r="L7" s="23"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="23"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="25"/>
+      <c r="I7" s="25"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
+      <c r="L7" s="25"/>
+      <c r="M7" s="25"/>
+      <c r="N7" s="25"/>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="9" t="str">
@@ -3795,11 +3824,13 @@
         <f>Exercise!D8</f>
         <v>นายธีรพัส แก้วงาม</v>
       </c>
-      <c r="D8" s="20">
-        <v>1</v>
-      </c>
-      <c r="E8" s="22"/>
-      <c r="F8" s="17"/>
+      <c r="D8" s="19">
+        <v>1</v>
+      </c>
+      <c r="E8" s="21"/>
+      <c r="F8" s="28">
+        <v>1</v>
+      </c>
       <c r="G8" s="9"/>
       <c r="H8" s="9"/>
       <c r="I8" s="9"/>
@@ -3822,11 +3853,11 @@
         <f>Exercise!D9</f>
         <v>นางสาวนภัสสร นูมหันต์</v>
       </c>
-      <c r="D9" s="20"/>
-      <c r="E9" s="22">
-        <v>1</v>
-      </c>
-      <c r="F9" s="17"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="21">
+        <v>1</v>
+      </c>
+      <c r="F9" s="28"/>
       <c r="G9" s="9"/>
       <c r="H9" s="9"/>
       <c r="I9" s="9"/>
@@ -3849,11 +3880,11 @@
         <f>Exercise!D10</f>
         <v>นางสาวนรภร เจริญสลุง</v>
       </c>
-      <c r="D10" s="20"/>
-      <c r="E10" s="22">
-        <v>1</v>
-      </c>
-      <c r="F10" s="17"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="21">
+        <v>1</v>
+      </c>
+      <c r="F10" s="28"/>
       <c r="G10" s="9"/>
       <c r="H10" s="9"/>
       <c r="I10" s="9"/>
@@ -3876,13 +3907,15 @@
         <f>Exercise!D11</f>
         <v>นายบุนยามีน มะสง</v>
       </c>
-      <c r="D11" s="20">
-        <v>1</v>
-      </c>
-      <c r="E11" s="22">
-        <v>1</v>
-      </c>
-      <c r="F11" s="17"/>
+      <c r="D11" s="19">
+        <v>1</v>
+      </c>
+      <c r="E11" s="21">
+        <v>1</v>
+      </c>
+      <c r="F11" s="28">
+        <v>1</v>
+      </c>
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
@@ -3905,13 +3938,15 @@
         <f>Exercise!D12</f>
         <v>นายปัญญานันท์ ทองแก้วเกิด</v>
       </c>
-      <c r="D12" s="20">
-        <v>1</v>
-      </c>
-      <c r="E12" s="22">
-        <v>1</v>
-      </c>
-      <c r="F12" s="17"/>
+      <c r="D12" s="19">
+        <v>1</v>
+      </c>
+      <c r="E12" s="21">
+        <v>1</v>
+      </c>
+      <c r="F12" s="28">
+        <v>1</v>
+      </c>
       <c r="G12" s="9"/>
       <c r="H12" s="9"/>
       <c r="I12" s="9"/>
@@ -3934,11 +3969,11 @@
         <f>Exercise!D13</f>
         <v>นางสาวภิญยดา ศรีแนน</v>
       </c>
-      <c r="D13" s="20"/>
-      <c r="E13" s="22">
-        <v>1</v>
-      </c>
-      <c r="F13" s="17"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="21">
+        <v>1</v>
+      </c>
+      <c r="F13" s="28"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
@@ -3961,11 +3996,13 @@
         <f>Exercise!D14</f>
         <v>นายภูริณ มานหมัด</v>
       </c>
-      <c r="D14" s="20">
-        <v>1</v>
-      </c>
-      <c r="E14" s="22"/>
-      <c r="F14" s="17"/>
+      <c r="D14" s="19">
+        <v>1</v>
+      </c>
+      <c r="E14" s="21"/>
+      <c r="F14" s="28">
+        <v>1</v>
+      </c>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
       <c r="I14" s="9"/>
@@ -3988,13 +4025,15 @@
         <f>Exercise!D15</f>
         <v>นายรัชชานนท์ สาคะเรศ</v>
       </c>
-      <c r="D15" s="20">
-        <v>1</v>
-      </c>
-      <c r="E15" s="22">
-        <v>1</v>
-      </c>
-      <c r="F15" s="17"/>
+      <c r="D15" s="19">
+        <v>1</v>
+      </c>
+      <c r="E15" s="21">
+        <v>1</v>
+      </c>
+      <c r="F15" s="28">
+        <v>1</v>
+      </c>
       <c r="G15" s="9"/>
       <c r="H15" s="9"/>
       <c r="I15" s="9"/>
@@ -4017,13 +4056,15 @@
         <f>Exercise!D16</f>
         <v>นายวรพล พลอยชัด</v>
       </c>
-      <c r="D16" s="20">
-        <v>1</v>
-      </c>
-      <c r="E16" s="22">
-        <v>1</v>
-      </c>
-      <c r="F16" s="17"/>
+      <c r="D16" s="19">
+        <v>1</v>
+      </c>
+      <c r="E16" s="21">
+        <v>1</v>
+      </c>
+      <c r="F16" s="28">
+        <v>1</v>
+      </c>
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
       <c r="I16" s="9"/>
@@ -4046,13 +4087,15 @@
         <f>Exercise!D17</f>
         <v>นายศุภณัฐ จันทรังษี</v>
       </c>
-      <c r="D17" s="20">
-        <v>1</v>
-      </c>
-      <c r="E17" s="22">
-        <v>1</v>
-      </c>
-      <c r="F17" s="17"/>
+      <c r="D17" s="19">
+        <v>1</v>
+      </c>
+      <c r="E17" s="21">
+        <v>1</v>
+      </c>
+      <c r="F17" s="28">
+        <v>1</v>
+      </c>
       <c r="G17" s="9"/>
       <c r="H17" s="9"/>
       <c r="I17" s="9"/>
@@ -4075,11 +4118,13 @@
         <f>Exercise!D18</f>
         <v>นางสาวเศรษฐกมล วังออมทรัพย์</v>
       </c>
-      <c r="D18" s="20"/>
-      <c r="E18" s="22">
-        <v>1</v>
-      </c>
-      <c r="F18" s="17"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="21">
+        <v>1</v>
+      </c>
+      <c r="F18" s="28">
+        <v>1</v>
+      </c>
       <c r="G18" s="9"/>
       <c r="H18" s="9"/>
       <c r="I18" s="9"/>
@@ -4102,9 +4147,9 @@
         <f>Exercise!D19</f>
         <v>นางสาวอริศรา เล่งกูล</v>
       </c>
-      <c r="D19" s="20"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="17"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="28"/>
       <c r="G19" s="9"/>
       <c r="H19" s="9"/>
       <c r="I19" s="9"/>
@@ -4127,9 +4172,11 @@
         <f>Exercise!D20</f>
         <v>นายภัทรพล ดิษฐาพร</v>
       </c>
-      <c r="D20" s="20"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="17"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="28">
+        <v>1</v>
+      </c>
       <c r="G20" s="9"/>
       <c r="H20" s="9"/>
       <c r="I20" s="9"/>
@@ -4152,13 +4199,13 @@
         <f>Exercise!D21</f>
         <v>นายภาคิน แซ่โง้ว</v>
       </c>
-      <c r="D21" s="20">
-        <v>1</v>
-      </c>
-      <c r="E21" s="22">
-        <v>1</v>
-      </c>
-      <c r="F21" s="17"/>
+      <c r="D21" s="19">
+        <v>1</v>
+      </c>
+      <c r="E21" s="21">
+        <v>1</v>
+      </c>
+      <c r="F21" s="28"/>
       <c r="G21" s="9"/>
       <c r="H21" s="9"/>
       <c r="I21" s="9"/>
@@ -4181,13 +4228,15 @@
         <f>Exercise!D22</f>
         <v>นายกนล แสงเดช</v>
       </c>
-      <c r="D22" s="20">
-        <v>1</v>
-      </c>
-      <c r="E22" s="22">
-        <v>1</v>
-      </c>
-      <c r="F22" s="17"/>
+      <c r="D22" s="19">
+        <v>1</v>
+      </c>
+      <c r="E22" s="21">
+        <v>1</v>
+      </c>
+      <c r="F22" s="28">
+        <v>1</v>
+      </c>
       <c r="G22" s="9"/>
       <c r="H22" s="9"/>
       <c r="I22" s="9"/>
@@ -4210,13 +4259,15 @@
         <f>Exercise!D23</f>
         <v>นางสาวกมลนิตย์ โตอยู่</v>
       </c>
-      <c r="D23" s="20">
-        <v>1</v>
-      </c>
-      <c r="E23" s="22">
-        <v>1</v>
-      </c>
-      <c r="F23" s="17"/>
+      <c r="D23" s="19">
+        <v>1</v>
+      </c>
+      <c r="E23" s="21">
+        <v>1</v>
+      </c>
+      <c r="F23" s="28">
+        <v>1</v>
+      </c>
       <c r="G23" s="9"/>
       <c r="H23" s="9"/>
       <c r="I23" s="9"/>
@@ -4239,13 +4290,15 @@
         <f>Exercise!D24</f>
         <v>นายกฤษกร ศรีสัจจัง</v>
       </c>
-      <c r="D24" s="20">
-        <v>1</v>
-      </c>
-      <c r="E24" s="22">
-        <v>1</v>
-      </c>
-      <c r="F24" s="17"/>
+      <c r="D24" s="19">
+        <v>1</v>
+      </c>
+      <c r="E24" s="21">
+        <v>1</v>
+      </c>
+      <c r="F24" s="28">
+        <v>1</v>
+      </c>
       <c r="G24" s="9"/>
       <c r="H24" s="9"/>
       <c r="I24" s="9"/>
@@ -4268,13 +4321,15 @@
         <f>Exercise!D25</f>
         <v>นายกันติวัสส์ ตันตระการย์</v>
       </c>
-      <c r="D25" s="20">
-        <v>1</v>
-      </c>
-      <c r="E25" s="22">
-        <v>1</v>
-      </c>
-      <c r="F25" s="17"/>
+      <c r="D25" s="19">
+        <v>1</v>
+      </c>
+      <c r="E25" s="21">
+        <v>1</v>
+      </c>
+      <c r="F25" s="28">
+        <v>1</v>
+      </c>
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
       <c r="I25" s="9"/>
@@ -4297,13 +4352,15 @@
         <f>Exercise!D26</f>
         <v>นายเกษมโชค นชะพงษ์</v>
       </c>
-      <c r="D26" s="20">
-        <v>1</v>
-      </c>
-      <c r="E26" s="22">
-        <v>1</v>
-      </c>
-      <c r="F26" s="17"/>
+      <c r="D26" s="19">
+        <v>1</v>
+      </c>
+      <c r="E26" s="21">
+        <v>1</v>
+      </c>
+      <c r="F26" s="28">
+        <v>1</v>
+      </c>
       <c r="G26" s="9"/>
       <c r="H26" s="9"/>
       <c r="I26" s="9"/>
@@ -4326,11 +4383,13 @@
         <f>Exercise!D27</f>
         <v>นายจักรินทร์ อินทร์น้อย</v>
       </c>
-      <c r="D27" s="20"/>
-      <c r="E27" s="22">
-        <v>1</v>
-      </c>
-      <c r="F27" s="17"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="21">
+        <v>1</v>
+      </c>
+      <c r="F27" s="28">
+        <v>1</v>
+      </c>
       <c r="G27" s="9"/>
       <c r="H27" s="9"/>
       <c r="I27" s="9"/>
@@ -4353,11 +4412,13 @@
         <f>Exercise!D28</f>
         <v>นางสาวจันทร์เจ้า เทพจิตต์</v>
       </c>
-      <c r="D28" s="20"/>
-      <c r="E28" s="22">
-        <v>1</v>
-      </c>
-      <c r="F28" s="17"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="21">
+        <v>1</v>
+      </c>
+      <c r="F28" s="28">
+        <v>1</v>
+      </c>
       <c r="G28" s="9"/>
       <c r="H28" s="9"/>
       <c r="I28" s="9"/>
@@ -4380,13 +4441,15 @@
         <f>Exercise!D29</f>
         <v>นางสาวฑิฆัมพร ตรีบุสยะรัตน์</v>
       </c>
-      <c r="D29" s="20">
-        <v>1</v>
-      </c>
-      <c r="E29" s="22">
-        <v>1</v>
-      </c>
-      <c r="F29" s="17"/>
+      <c r="D29" s="19">
+        <v>1</v>
+      </c>
+      <c r="E29" s="21">
+        <v>1</v>
+      </c>
+      <c r="F29" s="28">
+        <v>1</v>
+      </c>
       <c r="G29" s="9"/>
       <c r="H29" s="9"/>
       <c r="I29" s="9"/>
@@ -4409,13 +4472,15 @@
         <f>Exercise!D30</f>
         <v>นางสาวณปภัช บุญมายศ</v>
       </c>
-      <c r="D30" s="20">
-        <v>1</v>
-      </c>
-      <c r="E30" s="22">
-        <v>1</v>
-      </c>
-      <c r="F30" s="17"/>
+      <c r="D30" s="19">
+        <v>1</v>
+      </c>
+      <c r="E30" s="21">
+        <v>1</v>
+      </c>
+      <c r="F30" s="28">
+        <v>1</v>
+      </c>
       <c r="G30" s="9"/>
       <c r="H30" s="9"/>
       <c r="I30" s="9"/>
@@ -4438,9 +4503,9 @@
         <f>Exercise!D31</f>
         <v>นายธนทัต มุทธากาญจน์</v>
       </c>
-      <c r="D31" s="20"/>
-      <c r="E31" s="22"/>
-      <c r="F31" s="17"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="28"/>
       <c r="G31" s="9"/>
       <c r="H31" s="9"/>
       <c r="I31" s="9"/>
@@ -4463,13 +4528,15 @@
         <f>Exercise!D32</f>
         <v>นายธนภูมิ เหลืองชัยพัฒนา</v>
       </c>
-      <c r="D32" s="20">
-        <v>1</v>
-      </c>
-      <c r="E32" s="22">
-        <v>1</v>
-      </c>
-      <c r="F32" s="17"/>
+      <c r="D32" s="19">
+        <v>1</v>
+      </c>
+      <c r="E32" s="21">
+        <v>1</v>
+      </c>
+      <c r="F32" s="28">
+        <v>1</v>
+      </c>
       <c r="G32" s="9"/>
       <c r="H32" s="9"/>
       <c r="I32" s="9"/>
@@ -4492,11 +4559,13 @@
         <f>Exercise!D33</f>
         <v>นายธนากร เรืองพูน</v>
       </c>
-      <c r="D33" s="20"/>
-      <c r="E33" s="22">
-        <v>1</v>
-      </c>
-      <c r="F33" s="17"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="21">
+        <v>1</v>
+      </c>
+      <c r="F33" s="28">
+        <v>1</v>
+      </c>
       <c r="G33" s="9"/>
       <c r="H33" s="9"/>
       <c r="I33" s="9"/>
@@ -4519,11 +4588,15 @@
         <f>Exercise!D34</f>
         <v>นายธรรมกร เจริญพร</v>
       </c>
-      <c r="D34" s="20"/>
-      <c r="E34" s="22">
-        <v>1</v>
-      </c>
-      <c r="F34" s="17"/>
+      <c r="D34" s="19">
+        <v>1</v>
+      </c>
+      <c r="E34" s="21">
+        <v>1</v>
+      </c>
+      <c r="F34" s="28">
+        <v>1</v>
+      </c>
       <c r="G34" s="9"/>
       <c r="H34" s="9"/>
       <c r="I34" s="9"/>
@@ -4546,13 +4619,15 @@
         <f>Exercise!D35</f>
         <v>นางสาวธัชตะวัน ยกโต</v>
       </c>
-      <c r="D35" s="20">
-        <v>1</v>
-      </c>
-      <c r="E35" s="22">
-        <v>1</v>
-      </c>
-      <c r="F35" s="17"/>
+      <c r="D35" s="19">
+        <v>1</v>
+      </c>
+      <c r="E35" s="21">
+        <v>1</v>
+      </c>
+      <c r="F35" s="28">
+        <v>1</v>
+      </c>
       <c r="G35" s="9"/>
       <c r="H35" s="9"/>
       <c r="I35" s="9"/>
@@ -4575,13 +4650,15 @@
         <f>Exercise!D36</f>
         <v>นายนนทกร จวนทองรักษ์</v>
       </c>
-      <c r="D36" s="20">
-        <v>1</v>
-      </c>
-      <c r="E36" s="22">
-        <v>1</v>
-      </c>
-      <c r="F36" s="17"/>
+      <c r="D36" s="19">
+        <v>1</v>
+      </c>
+      <c r="E36" s="21">
+        <v>1</v>
+      </c>
+      <c r="F36" s="28">
+        <v>1</v>
+      </c>
       <c r="G36" s="9"/>
       <c r="H36" s="9"/>
       <c r="I36" s="9"/>
@@ -4604,13 +4681,15 @@
         <f>Exercise!D37</f>
         <v>นายนภัสรพี อร่ามฉิม</v>
       </c>
-      <c r="D37" s="20">
-        <v>1</v>
-      </c>
-      <c r="E37" s="22">
-        <v>1</v>
-      </c>
-      <c r="F37" s="17"/>
+      <c r="D37" s="19">
+        <v>1</v>
+      </c>
+      <c r="E37" s="21">
+        <v>1</v>
+      </c>
+      <c r="F37" s="28">
+        <v>1</v>
+      </c>
       <c r="G37" s="9"/>
       <c r="H37" s="9"/>
       <c r="I37" s="9"/>
@@ -4633,11 +4712,13 @@
         <f>Exercise!D38</f>
         <v>นายพิชญุตม์ ลอยมา</v>
       </c>
-      <c r="D38" s="20">
-        <v>1</v>
-      </c>
-      <c r="E38" s="22"/>
-      <c r="F38" s="17"/>
+      <c r="D38" s="19">
+        <v>1</v>
+      </c>
+      <c r="E38" s="21"/>
+      <c r="F38" s="28">
+        <v>1</v>
+      </c>
       <c r="G38" s="9"/>
       <c r="H38" s="9"/>
       <c r="I38" s="9"/>
@@ -4660,13 +4741,15 @@
         <f>Exercise!D39</f>
         <v>นายภควัฒน์ พรมประโคน</v>
       </c>
-      <c r="D39" s="20">
-        <v>1</v>
-      </c>
-      <c r="E39" s="22">
-        <v>1</v>
-      </c>
-      <c r="F39" s="17"/>
+      <c r="D39" s="19">
+        <v>1</v>
+      </c>
+      <c r="E39" s="21">
+        <v>1</v>
+      </c>
+      <c r="F39" s="28">
+        <v>1</v>
+      </c>
       <c r="G39" s="9"/>
       <c r="H39" s="9"/>
       <c r="I39" s="9"/>
@@ -4689,13 +4772,15 @@
         <f>Exercise!D40</f>
         <v>นายภัคพล ลาวชัย</v>
       </c>
-      <c r="D40" s="20">
-        <v>1</v>
-      </c>
-      <c r="E40" s="22">
-        <v>1</v>
-      </c>
-      <c r="F40" s="17"/>
+      <c r="D40" s="19">
+        <v>1</v>
+      </c>
+      <c r="E40" s="21">
+        <v>1</v>
+      </c>
+      <c r="F40" s="28">
+        <v>1</v>
+      </c>
       <c r="G40" s="9"/>
       <c r="H40" s="9"/>
       <c r="I40" s="9"/>
@@ -4718,13 +4803,15 @@
         <f>Exercise!D41</f>
         <v>นายภัคพล อินทะรังษี</v>
       </c>
-      <c r="D41" s="20">
-        <v>1</v>
-      </c>
-      <c r="E41" s="22">
-        <v>1</v>
-      </c>
-      <c r="F41" s="17"/>
+      <c r="D41" s="19">
+        <v>1</v>
+      </c>
+      <c r="E41" s="21">
+        <v>1</v>
+      </c>
+      <c r="F41" s="28">
+        <v>1</v>
+      </c>
       <c r="G41" s="9"/>
       <c r="H41" s="9"/>
       <c r="I41" s="9"/>
@@ -4747,13 +4834,15 @@
         <f>Exercise!D42</f>
         <v>นายยุทธนา สุขกำเนิด</v>
       </c>
-      <c r="D42" s="20">
-        <v>1</v>
-      </c>
-      <c r="E42" s="22">
-        <v>1</v>
-      </c>
-      <c r="F42" s="17"/>
+      <c r="D42" s="19">
+        <v>1</v>
+      </c>
+      <c r="E42" s="21">
+        <v>1</v>
+      </c>
+      <c r="F42" s="28">
+        <v>1</v>
+      </c>
       <c r="G42" s="9"/>
       <c r="H42" s="9"/>
       <c r="I42" s="9"/>
@@ -4776,13 +4865,15 @@
         <f>Exercise!D43</f>
         <v>นายรพีภัทร มอยนา</v>
       </c>
-      <c r="D43" s="20">
-        <v>1</v>
-      </c>
-      <c r="E43" s="22">
-        <v>1</v>
-      </c>
-      <c r="F43" s="17"/>
+      <c r="D43" s="19">
+        <v>1</v>
+      </c>
+      <c r="E43" s="21">
+        <v>1</v>
+      </c>
+      <c r="F43" s="28">
+        <v>1</v>
+      </c>
       <c r="G43" s="9"/>
       <c r="H43" s="9"/>
       <c r="I43" s="9"/>
@@ -4805,13 +4896,15 @@
         <f>Exercise!D44</f>
         <v>นายวีรภัทร ดีมาก</v>
       </c>
-      <c r="D44" s="20">
-        <v>1</v>
-      </c>
-      <c r="E44" s="22">
-        <v>1</v>
-      </c>
-      <c r="F44" s="17"/>
+      <c r="D44" s="19">
+        <v>1</v>
+      </c>
+      <c r="E44" s="21">
+        <v>1</v>
+      </c>
+      <c r="F44" s="28">
+        <v>1</v>
+      </c>
       <c r="G44" s="9"/>
       <c r="H44" s="9"/>
       <c r="I44" s="9"/>
@@ -4834,13 +4927,15 @@
         <f>Exercise!D45</f>
         <v>นางสาวศวิตา ไชยสุนทร</v>
       </c>
-      <c r="D45" s="20">
-        <v>1</v>
-      </c>
-      <c r="E45" s="22">
-        <v>1</v>
-      </c>
-      <c r="F45" s="17"/>
+      <c r="D45" s="19">
+        <v>1</v>
+      </c>
+      <c r="E45" s="21">
+        <v>1</v>
+      </c>
+      <c r="F45" s="28">
+        <v>1</v>
+      </c>
       <c r="G45" s="9"/>
       <c r="H45" s="9"/>
       <c r="I45" s="9"/>
@@ -4863,13 +4958,15 @@
         <f>Exercise!D46</f>
         <v>นายสรศักดิ์ โคตรนาม</v>
       </c>
-      <c r="D46" s="20">
-        <v>1</v>
-      </c>
-      <c r="E46" s="22">
-        <v>1</v>
-      </c>
-      <c r="F46" s="17"/>
+      <c r="D46" s="19">
+        <v>1</v>
+      </c>
+      <c r="E46" s="21">
+        <v>1</v>
+      </c>
+      <c r="F46" s="28">
+        <v>1</v>
+      </c>
       <c r="G46" s="9"/>
       <c r="H46" s="9"/>
       <c r="I46" s="9"/>
@@ -4892,13 +4989,15 @@
         <f>Exercise!D47</f>
         <v>นายสราวุฒิ ยะโส</v>
       </c>
-      <c r="D47" s="20">
-        <v>1</v>
-      </c>
-      <c r="E47" s="22">
-        <v>1</v>
-      </c>
-      <c r="F47" s="17"/>
+      <c r="D47" s="19">
+        <v>1</v>
+      </c>
+      <c r="E47" s="21">
+        <v>1</v>
+      </c>
+      <c r="F47" s="28">
+        <v>1</v>
+      </c>
       <c r="G47" s="9"/>
       <c r="H47" s="9"/>
       <c r="I47" s="9"/>
@@ -4921,13 +5020,15 @@
         <f>Exercise!D48</f>
         <v>นายสิทชัยเลิศ ศรนรายณ์</v>
       </c>
-      <c r="D48" s="20">
-        <v>1</v>
-      </c>
-      <c r="E48" s="22">
-        <v>1</v>
-      </c>
-      <c r="F48" s="17"/>
+      <c r="D48" s="19">
+        <v>1</v>
+      </c>
+      <c r="E48" s="21">
+        <v>1</v>
+      </c>
+      <c r="F48" s="28">
+        <v>1</v>
+      </c>
       <c r="G48" s="9"/>
       <c r="H48" s="9"/>
       <c r="I48" s="9"/>
@@ -4950,13 +5051,15 @@
         <f>Exercise!D49</f>
         <v>นายสุทธิโชติ ใบเตย</v>
       </c>
-      <c r="D49" s="20">
-        <v>1</v>
-      </c>
-      <c r="E49" s="22">
-        <v>1</v>
-      </c>
-      <c r="F49" s="17"/>
+      <c r="D49" s="19">
+        <v>1</v>
+      </c>
+      <c r="E49" s="21">
+        <v>1</v>
+      </c>
+      <c r="F49" s="28">
+        <v>1</v>
+      </c>
       <c r="G49" s="9"/>
       <c r="H49" s="9"/>
       <c r="I49" s="9"/>
@@ -4979,13 +5082,15 @@
         <f>Exercise!D50</f>
         <v>นายสุเมธ อบอารีย์</v>
       </c>
-      <c r="D50" s="20">
-        <v>1</v>
-      </c>
-      <c r="E50" s="22">
-        <v>1</v>
-      </c>
-      <c r="F50" s="17"/>
+      <c r="D50" s="19">
+        <v>1</v>
+      </c>
+      <c r="E50" s="21">
+        <v>1</v>
+      </c>
+      <c r="F50" s="28">
+        <v>1</v>
+      </c>
       <c r="G50" s="9"/>
       <c r="H50" s="9"/>
       <c r="I50" s="9"/>
@@ -5008,13 +5113,15 @@
         <f>Exercise!D51</f>
         <v>นายอัสนี คงดีจันทร์</v>
       </c>
-      <c r="D51" s="20">
-        <v>1</v>
-      </c>
-      <c r="E51" s="22">
-        <v>1</v>
-      </c>
-      <c r="F51" s="17"/>
+      <c r="D51" s="19">
+        <v>1</v>
+      </c>
+      <c r="E51" s="21">
+        <v>1</v>
+      </c>
+      <c r="F51" s="28">
+        <v>1</v>
+      </c>
       <c r="G51" s="9"/>
       <c r="H51" s="9"/>
       <c r="I51" s="9"/>
@@ -5037,13 +5144,15 @@
         <f>Exercise!D52</f>
         <v>นางสาวอาทิตยา ไทยเจริญ</v>
       </c>
-      <c r="D52" s="20">
-        <v>1</v>
-      </c>
-      <c r="E52" s="22">
-        <v>1</v>
-      </c>
-      <c r="F52" s="17"/>
+      <c r="D52" s="19">
+        <v>1</v>
+      </c>
+      <c r="E52" s="21">
+        <v>1</v>
+      </c>
+      <c r="F52" s="28">
+        <v>1</v>
+      </c>
       <c r="G52" s="9"/>
       <c r="H52" s="9"/>
       <c r="I52" s="9"/>
@@ -5066,13 +5175,15 @@
         <f>Exercise!D53</f>
         <v>นางสาวอารยา แสนสุข</v>
       </c>
-      <c r="D53" s="21">
-        <v>1</v>
-      </c>
-      <c r="E53" s="22">
-        <v>1</v>
-      </c>
-      <c r="F53" s="17"/>
+      <c r="D53" s="20">
+        <v>1</v>
+      </c>
+      <c r="E53" s="21">
+        <v>1</v>
+      </c>
+      <c r="F53" s="28">
+        <v>1</v>
+      </c>
       <c r="G53" s="9"/>
       <c r="H53" s="9"/>
       <c r="I53" s="9"/>

--- a/Score_Class_2026.xlsx
+++ b/Score_Class_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Phisan\Consultancy\2569-KU_MapProjection\Admin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CADF2D12-1106-4911-9AA3-4C7F38FE111D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC171A62-CAEC-4A91-A698-BF84F0C3AE8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="39620" yWindow="-5780" windowWidth="28800" windowHeight="15200" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Exercise" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="309">
   <si>
     <t>รายงานแสดงจำนวนนิสิต จำแนกตามหมู่เรียน ภาคต้น ปีการศึกษา 2569</t>
   </si>
@@ -958,6 +958,9 @@
   </si>
   <si>
     <t>06-10/8/1969</t>
+  </si>
+  <si>
+    <t>24-Aug-2026\</t>
   </si>
 </sst>
 </file>
@@ -1009,7 +1012,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1035,7 +1038,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="1" tint="4.9989318521683403E-2"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1080,7 +1095,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1111,7 +1126,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
@@ -1121,8 +1135,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1139,24 +1151,51 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="187" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="187" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1188,7 +1227,7 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>1313180</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>1420790</xdr:rowOff>
+      <xdr:rowOff>1423330</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1382,58 +1421,56 @@
     <col min="4" max="4" width="20.6484375" customWidth="1"/>
     <col min="5" max="6" width="18" hidden="1" customWidth="1"/>
     <col min="7" max="8" width="10" hidden="1" customWidth="1"/>
-    <col min="9" max="11" width="0" hidden="1" customWidth="1"/>
-    <col min="12" max="13" width="4.6484375" customWidth="1"/>
-    <col min="14" max="14" width="4.6484375" style="8" customWidth="1"/>
-    <col min="15" max="20" width="4.6484375" customWidth="1"/>
+    <col min="9" max="11" width="10.796875" hidden="1" customWidth="1"/>
+    <col min="12" max="20" width="4.6484375" style="8" customWidth="1"/>
     <col min="21" max="21" width="10.796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:20" ht="16" customHeight="1">
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29"/>
-      <c r="M2" s="29"/>
-      <c r="N2" s="29"/>
-      <c r="O2" s="29"/>
-      <c r="P2" s="29"/>
-      <c r="Q2" s="29"/>
-      <c r="R2" s="29"/>
-      <c r="S2" s="29"/>
-      <c r="T2" s="29"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
+      <c r="P2" s="32"/>
+      <c r="Q2" s="32"/>
+      <c r="R2" s="32"/>
+      <c r="S2" s="32"/>
+      <c r="T2" s="32"/>
     </row>
     <row r="3" spans="2:20" ht="18.3" customHeight="1">
-      <c r="B3" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29"/>
-      <c r="K3" s="29"/>
-      <c r="L3" s="29"/>
-      <c r="M3" s="29"/>
-      <c r="N3" s="29"/>
-      <c r="O3" s="29"/>
-      <c r="P3" s="29"/>
-      <c r="Q3" s="29"/>
-      <c r="R3" s="29"/>
-      <c r="S3" s="29"/>
-      <c r="T3" s="29"/>
+      <c r="B3" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="32"/>
+      <c r="M3" s="32"/>
+      <c r="N3" s="32"/>
+      <c r="O3" s="32"/>
+      <c r="P3" s="32"/>
+      <c r="Q3" s="32"/>
+      <c r="R3" s="32"/>
+      <c r="S3" s="32"/>
+      <c r="T3" s="32"/>
     </row>
     <row r="4" spans="2:20" ht="26.1" customHeight="1">
       <c r="B4" s="1" t="s">
@@ -1442,16 +1479,16 @@
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="M4" s="30" t="s">
+      <c r="M4" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="N4" s="30"/>
-      <c r="O4" s="30"/>
-      <c r="P4" s="30"/>
-      <c r="Q4" s="30"/>
-      <c r="R4" s="30"/>
-      <c r="S4" s="30"/>
-      <c r="T4" s="30"/>
+      <c r="N4" s="33"/>
+      <c r="O4" s="33"/>
+      <c r="P4" s="33"/>
+      <c r="Q4" s="33"/>
+      <c r="R4" s="33"/>
+      <c r="S4" s="33"/>
+      <c r="T4" s="33"/>
     </row>
     <row r="5" spans="2:20" ht="18">
       <c r="E5" s="1" t="s">
@@ -1471,22 +1508,22 @@
       <c r="G6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L6" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="M6" s="13" t="s">
+      <c r="L6" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="M6" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="N6" s="14" t="s">
+      <c r="N6" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="O6" s="13" t="s">
+      <c r="O6" s="12" t="s">
         <v>305</v>
       </c>
-      <c r="P6" s="13" t="s">
+      <c r="P6" s="12" t="s">
         <v>306</v>
       </c>
-      <c r="Q6" s="13"/>
+      <c r="Q6" s="12"/>
       <c r="R6" s="10"/>
       <c r="S6" s="10"/>
       <c r="T6" s="10"/>
@@ -1522,23 +1559,25 @@
       <c r="K7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="L7" s="16">
+      <c r="L7" s="34">
         <v>12</v>
       </c>
-      <c r="M7" s="12">
-        <v>10</v>
-      </c>
-      <c r="N7" s="12">
-        <v>10</v>
-      </c>
-      <c r="O7" s="12">
-        <v>10</v>
-      </c>
-      <c r="P7" s="12"/>
-      <c r="Q7" s="12"/>
-      <c r="R7" s="12"/>
-      <c r="S7" s="12"/>
-      <c r="T7" s="12"/>
+      <c r="M7" s="35">
+        <v>10</v>
+      </c>
+      <c r="N7" s="35">
+        <v>10</v>
+      </c>
+      <c r="O7" s="35">
+        <v>10</v>
+      </c>
+      <c r="P7" s="35">
+        <v>10</v>
+      </c>
+      <c r="Q7" s="35"/>
+      <c r="R7" s="35"/>
+      <c r="S7" s="35"/>
+      <c r="T7" s="35"/>
     </row>
     <row r="8" spans="2:20" ht="18">
       <c r="B8" s="5" t="s">
@@ -1571,17 +1610,17 @@
       <c r="K8" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="L8" s="17"/>
-      <c r="M8" s="9"/>
+      <c r="L8" s="36"/>
+      <c r="M8" s="10"/>
       <c r="N8" s="11">
         <v>8</v>
       </c>
-      <c r="O8" s="9"/>
-      <c r="P8" s="9"/>
-      <c r="Q8" s="9"/>
-      <c r="R8" s="9"/>
-      <c r="S8" s="9"/>
-      <c r="T8" s="9"/>
+      <c r="O8" s="10"/>
+      <c r="P8" s="10"/>
+      <c r="Q8" s="10"/>
+      <c r="R8" s="10"/>
+      <c r="S8" s="10"/>
+      <c r="T8" s="10"/>
     </row>
     <row r="9" spans="2:20" ht="18">
       <c r="B9" s="5" t="s">
@@ -1614,19 +1653,19 @@
       <c r="K9" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="L9" s="17"/>
-      <c r="M9" s="9">
+      <c r="L9" s="36"/>
+      <c r="M9" s="10">
         <v>3</v>
       </c>
       <c r="N9" s="11"/>
-      <c r="O9" s="9">
-        <v>10</v>
-      </c>
-      <c r="P9" s="9"/>
-      <c r="Q9" s="9"/>
-      <c r="R9" s="9"/>
-      <c r="S9" s="9"/>
-      <c r="T9" s="9"/>
+      <c r="O9" s="10">
+        <v>10</v>
+      </c>
+      <c r="P9" s="10"/>
+      <c r="Q9" s="10"/>
+      <c r="R9" s="10"/>
+      <c r="S9" s="10"/>
+      <c r="T9" s="10"/>
     </row>
     <row r="10" spans="2:20" ht="18">
       <c r="B10" s="5" t="s">
@@ -1659,19 +1698,21 @@
       <c r="K10" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L10" s="17"/>
-      <c r="M10" s="9">
+      <c r="L10" s="36"/>
+      <c r="M10" s="10">
         <v>3</v>
       </c>
       <c r="N10" s="11"/>
-      <c r="O10" s="9">
+      <c r="O10" s="10">
         <v>5</v>
       </c>
-      <c r="P10" s="9"/>
-      <c r="Q10" s="9"/>
-      <c r="R10" s="9"/>
-      <c r="S10" s="9"/>
-      <c r="T10" s="9"/>
+      <c r="P10" s="10">
+        <v>8</v>
+      </c>
+      <c r="Q10" s="10"/>
+      <c r="R10" s="10"/>
+      <c r="S10" s="10"/>
+      <c r="T10" s="10"/>
     </row>
     <row r="11" spans="2:20" ht="18">
       <c r="B11" s="5" t="s">
@@ -1704,23 +1745,25 @@
       <c r="K11" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="L11" s="17">
+      <c r="L11" s="36">
         <v>11</v>
       </c>
-      <c r="M11" s="9">
+      <c r="M11" s="10">
         <v>3</v>
       </c>
       <c r="N11" s="11">
         <v>7</v>
       </c>
-      <c r="O11" s="9">
+      <c r="O11" s="10">
         <v>5</v>
       </c>
-      <c r="P11" s="9"/>
-      <c r="Q11" s="9"/>
-      <c r="R11" s="9"/>
-      <c r="S11" s="9"/>
-      <c r="T11" s="9"/>
+      <c r="P11" s="10">
+        <v>9</v>
+      </c>
+      <c r="Q11" s="10"/>
+      <c r="R11" s="10"/>
+      <c r="S11" s="10"/>
+      <c r="T11" s="10"/>
     </row>
     <row r="12" spans="2:20" ht="18">
       <c r="B12" s="5" t="s">
@@ -1753,17 +1796,19 @@
       <c r="K12" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="L12" s="17"/>
-      <c r="M12" s="9"/>
+      <c r="L12" s="36"/>
+      <c r="M12" s="10"/>
       <c r="N12" s="11">
         <v>7</v>
       </c>
-      <c r="O12" s="9"/>
-      <c r="P12" s="9"/>
-      <c r="Q12" s="9"/>
-      <c r="R12" s="9"/>
-      <c r="S12" s="9"/>
-      <c r="T12" s="9"/>
+      <c r="O12" s="10"/>
+      <c r="P12" s="10">
+        <v>10</v>
+      </c>
+      <c r="Q12" s="10"/>
+      <c r="R12" s="10"/>
+      <c r="S12" s="10"/>
+      <c r="T12" s="10"/>
     </row>
     <row r="13" spans="2:20" ht="18">
       <c r="B13" s="5" t="s">
@@ -1796,15 +1841,15 @@
       <c r="K13" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="L13" s="17"/>
-      <c r="M13" s="9"/>
+      <c r="L13" s="36"/>
+      <c r="M13" s="10"/>
       <c r="N13" s="11"/>
-      <c r="O13" s="9"/>
-      <c r="P13" s="9"/>
-      <c r="Q13" s="9"/>
-      <c r="R13" s="9"/>
-      <c r="S13" s="9"/>
-      <c r="T13" s="9"/>
+      <c r="O13" s="10"/>
+      <c r="P13" s="10"/>
+      <c r="Q13" s="10"/>
+      <c r="R13" s="10"/>
+      <c r="S13" s="10"/>
+      <c r="T13" s="10"/>
     </row>
     <row r="14" spans="2:20" ht="18">
       <c r="B14" s="5" t="s">
@@ -1837,19 +1882,21 @@
       <c r="K14" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="L14" s="17"/>
-      <c r="M14" s="9">
+      <c r="L14" s="36"/>
+      <c r="M14" s="10">
         <v>4</v>
       </c>
       <c r="N14" s="11"/>
-      <c r="O14" s="9">
+      <c r="O14" s="10">
         <v>5</v>
       </c>
-      <c r="P14" s="9"/>
-      <c r="Q14" s="9"/>
-      <c r="R14" s="9"/>
-      <c r="S14" s="9"/>
-      <c r="T14" s="9"/>
+      <c r="P14" s="10">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="10"/>
+      <c r="R14" s="10"/>
+      <c r="S14" s="10"/>
+      <c r="T14" s="10"/>
     </row>
     <row r="15" spans="2:20" ht="18">
       <c r="B15" s="5" t="s">
@@ -1882,23 +1929,25 @@
       <c r="K15" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="L15" s="17">
+      <c r="L15" s="36">
         <v>12</v>
       </c>
-      <c r="M15" s="9">
+      <c r="M15" s="10">
         <v>2</v>
       </c>
       <c r="N15" s="11">
         <v>8</v>
       </c>
-      <c r="O15" s="9">
+      <c r="O15" s="10">
         <v>5</v>
       </c>
-      <c r="P15" s="9"/>
-      <c r="Q15" s="9"/>
-      <c r="R15" s="9"/>
-      <c r="S15" s="9"/>
-      <c r="T15" s="9"/>
+      <c r="P15" s="10">
+        <v>8</v>
+      </c>
+      <c r="Q15" s="10"/>
+      <c r="R15" s="10"/>
+      <c r="S15" s="10"/>
+      <c r="T15" s="10"/>
     </row>
     <row r="16" spans="2:20" ht="18">
       <c r="B16" s="5" t="s">
@@ -1931,21 +1980,21 @@
       <c r="K16" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="L16" s="17"/>
-      <c r="M16" s="9">
+      <c r="L16" s="36"/>
+      <c r="M16" s="10">
         <v>7</v>
       </c>
       <c r="N16" s="11">
         <v>10</v>
       </c>
-      <c r="O16" s="9">
+      <c r="O16" s="10">
         <v>5</v>
       </c>
-      <c r="P16" s="9"/>
-      <c r="Q16" s="9"/>
-      <c r="R16" s="9"/>
-      <c r="S16" s="9"/>
-      <c r="T16" s="9"/>
+      <c r="P16" s="10"/>
+      <c r="Q16" s="10"/>
+      <c r="R16" s="10"/>
+      <c r="S16" s="10"/>
+      <c r="T16" s="10"/>
     </row>
     <row r="17" spans="2:20" ht="18">
       <c r="B17" s="5" t="s">
@@ -1978,23 +2027,25 @@
       <c r="K17" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="L17" s="17">
+      <c r="L17" s="36">
         <v>12</v>
       </c>
-      <c r="M17" s="9">
+      <c r="M17" s="10">
         <v>3</v>
       </c>
       <c r="N17" s="11">
         <v>8</v>
       </c>
-      <c r="O17" s="9">
+      <c r="O17" s="10">
         <v>5</v>
       </c>
-      <c r="P17" s="9"/>
-      <c r="Q17" s="9"/>
-      <c r="R17" s="9"/>
-      <c r="S17" s="9"/>
-      <c r="T17" s="9"/>
+      <c r="P17" s="10">
+        <v>10</v>
+      </c>
+      <c r="Q17" s="10"/>
+      <c r="R17" s="10"/>
+      <c r="S17" s="10"/>
+      <c r="T17" s="10"/>
     </row>
     <row r="18" spans="2:20" ht="18">
       <c r="B18" s="5" t="s">
@@ -2027,19 +2078,21 @@
       <c r="K18" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="L18" s="17"/>
-      <c r="M18" s="9">
+      <c r="L18" s="36"/>
+      <c r="M18" s="10">
         <v>5</v>
       </c>
       <c r="N18" s="11"/>
-      <c r="O18" s="9">
+      <c r="O18" s="10">
         <v>5</v>
       </c>
-      <c r="P18" s="9"/>
-      <c r="Q18" s="9"/>
-      <c r="R18" s="9"/>
-      <c r="S18" s="9"/>
-      <c r="T18" s="9"/>
+      <c r="P18" s="10">
+        <v>9</v>
+      </c>
+      <c r="Q18" s="10"/>
+      <c r="R18" s="10"/>
+      <c r="S18" s="10"/>
+      <c r="T18" s="10"/>
     </row>
     <row r="19" spans="2:20" ht="18">
       <c r="B19" s="5" t="s">
@@ -2072,15 +2125,15 @@
       <c r="K19" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="L19" s="17"/>
-      <c r="M19" s="9"/>
+      <c r="L19" s="36"/>
+      <c r="M19" s="10"/>
       <c r="N19" s="11"/>
-      <c r="O19" s="9"/>
-      <c r="P19" s="9"/>
-      <c r="Q19" s="9"/>
-      <c r="R19" s="9"/>
-      <c r="S19" s="9"/>
-      <c r="T19" s="9"/>
+      <c r="O19" s="10"/>
+      <c r="P19" s="10"/>
+      <c r="Q19" s="10"/>
+      <c r="R19" s="10"/>
+      <c r="S19" s="10"/>
+      <c r="T19" s="10"/>
     </row>
     <row r="20" spans="2:20" ht="18">
       <c r="B20" s="5" t="s">
@@ -2113,23 +2166,25 @@
       <c r="K20" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="L20" s="17">
+      <c r="L20" s="36">
         <v>12</v>
       </c>
-      <c r="M20" s="9">
+      <c r="M20" s="10">
         <v>4</v>
       </c>
       <c r="N20" s="11">
         <v>9</v>
       </c>
-      <c r="O20" s="9">
+      <c r="O20" s="10">
         <v>5</v>
       </c>
-      <c r="P20" s="9"/>
-      <c r="Q20" s="9"/>
-      <c r="R20" s="9"/>
-      <c r="S20" s="9"/>
-      <c r="T20" s="9"/>
+      <c r="P20" s="10">
+        <v>10</v>
+      </c>
+      <c r="Q20" s="10"/>
+      <c r="R20" s="10"/>
+      <c r="S20" s="10"/>
+      <c r="T20" s="10"/>
     </row>
     <row r="21" spans="2:20" ht="18">
       <c r="B21" s="5" t="s">
@@ -2162,21 +2217,21 @@
       <c r="K21" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="L21" s="17">
+      <c r="L21" s="36">
         <v>12</v>
       </c>
-      <c r="M21" s="9">
+      <c r="M21" s="10">
         <v>5</v>
       </c>
       <c r="N21" s="11"/>
-      <c r="O21" s="9">
+      <c r="O21" s="10">
         <v>5</v>
       </c>
-      <c r="P21" s="9"/>
-      <c r="Q21" s="9"/>
-      <c r="R21" s="9"/>
-      <c r="S21" s="9"/>
-      <c r="T21" s="9"/>
+      <c r="P21" s="10"/>
+      <c r="Q21" s="10"/>
+      <c r="R21" s="10"/>
+      <c r="S21" s="10"/>
+      <c r="T21" s="10"/>
     </row>
     <row r="22" spans="2:20" ht="18">
       <c r="B22" s="5" t="s">
@@ -2209,23 +2264,25 @@
       <c r="K22" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="L22" s="17">
-        <v>10</v>
-      </c>
-      <c r="M22" s="9">
+      <c r="L22" s="36">
+        <v>10</v>
+      </c>
+      <c r="M22" s="10">
         <v>7</v>
       </c>
       <c r="N22" s="11">
         <v>7</v>
       </c>
-      <c r="O22" s="9">
-        <v>10</v>
-      </c>
-      <c r="P22" s="9"/>
-      <c r="Q22" s="9"/>
-      <c r="R22" s="9"/>
-      <c r="S22" s="9"/>
-      <c r="T22" s="9"/>
+      <c r="O22" s="10">
+        <v>10</v>
+      </c>
+      <c r="P22" s="10">
+        <v>10</v>
+      </c>
+      <c r="Q22" s="10"/>
+      <c r="R22" s="10"/>
+      <c r="S22" s="10"/>
+      <c r="T22" s="10"/>
     </row>
     <row r="23" spans="2:20" ht="18">
       <c r="B23" s="5" t="s">
@@ -2258,23 +2315,25 @@
       <c r="K23" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="L23" s="17">
+      <c r="L23" s="36">
         <v>8</v>
       </c>
-      <c r="M23" s="9">
+      <c r="M23" s="10">
         <v>7</v>
       </c>
       <c r="N23" s="11">
         <v>10</v>
       </c>
-      <c r="O23" s="9">
-        <v>10</v>
-      </c>
-      <c r="P23" s="9"/>
-      <c r="Q23" s="9"/>
-      <c r="R23" s="9"/>
-      <c r="S23" s="9"/>
-      <c r="T23" s="9"/>
+      <c r="O23" s="10">
+        <v>10</v>
+      </c>
+      <c r="P23" s="10">
+        <v>10</v>
+      </c>
+      <c r="Q23" s="10"/>
+      <c r="R23" s="10"/>
+      <c r="S23" s="10"/>
+      <c r="T23" s="10"/>
     </row>
     <row r="24" spans="2:20" ht="18">
       <c r="B24" s="5" t="s">
@@ -2307,23 +2366,25 @@
       <c r="K24" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="L24" s="17">
+      <c r="L24" s="36">
         <v>11</v>
       </c>
-      <c r="M24" s="9">
+      <c r="M24" s="10">
         <v>10</v>
       </c>
       <c r="N24" s="11">
         <v>7</v>
       </c>
-      <c r="O24" s="9">
-        <v>10</v>
-      </c>
-      <c r="P24" s="9"/>
-      <c r="Q24" s="9"/>
-      <c r="R24" s="9"/>
-      <c r="S24" s="9"/>
-      <c r="T24" s="9"/>
+      <c r="O24" s="10">
+        <v>10</v>
+      </c>
+      <c r="P24" s="10">
+        <v>10</v>
+      </c>
+      <c r="Q24" s="10"/>
+      <c r="R24" s="10"/>
+      <c r="S24" s="10"/>
+      <c r="T24" s="10"/>
     </row>
     <row r="25" spans="2:20" ht="18">
       <c r="B25" s="5" t="s">
@@ -2356,23 +2417,25 @@
       <c r="K25" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="L25" s="17">
+      <c r="L25" s="36">
         <v>6</v>
       </c>
-      <c r="M25" s="9">
+      <c r="M25" s="10">
         <v>7</v>
       </c>
       <c r="N25" s="11">
         <v>7</v>
       </c>
-      <c r="O25" s="9">
+      <c r="O25" s="10">
         <v>5</v>
       </c>
-      <c r="P25" s="9"/>
-      <c r="Q25" s="9"/>
-      <c r="R25" s="9"/>
-      <c r="S25" s="9"/>
-      <c r="T25" s="9"/>
+      <c r="P25" s="10">
+        <v>10</v>
+      </c>
+      <c r="Q25" s="10"/>
+      <c r="R25" s="10"/>
+      <c r="S25" s="10"/>
+      <c r="T25" s="10"/>
     </row>
     <row r="26" spans="2:20" ht="18">
       <c r="B26" s="5" t="s">
@@ -2405,23 +2468,25 @@
       <c r="K26" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="L26" s="17">
+      <c r="L26" s="36">
         <v>12</v>
       </c>
-      <c r="M26" s="9">
+      <c r="M26" s="10">
         <v>5</v>
       </c>
       <c r="N26" s="11">
         <v>10</v>
       </c>
-      <c r="O26" s="9">
-        <v>10</v>
-      </c>
-      <c r="P26" s="9"/>
-      <c r="Q26" s="9"/>
-      <c r="R26" s="9"/>
-      <c r="S26" s="9"/>
-      <c r="T26" s="9"/>
+      <c r="O26" s="10">
+        <v>10</v>
+      </c>
+      <c r="P26" s="10">
+        <v>10</v>
+      </c>
+      <c r="Q26" s="10"/>
+      <c r="R26" s="10"/>
+      <c r="S26" s="10"/>
+      <c r="T26" s="10"/>
     </row>
     <row r="27" spans="2:20" ht="18">
       <c r="B27" s="5" t="s">
@@ -2454,21 +2519,23 @@
       <c r="K27" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="L27" s="17">
+      <c r="L27" s="36">
         <v>7</v>
       </c>
-      <c r="M27" s="9">
+      <c r="M27" s="10">
         <v>5</v>
       </c>
       <c r="N27" s="11"/>
-      <c r="O27" s="9">
-        <v>10</v>
-      </c>
-      <c r="P27" s="9"/>
-      <c r="Q27" s="9"/>
-      <c r="R27" s="9"/>
-      <c r="S27" s="9"/>
-      <c r="T27" s="9"/>
+      <c r="O27" s="10">
+        <v>10</v>
+      </c>
+      <c r="P27" s="10">
+        <v>10</v>
+      </c>
+      <c r="Q27" s="10"/>
+      <c r="R27" s="10"/>
+      <c r="S27" s="10"/>
+      <c r="T27" s="10"/>
     </row>
     <row r="28" spans="2:20" ht="18">
       <c r="B28" s="5" t="s">
@@ -2501,21 +2568,21 @@
       <c r="K28" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="L28" s="17">
+      <c r="L28" s="36">
         <v>7</v>
       </c>
-      <c r="M28" s="9"/>
+      <c r="M28" s="10"/>
       <c r="N28" s="11">
         <v>7</v>
       </c>
-      <c r="O28" s="9">
+      <c r="O28" s="10">
         <v>4</v>
       </c>
-      <c r="P28" s="9"/>
-      <c r="Q28" s="9"/>
-      <c r="R28" s="9"/>
-      <c r="S28" s="9"/>
-      <c r="T28" s="9"/>
+      <c r="P28" s="10"/>
+      <c r="Q28" s="10"/>
+      <c r="R28" s="10"/>
+      <c r="S28" s="10"/>
+      <c r="T28" s="10"/>
     </row>
     <row r="29" spans="2:20" ht="18">
       <c r="B29" s="5" t="s">
@@ -2548,23 +2615,25 @@
       <c r="K29" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="L29" s="17">
+      <c r="L29" s="36">
         <v>6</v>
       </c>
-      <c r="M29" s="9">
+      <c r="M29" s="10">
         <v>8</v>
       </c>
       <c r="N29" s="11">
         <v>10</v>
       </c>
-      <c r="O29" s="9">
-        <v>10</v>
-      </c>
-      <c r="P29" s="9"/>
-      <c r="Q29" s="9"/>
-      <c r="R29" s="9"/>
-      <c r="S29" s="9"/>
-      <c r="T29" s="9"/>
+      <c r="O29" s="10">
+        <v>10</v>
+      </c>
+      <c r="P29" s="10">
+        <v>10</v>
+      </c>
+      <c r="Q29" s="10"/>
+      <c r="R29" s="10"/>
+      <c r="S29" s="10"/>
+      <c r="T29" s="10"/>
     </row>
     <row r="30" spans="2:20" ht="18">
       <c r="B30" s="5" t="s">
@@ -2597,23 +2666,25 @@
       <c r="K30" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="L30" s="17">
+      <c r="L30" s="36">
         <v>12</v>
       </c>
-      <c r="M30" s="9">
+      <c r="M30" s="10">
         <v>10</v>
       </c>
       <c r="N30" s="11">
         <v>10</v>
       </c>
-      <c r="O30" s="9">
-        <v>10</v>
-      </c>
-      <c r="P30" s="9"/>
-      <c r="Q30" s="9"/>
-      <c r="R30" s="9"/>
-      <c r="S30" s="9"/>
-      <c r="T30" s="9"/>
+      <c r="O30" s="10">
+        <v>10</v>
+      </c>
+      <c r="P30" s="10">
+        <v>10</v>
+      </c>
+      <c r="Q30" s="10"/>
+      <c r="R30" s="10"/>
+      <c r="S30" s="10"/>
+      <c r="T30" s="10"/>
     </row>
     <row r="31" spans="2:20" ht="18">
       <c r="B31" s="5" t="s">
@@ -2646,15 +2717,15 @@
       <c r="K31" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="L31" s="17"/>
-      <c r="M31" s="9"/>
+      <c r="L31" s="36"/>
+      <c r="M31" s="10"/>
       <c r="N31" s="11"/>
-      <c r="O31" s="9"/>
-      <c r="P31" s="9"/>
-      <c r="Q31" s="9"/>
-      <c r="R31" s="9"/>
-      <c r="S31" s="9"/>
-      <c r="T31" s="9"/>
+      <c r="O31" s="10"/>
+      <c r="P31" s="10"/>
+      <c r="Q31" s="10"/>
+      <c r="R31" s="10"/>
+      <c r="S31" s="10"/>
+      <c r="T31" s="10"/>
     </row>
     <row r="32" spans="2:20" ht="18">
       <c r="B32" s="5" t="s">
@@ -2687,23 +2758,25 @@
       <c r="K32" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="L32" s="17">
+      <c r="L32" s="36">
         <v>12</v>
       </c>
-      <c r="M32" s="9">
+      <c r="M32" s="10">
         <v>9</v>
       </c>
       <c r="N32" s="11">
         <v>10</v>
       </c>
-      <c r="O32" s="9">
-        <v>10</v>
-      </c>
-      <c r="P32" s="9"/>
-      <c r="Q32" s="9"/>
-      <c r="R32" s="9"/>
-      <c r="S32" s="9"/>
-      <c r="T32" s="9"/>
+      <c r="O32" s="10">
+        <v>10</v>
+      </c>
+      <c r="P32" s="10">
+        <v>10</v>
+      </c>
+      <c r="Q32" s="10"/>
+      <c r="R32" s="10"/>
+      <c r="S32" s="10"/>
+      <c r="T32" s="10"/>
     </row>
     <row r="33" spans="2:20" ht="18">
       <c r="B33" s="5" t="s">
@@ -2736,68 +2809,72 @@
       <c r="K33" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="L33" s="17">
+      <c r="L33" s="36">
         <v>5</v>
       </c>
-      <c r="M33" s="9">
+      <c r="M33" s="10">
         <v>10</v>
       </c>
       <c r="N33" s="11"/>
-      <c r="O33" s="9">
-        <v>10</v>
-      </c>
-      <c r="P33" s="9"/>
-      <c r="Q33" s="9"/>
-      <c r="R33" s="9"/>
-      <c r="S33" s="9"/>
-      <c r="T33" s="9"/>
+      <c r="O33" s="10">
+        <v>10</v>
+      </c>
+      <c r="P33" s="10">
+        <v>10</v>
+      </c>
+      <c r="Q33" s="10"/>
+      <c r="R33" s="10"/>
+      <c r="S33" s="10"/>
+      <c r="T33" s="10"/>
     </row>
     <row r="34" spans="2:20" ht="18">
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="29" t="s">
         <v>182</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="29" t="s">
         <v>183</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="E34" s="29" t="s">
         <v>184</v>
       </c>
-      <c r="F34" s="4" t="s">
+      <c r="F34" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="G34" s="4" t="s">
+      <c r="G34" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="H34" s="4" t="s">
+      <c r="H34" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="I34" s="4" t="s">
+      <c r="I34" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="J34" s="4" t="s">
+      <c r="J34" s="29" t="s">
         <v>185</v>
       </c>
-      <c r="K34" s="7" t="s">
+      <c r="K34" s="30" t="s">
         <v>186</v>
       </c>
-      <c r="L34" s="17">
+      <c r="L34" s="31">
         <v>12</v>
       </c>
-      <c r="M34" s="9">
+      <c r="M34" s="31">
         <v>4</v>
       </c>
-      <c r="N34" s="11"/>
-      <c r="O34" s="9">
-        <v>10</v>
-      </c>
-      <c r="P34" s="9"/>
-      <c r="Q34" s="9"/>
-      <c r="R34" s="9"/>
-      <c r="S34" s="9"/>
-      <c r="T34" s="9"/>
+      <c r="N34" s="31"/>
+      <c r="O34" s="31">
+        <v>10</v>
+      </c>
+      <c r="P34" s="31">
+        <v>10</v>
+      </c>
+      <c r="Q34" s="31"/>
+      <c r="R34" s="31"/>
+      <c r="S34" s="31"/>
+      <c r="T34" s="31"/>
     </row>
     <row r="35" spans="2:20" ht="18">
       <c r="B35" s="5" t="s">
@@ -2830,23 +2907,25 @@
       <c r="K35" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="L35" s="17">
+      <c r="L35" s="36">
         <v>8</v>
       </c>
-      <c r="M35" s="9">
+      <c r="M35" s="10">
         <v>10</v>
       </c>
       <c r="N35" s="11">
         <v>10</v>
       </c>
-      <c r="O35" s="9">
-        <v>10</v>
-      </c>
-      <c r="P35" s="9"/>
-      <c r="Q35" s="9"/>
-      <c r="R35" s="9"/>
-      <c r="S35" s="9"/>
-      <c r="T35" s="9"/>
+      <c r="O35" s="10">
+        <v>10</v>
+      </c>
+      <c r="P35" s="10">
+        <v>10</v>
+      </c>
+      <c r="Q35" s="10"/>
+      <c r="R35" s="10"/>
+      <c r="S35" s="10"/>
+      <c r="T35" s="10"/>
     </row>
     <row r="36" spans="2:20" ht="18">
       <c r="B36" s="5" t="s">
@@ -2879,23 +2958,25 @@
       <c r="K36" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="L36" s="17">
+      <c r="L36" s="36">
         <v>12</v>
       </c>
-      <c r="M36" s="9">
+      <c r="M36" s="10">
         <v>8</v>
       </c>
       <c r="N36" s="11">
         <v>7</v>
       </c>
-      <c r="O36" s="9">
-        <v>10</v>
-      </c>
-      <c r="P36" s="9"/>
-      <c r="Q36" s="9"/>
-      <c r="R36" s="9"/>
-      <c r="S36" s="9"/>
-      <c r="T36" s="9"/>
+      <c r="O36" s="10">
+        <v>10</v>
+      </c>
+      <c r="P36" s="10">
+        <v>10</v>
+      </c>
+      <c r="Q36" s="10"/>
+      <c r="R36" s="10"/>
+      <c r="S36" s="10"/>
+      <c r="T36" s="10"/>
     </row>
     <row r="37" spans="2:20" ht="18">
       <c r="B37" s="5" t="s">
@@ -2928,23 +3009,25 @@
       <c r="K37" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="L37" s="17">
+      <c r="L37" s="36">
         <v>11</v>
       </c>
-      <c r="M37" s="9">
+      <c r="M37" s="10">
         <v>8</v>
       </c>
       <c r="N37" s="11">
         <v>10</v>
       </c>
-      <c r="O37" s="9">
-        <v>10</v>
-      </c>
-      <c r="P37" s="9"/>
-      <c r="Q37" s="9"/>
-      <c r="R37" s="9"/>
-      <c r="S37" s="9"/>
-      <c r="T37" s="9"/>
+      <c r="O37" s="10">
+        <v>10</v>
+      </c>
+      <c r="P37" s="10">
+        <v>9</v>
+      </c>
+      <c r="Q37" s="10"/>
+      <c r="R37" s="10"/>
+      <c r="S37" s="10"/>
+      <c r="T37" s="10"/>
     </row>
     <row r="38" spans="2:20" ht="18">
       <c r="B38" s="5" t="s">
@@ -2977,21 +3060,23 @@
       <c r="K38" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="L38" s="17"/>
-      <c r="M38" s="9">
+      <c r="L38" s="36"/>
+      <c r="M38" s="10">
         <v>5</v>
       </c>
       <c r="N38" s="11">
         <v>10</v>
       </c>
-      <c r="O38" s="9">
+      <c r="O38" s="10">
         <v>5</v>
       </c>
-      <c r="P38" s="9"/>
-      <c r="Q38" s="9"/>
-      <c r="R38" s="9"/>
-      <c r="S38" s="9"/>
-      <c r="T38" s="9"/>
+      <c r="P38" s="10">
+        <v>10</v>
+      </c>
+      <c r="Q38" s="10"/>
+      <c r="R38" s="10"/>
+      <c r="S38" s="10"/>
+      <c r="T38" s="10"/>
     </row>
     <row r="39" spans="2:20" ht="18">
       <c r="B39" s="5" t="s">
@@ -3024,23 +3109,25 @@
       <c r="K39" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="L39" s="17">
+      <c r="L39" s="36">
         <v>12</v>
       </c>
-      <c r="M39" s="9">
+      <c r="M39" s="10">
         <v>10</v>
       </c>
       <c r="N39" s="11">
         <v>10</v>
       </c>
-      <c r="O39" s="9">
-        <v>10</v>
-      </c>
-      <c r="P39" s="9"/>
-      <c r="Q39" s="9"/>
-      <c r="R39" s="9"/>
-      <c r="S39" s="9"/>
-      <c r="T39" s="9"/>
+      <c r="O39" s="10">
+        <v>10</v>
+      </c>
+      <c r="P39" s="10">
+        <v>10</v>
+      </c>
+      <c r="Q39" s="10"/>
+      <c r="R39" s="10"/>
+      <c r="S39" s="10"/>
+      <c r="T39" s="10"/>
     </row>
     <row r="40" spans="2:20" ht="18">
       <c r="B40" s="5" t="s">
@@ -3073,23 +3160,25 @@
       <c r="K40" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="L40" s="17">
+      <c r="L40" s="36">
         <v>11</v>
       </c>
-      <c r="M40" s="9">
+      <c r="M40" s="10">
         <v>9</v>
       </c>
       <c r="N40" s="11">
         <v>9</v>
       </c>
-      <c r="O40" s="9">
-        <v>10</v>
-      </c>
-      <c r="P40" s="9"/>
-      <c r="Q40" s="9"/>
-      <c r="R40" s="9"/>
-      <c r="S40" s="9"/>
-      <c r="T40" s="9"/>
+      <c r="O40" s="10">
+        <v>10</v>
+      </c>
+      <c r="P40" s="10">
+        <v>10</v>
+      </c>
+      <c r="Q40" s="10"/>
+      <c r="R40" s="10"/>
+      <c r="S40" s="10"/>
+      <c r="T40" s="10"/>
     </row>
     <row r="41" spans="2:20" ht="18">
       <c r="B41" s="5" t="s">
@@ -3122,23 +3211,25 @@
       <c r="K41" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="L41" s="17">
-        <v>10</v>
-      </c>
-      <c r="M41" s="9">
+      <c r="L41" s="36">
+        <v>10</v>
+      </c>
+      <c r="M41" s="10">
         <v>9</v>
       </c>
       <c r="N41" s="11">
         <v>10</v>
       </c>
-      <c r="O41" s="9">
-        <v>10</v>
-      </c>
-      <c r="P41" s="9"/>
-      <c r="Q41" s="9"/>
-      <c r="R41" s="9"/>
-      <c r="S41" s="9"/>
-      <c r="T41" s="9"/>
+      <c r="O41" s="10">
+        <v>10</v>
+      </c>
+      <c r="P41" s="10">
+        <v>10</v>
+      </c>
+      <c r="Q41" s="10"/>
+      <c r="R41" s="10"/>
+      <c r="S41" s="10"/>
+      <c r="T41" s="10"/>
     </row>
     <row r="42" spans="2:20" ht="18">
       <c r="B42" s="5" t="s">
@@ -3171,23 +3262,23 @@
       <c r="K42" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="L42" s="17">
-        <v>10</v>
-      </c>
-      <c r="M42" s="9">
+      <c r="L42" s="36">
+        <v>10</v>
+      </c>
+      <c r="M42" s="10">
         <v>7</v>
       </c>
       <c r="N42" s="11">
         <v>7</v>
       </c>
-      <c r="O42" s="9">
-        <v>10</v>
-      </c>
-      <c r="P42" s="9"/>
-      <c r="Q42" s="9"/>
-      <c r="R42" s="9"/>
-      <c r="S42" s="9"/>
-      <c r="T42" s="9"/>
+      <c r="O42" s="10">
+        <v>10</v>
+      </c>
+      <c r="P42" s="10"/>
+      <c r="Q42" s="10"/>
+      <c r="R42" s="10"/>
+      <c r="S42" s="10"/>
+      <c r="T42" s="10"/>
     </row>
     <row r="43" spans="2:20" ht="18">
       <c r="B43" s="5" t="s">
@@ -3220,23 +3311,25 @@
       <c r="K43" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="L43" s="17">
+      <c r="L43" s="36">
         <v>8</v>
       </c>
-      <c r="M43" s="9">
+      <c r="M43" s="10">
         <v>6</v>
       </c>
       <c r="N43" s="11">
         <v>10</v>
       </c>
-      <c r="O43" s="9">
+      <c r="O43" s="10">
         <v>5</v>
       </c>
-      <c r="P43" s="9"/>
-      <c r="Q43" s="9"/>
-      <c r="R43" s="9"/>
-      <c r="S43" s="9"/>
-      <c r="T43" s="9"/>
+      <c r="P43" s="10">
+        <v>9</v>
+      </c>
+      <c r="Q43" s="10"/>
+      <c r="R43" s="10"/>
+      <c r="S43" s="10"/>
+      <c r="T43" s="10"/>
     </row>
     <row r="44" spans="2:20" ht="18">
       <c r="B44" s="5" t="s">
@@ -3269,23 +3362,25 @@
       <c r="K44" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="L44" s="17">
+      <c r="L44" s="36">
         <v>5</v>
       </c>
-      <c r="M44" s="9">
+      <c r="M44" s="10">
         <v>10</v>
       </c>
       <c r="N44" s="11">
         <v>7</v>
       </c>
-      <c r="O44" s="9">
-        <v>10</v>
-      </c>
-      <c r="P44" s="9"/>
-      <c r="Q44" s="9"/>
-      <c r="R44" s="9"/>
-      <c r="S44" s="9"/>
-      <c r="T44" s="9"/>
+      <c r="O44" s="10">
+        <v>10</v>
+      </c>
+      <c r="P44" s="10">
+        <v>5</v>
+      </c>
+      <c r="Q44" s="10"/>
+      <c r="R44" s="10"/>
+      <c r="S44" s="10"/>
+      <c r="T44" s="10"/>
     </row>
     <row r="45" spans="2:20" ht="18">
       <c r="B45" s="5" t="s">
@@ -3318,23 +3413,25 @@
       <c r="K45" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="L45" s="17">
+      <c r="L45" s="36">
         <v>8</v>
       </c>
-      <c r="M45" s="9">
+      <c r="M45" s="10">
         <v>10</v>
       </c>
       <c r="N45" s="11">
         <v>10</v>
       </c>
-      <c r="O45" s="9">
-        <v>10</v>
-      </c>
-      <c r="P45" s="9"/>
-      <c r="Q45" s="9"/>
-      <c r="R45" s="9"/>
-      <c r="S45" s="9"/>
-      <c r="T45" s="9"/>
+      <c r="O45" s="10">
+        <v>10</v>
+      </c>
+      <c r="P45" s="10">
+        <v>9</v>
+      </c>
+      <c r="Q45" s="10"/>
+      <c r="R45" s="10"/>
+      <c r="S45" s="10"/>
+      <c r="T45" s="10"/>
     </row>
     <row r="46" spans="2:20" ht="18">
       <c r="B46" s="5" t="s">
@@ -3367,23 +3464,25 @@
       <c r="K46" s="7" t="s">
         <v>258</v>
       </c>
-      <c r="L46" s="17">
+      <c r="L46" s="36">
         <v>8</v>
       </c>
-      <c r="M46" s="9">
+      <c r="M46" s="10">
         <v>10</v>
       </c>
       <c r="N46" s="11">
         <v>7</v>
       </c>
-      <c r="O46" s="9">
+      <c r="O46" s="10">
         <v>8</v>
       </c>
-      <c r="P46" s="9"/>
-      <c r="Q46" s="9"/>
-      <c r="R46" s="9"/>
-      <c r="S46" s="9"/>
-      <c r="T46" s="9"/>
+      <c r="P46" s="10">
+        <v>10</v>
+      </c>
+      <c r="Q46" s="10"/>
+      <c r="R46" s="10"/>
+      <c r="S46" s="10"/>
+      <c r="T46" s="10"/>
     </row>
     <row r="47" spans="2:20" ht="18">
       <c r="B47" s="5" t="s">
@@ -3416,23 +3515,25 @@
       <c r="K47" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="L47" s="17">
-        <v>10</v>
-      </c>
-      <c r="M47" s="9">
+      <c r="L47" s="36">
+        <v>10</v>
+      </c>
+      <c r="M47" s="10">
         <v>10</v>
       </c>
       <c r="N47" s="11">
         <v>7</v>
       </c>
-      <c r="O47" s="9">
-        <v>10</v>
-      </c>
-      <c r="P47" s="9"/>
-      <c r="Q47" s="9"/>
-      <c r="R47" s="9"/>
-      <c r="S47" s="9"/>
-      <c r="T47" s="9"/>
+      <c r="O47" s="10">
+        <v>10</v>
+      </c>
+      <c r="P47" s="10">
+        <v>10</v>
+      </c>
+      <c r="Q47" s="10"/>
+      <c r="R47" s="10"/>
+      <c r="S47" s="10"/>
+      <c r="T47" s="10"/>
     </row>
     <row r="48" spans="2:20" ht="18">
       <c r="B48" s="5" t="s">
@@ -3465,23 +3566,25 @@
       <c r="K48" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="L48" s="17">
-        <v>10</v>
-      </c>
-      <c r="M48" s="9">
+      <c r="L48" s="36">
+        <v>10</v>
+      </c>
+      <c r="M48" s="10">
         <v>8</v>
       </c>
       <c r="N48" s="11">
         <v>7</v>
       </c>
-      <c r="O48" s="9">
-        <v>10</v>
-      </c>
-      <c r="P48" s="9"/>
-      <c r="Q48" s="9"/>
-      <c r="R48" s="9"/>
-      <c r="S48" s="9"/>
-      <c r="T48" s="9"/>
+      <c r="O48" s="10">
+        <v>10</v>
+      </c>
+      <c r="P48" s="10">
+        <v>10</v>
+      </c>
+      <c r="Q48" s="10"/>
+      <c r="R48" s="10"/>
+      <c r="S48" s="10"/>
+      <c r="T48" s="10"/>
     </row>
     <row r="49" spans="2:20" ht="18">
       <c r="B49" s="5" t="s">
@@ -3514,23 +3617,25 @@
       <c r="K49" s="7" t="s">
         <v>276</v>
       </c>
-      <c r="L49" s="17">
+      <c r="L49" s="36">
         <v>11</v>
       </c>
-      <c r="M49" s="9">
+      <c r="M49" s="10">
         <v>9</v>
       </c>
       <c r="N49" s="11">
         <v>10</v>
       </c>
-      <c r="O49" s="9">
-        <v>10</v>
-      </c>
-      <c r="P49" s="9"/>
-      <c r="Q49" s="9"/>
-      <c r="R49" s="9"/>
-      <c r="S49" s="9"/>
-      <c r="T49" s="9"/>
+      <c r="O49" s="10">
+        <v>10</v>
+      </c>
+      <c r="P49" s="10">
+        <v>10</v>
+      </c>
+      <c r="Q49" s="10"/>
+      <c r="R49" s="10"/>
+      <c r="S49" s="10"/>
+      <c r="T49" s="10"/>
     </row>
     <row r="50" spans="2:20" ht="18">
       <c r="B50" s="5" t="s">
@@ -3563,23 +3668,25 @@
       <c r="K50" s="7" t="s">
         <v>282</v>
       </c>
-      <c r="L50" s="17">
+      <c r="L50" s="36">
         <v>11</v>
       </c>
-      <c r="M50" s="9">
+      <c r="M50" s="10">
         <v>10</v>
       </c>
       <c r="N50" s="11">
         <v>10</v>
       </c>
-      <c r="O50" s="9">
+      <c r="O50" s="10">
         <v>5</v>
       </c>
-      <c r="P50" s="9"/>
-      <c r="Q50" s="9"/>
-      <c r="R50" s="9"/>
-      <c r="S50" s="9"/>
-      <c r="T50" s="9"/>
+      <c r="P50" s="10">
+        <v>10</v>
+      </c>
+      <c r="Q50" s="10"/>
+      <c r="R50" s="10"/>
+      <c r="S50" s="10"/>
+      <c r="T50" s="10"/>
     </row>
     <row r="51" spans="2:20" ht="18">
       <c r="B51" s="5" t="s">
@@ -3612,23 +3719,23 @@
       <c r="K51" s="7" t="s">
         <v>288</v>
       </c>
-      <c r="L51" s="17">
+      <c r="L51" s="36">
         <v>7</v>
       </c>
-      <c r="M51" s="9">
+      <c r="M51" s="10">
         <v>10</v>
       </c>
       <c r="N51" s="11">
         <v>7</v>
       </c>
-      <c r="O51" s="9">
-        <v>10</v>
-      </c>
-      <c r="P51" s="9"/>
-      <c r="Q51" s="9"/>
-      <c r="R51" s="9"/>
-      <c r="S51" s="9"/>
-      <c r="T51" s="9"/>
+      <c r="O51" s="10">
+        <v>10</v>
+      </c>
+      <c r="P51" s="10"/>
+      <c r="Q51" s="10"/>
+      <c r="R51" s="10"/>
+      <c r="S51" s="10"/>
+      <c r="T51" s="10"/>
     </row>
     <row r="52" spans="2:20" ht="18">
       <c r="B52" s="5" t="s">
@@ -3661,23 +3768,25 @@
       <c r="K52" s="7" t="s">
         <v>294</v>
       </c>
-      <c r="L52" s="17">
+      <c r="L52" s="36">
         <v>12</v>
       </c>
-      <c r="M52" s="9">
+      <c r="M52" s="10">
         <v>10</v>
       </c>
       <c r="N52" s="11">
         <v>10</v>
       </c>
-      <c r="O52" s="9">
-        <v>10</v>
-      </c>
-      <c r="P52" s="9"/>
-      <c r="Q52" s="9"/>
-      <c r="R52" s="9"/>
-      <c r="S52" s="9"/>
-      <c r="T52" s="9"/>
+      <c r="O52" s="10">
+        <v>10</v>
+      </c>
+      <c r="P52" s="10">
+        <v>8</v>
+      </c>
+      <c r="Q52" s="10"/>
+      <c r="R52" s="10"/>
+      <c r="S52" s="10"/>
+      <c r="T52" s="10"/>
     </row>
     <row r="53" spans="2:20" ht="18">
       <c r="B53" s="5" t="s">
@@ -3710,23 +3819,25 @@
       <c r="K53" s="7" t="s">
         <v>300</v>
       </c>
-      <c r="L53" s="17">
+      <c r="L53" s="36">
         <v>8</v>
       </c>
-      <c r="M53" s="9">
+      <c r="M53" s="10">
         <v>9</v>
       </c>
       <c r="N53" s="11">
         <v>10</v>
       </c>
-      <c r="O53" s="9">
-        <v>10</v>
-      </c>
-      <c r="P53" s="9"/>
-      <c r="Q53" s="9"/>
-      <c r="R53" s="9"/>
-      <c r="S53" s="9"/>
-      <c r="T53" s="9"/>
+      <c r="O53" s="10">
+        <v>10</v>
+      </c>
+      <c r="P53" s="10">
+        <v>10</v>
+      </c>
+      <c r="Q53" s="10"/>
+      <c r="R53" s="10"/>
+      <c r="S53" s="10"/>
+      <c r="T53" s="10"/>
     </row>
     <row r="56" spans="2:20" ht="18">
       <c r="B56" s="1"/>
@@ -3753,10 +3864,11 @@
     <col min="1" max="1" width="6.94921875" customWidth="1"/>
     <col min="2" max="2" width="16.19921875" customWidth="1"/>
     <col min="3" max="3" width="31.046875" customWidth="1"/>
-    <col min="4" max="4" width="3.796875" style="18" customWidth="1"/>
+    <col min="4" max="4" width="3.796875" style="15" customWidth="1"/>
     <col min="5" max="5" width="3.796875" customWidth="1"/>
-    <col min="6" max="6" width="3.796875" style="26" customWidth="1"/>
-    <col min="7" max="14" width="3.796875" customWidth="1"/>
+    <col min="6" max="6" width="3.796875" style="21" customWidth="1"/>
+    <col min="7" max="7" width="3.796875" style="24" customWidth="1"/>
+    <col min="8" max="14" width="3.796875" customWidth="1"/>
     <col min="15" max="15" width="8.796875" customWidth="1"/>
     <col min="16" max="26" width="4.6484375" customWidth="1"/>
   </cols>
@@ -3768,23 +3880,25 @@
       <c r="C6" s="10" t="s">
         <v>302</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="19" t="s">
         <v>303</v>
       </c>
-      <c r="E6" s="23" t="s">
+      <c r="E6" s="20" t="s">
         <v>304</v>
       </c>
-      <c r="F6" s="24" t="s">
+      <c r="F6" s="22" t="s">
         <v>307</v>
       </c>
-      <c r="G6" s="23"/>
-      <c r="H6" s="23"/>
-      <c r="I6" s="23"/>
-      <c r="J6" s="23"/>
-      <c r="K6" s="23"/>
-      <c r="L6" s="23"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="23"/>
+      <c r="G6" s="23" t="s">
+        <v>308</v>
+      </c>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
+      <c r="M6" s="20"/>
+      <c r="N6" s="20"/>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="9" t="str">
@@ -3799,17 +3913,17 @@
         <f>Exercise!D7</f>
         <v>ชื่อ-นามสกุล</v>
       </c>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
       <c r="F7" s="27"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="25"/>
-      <c r="I7" s="25"/>
-      <c r="J7" s="25"/>
-      <c r="K7" s="25"/>
-      <c r="L7" s="25"/>
-      <c r="M7" s="25"/>
-      <c r="N7" s="25"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="26"/>
+      <c r="I7" s="26"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="26"/>
+      <c r="L7" s="26"/>
+      <c r="M7" s="26"/>
+      <c r="N7" s="26"/>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="9" t="str">
@@ -3824,14 +3938,14 @@
         <f>Exercise!D8</f>
         <v>นายธีรพัส แก้วงาม</v>
       </c>
-      <c r="D8" s="19">
-        <v>1</v>
-      </c>
-      <c r="E8" s="21"/>
-      <c r="F8" s="28">
-        <v>1</v>
-      </c>
-      <c r="G8" s="9"/>
+      <c r="D8" s="16">
+        <v>1</v>
+      </c>
+      <c r="E8" s="18"/>
+      <c r="F8" s="17">
+        <v>1</v>
+      </c>
+      <c r="G8" s="25"/>
       <c r="H8" s="9"/>
       <c r="I8" s="9"/>
       <c r="J8" s="9"/>
@@ -3853,12 +3967,14 @@
         <f>Exercise!D9</f>
         <v>นางสาวนภัสสร นูมหันต์</v>
       </c>
-      <c r="D9" s="19"/>
-      <c r="E9" s="21">
-        <v>1</v>
-      </c>
-      <c r="F9" s="28"/>
-      <c r="G9" s="9"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="18">
+        <v>1</v>
+      </c>
+      <c r="F9" s="17"/>
+      <c r="G9" s="25">
+        <v>1</v>
+      </c>
       <c r="H9" s="9"/>
       <c r="I9" s="9"/>
       <c r="J9" s="9"/>
@@ -3880,12 +3996,12 @@
         <f>Exercise!D10</f>
         <v>นางสาวนรภร เจริญสลุง</v>
       </c>
-      <c r="D10" s="19"/>
-      <c r="E10" s="21">
-        <v>1</v>
-      </c>
-      <c r="F10" s="28"/>
-      <c r="G10" s="9"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="18">
+        <v>1</v>
+      </c>
+      <c r="F10" s="17"/>
+      <c r="G10" s="25"/>
       <c r="H10" s="9"/>
       <c r="I10" s="9"/>
       <c r="J10" s="9"/>
@@ -3907,16 +4023,18 @@
         <f>Exercise!D11</f>
         <v>นายบุนยามีน มะสง</v>
       </c>
-      <c r="D11" s="19">
-        <v>1</v>
-      </c>
-      <c r="E11" s="21">
-        <v>1</v>
-      </c>
-      <c r="F11" s="28">
-        <v>1</v>
-      </c>
-      <c r="G11" s="9"/>
+      <c r="D11" s="16">
+        <v>1</v>
+      </c>
+      <c r="E11" s="18">
+        <v>1</v>
+      </c>
+      <c r="F11" s="17">
+        <v>1</v>
+      </c>
+      <c r="G11" s="25">
+        <v>1</v>
+      </c>
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
       <c r="J11" s="9"/>
@@ -3938,16 +4056,18 @@
         <f>Exercise!D12</f>
         <v>นายปัญญานันท์ ทองแก้วเกิด</v>
       </c>
-      <c r="D12" s="19">
-        <v>1</v>
-      </c>
-      <c r="E12" s="21">
-        <v>1</v>
-      </c>
-      <c r="F12" s="28">
-        <v>1</v>
-      </c>
-      <c r="G12" s="9"/>
+      <c r="D12" s="16">
+        <v>1</v>
+      </c>
+      <c r="E12" s="18">
+        <v>1</v>
+      </c>
+      <c r="F12" s="17">
+        <v>1</v>
+      </c>
+      <c r="G12" s="25">
+        <v>1</v>
+      </c>
       <c r="H12" s="9"/>
       <c r="I12" s="9"/>
       <c r="J12" s="9"/>
@@ -3969,12 +4089,14 @@
         <f>Exercise!D13</f>
         <v>นางสาวภิญยดา ศรีแนน</v>
       </c>
-      <c r="D13" s="19"/>
-      <c r="E13" s="21">
-        <v>1</v>
-      </c>
-      <c r="F13" s="28"/>
-      <c r="G13" s="9"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="18">
+        <v>1</v>
+      </c>
+      <c r="F13" s="17"/>
+      <c r="G13" s="25">
+        <v>1</v>
+      </c>
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
       <c r="J13" s="9"/>
@@ -3996,14 +4118,16 @@
         <f>Exercise!D14</f>
         <v>นายภูริณ มานหมัด</v>
       </c>
-      <c r="D14" s="19">
-        <v>1</v>
-      </c>
-      <c r="E14" s="21"/>
-      <c r="F14" s="28">
-        <v>1</v>
-      </c>
-      <c r="G14" s="9"/>
+      <c r="D14" s="16">
+        <v>1</v>
+      </c>
+      <c r="E14" s="18"/>
+      <c r="F14" s="17">
+        <v>1</v>
+      </c>
+      <c r="G14" s="25">
+        <v>1</v>
+      </c>
       <c r="H14" s="9"/>
       <c r="I14" s="9"/>
       <c r="J14" s="9"/>
@@ -4025,16 +4149,18 @@
         <f>Exercise!D15</f>
         <v>นายรัชชานนท์ สาคะเรศ</v>
       </c>
-      <c r="D15" s="19">
-        <v>1</v>
-      </c>
-      <c r="E15" s="21">
-        <v>1</v>
-      </c>
-      <c r="F15" s="28">
-        <v>1</v>
-      </c>
-      <c r="G15" s="9"/>
+      <c r="D15" s="16">
+        <v>1</v>
+      </c>
+      <c r="E15" s="18">
+        <v>1</v>
+      </c>
+      <c r="F15" s="17">
+        <v>1</v>
+      </c>
+      <c r="G15" s="25">
+        <v>1</v>
+      </c>
       <c r="H15" s="9"/>
       <c r="I15" s="9"/>
       <c r="J15" s="9"/>
@@ -4056,16 +4182,18 @@
         <f>Exercise!D16</f>
         <v>นายวรพล พลอยชัด</v>
       </c>
-      <c r="D16" s="19">
-        <v>1</v>
-      </c>
-      <c r="E16" s="21">
-        <v>1</v>
-      </c>
-      <c r="F16" s="28">
-        <v>1</v>
-      </c>
-      <c r="G16" s="9"/>
+      <c r="D16" s="16">
+        <v>1</v>
+      </c>
+      <c r="E16" s="18">
+        <v>1</v>
+      </c>
+      <c r="F16" s="17">
+        <v>1</v>
+      </c>
+      <c r="G16" s="25">
+        <v>1</v>
+      </c>
       <c r="H16" s="9"/>
       <c r="I16" s="9"/>
       <c r="J16" s="9"/>
@@ -4087,16 +4215,18 @@
         <f>Exercise!D17</f>
         <v>นายศุภณัฐ จันทรังษี</v>
       </c>
-      <c r="D17" s="19">
-        <v>1</v>
-      </c>
-      <c r="E17" s="21">
-        <v>1</v>
-      </c>
-      <c r="F17" s="28">
-        <v>1</v>
-      </c>
-      <c r="G17" s="9"/>
+      <c r="D17" s="16">
+        <v>1</v>
+      </c>
+      <c r="E17" s="18">
+        <v>1</v>
+      </c>
+      <c r="F17" s="17">
+        <v>1</v>
+      </c>
+      <c r="G17" s="25">
+        <v>1</v>
+      </c>
       <c r="H17" s="9"/>
       <c r="I17" s="9"/>
       <c r="J17" s="9"/>
@@ -4118,14 +4248,16 @@
         <f>Exercise!D18</f>
         <v>นางสาวเศรษฐกมล วังออมทรัพย์</v>
       </c>
-      <c r="D18" s="19"/>
-      <c r="E18" s="21">
-        <v>1</v>
-      </c>
-      <c r="F18" s="28">
-        <v>1</v>
-      </c>
-      <c r="G18" s="9"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="18">
+        <v>1</v>
+      </c>
+      <c r="F18" s="17">
+        <v>1</v>
+      </c>
+      <c r="G18" s="25">
+        <v>1</v>
+      </c>
       <c r="H18" s="9"/>
       <c r="I18" s="9"/>
       <c r="J18" s="9"/>
@@ -4147,10 +4279,12 @@
         <f>Exercise!D19</f>
         <v>นางสาวอริศรา เล่งกูล</v>
       </c>
-      <c r="D19" s="19"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="9"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="25">
+        <v>1</v>
+      </c>
       <c r="H19" s="9"/>
       <c r="I19" s="9"/>
       <c r="J19" s="9"/>
@@ -4172,12 +4306,14 @@
         <f>Exercise!D20</f>
         <v>นายภัทรพล ดิษฐาพร</v>
       </c>
-      <c r="D20" s="19"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="28">
-        <v>1</v>
-      </c>
-      <c r="G20" s="9"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="17">
+        <v>1</v>
+      </c>
+      <c r="G20" s="25">
+        <v>1</v>
+      </c>
       <c r="H20" s="9"/>
       <c r="I20" s="9"/>
       <c r="J20" s="9"/>
@@ -4199,14 +4335,14 @@
         <f>Exercise!D21</f>
         <v>นายภาคิน แซ่โง้ว</v>
       </c>
-      <c r="D21" s="19">
-        <v>1</v>
-      </c>
-      <c r="E21" s="21">
-        <v>1</v>
-      </c>
-      <c r="F21" s="28"/>
-      <c r="G21" s="9"/>
+      <c r="D21" s="16">
+        <v>1</v>
+      </c>
+      <c r="E21" s="18">
+        <v>1</v>
+      </c>
+      <c r="F21" s="17"/>
+      <c r="G21" s="25"/>
       <c r="H21" s="9"/>
       <c r="I21" s="9"/>
       <c r="J21" s="9"/>
@@ -4228,16 +4364,18 @@
         <f>Exercise!D22</f>
         <v>นายกนล แสงเดช</v>
       </c>
-      <c r="D22" s="19">
-        <v>1</v>
-      </c>
-      <c r="E22" s="21">
-        <v>1</v>
-      </c>
-      <c r="F22" s="28">
-        <v>1</v>
-      </c>
-      <c r="G22" s="9"/>
+      <c r="D22" s="16">
+        <v>1</v>
+      </c>
+      <c r="E22" s="18">
+        <v>1</v>
+      </c>
+      <c r="F22" s="17">
+        <v>1</v>
+      </c>
+      <c r="G22" s="25">
+        <v>1</v>
+      </c>
       <c r="H22" s="9"/>
       <c r="I22" s="9"/>
       <c r="J22" s="9"/>
@@ -4259,16 +4397,18 @@
         <f>Exercise!D23</f>
         <v>นางสาวกมลนิตย์ โตอยู่</v>
       </c>
-      <c r="D23" s="19">
-        <v>1</v>
-      </c>
-      <c r="E23" s="21">
-        <v>1</v>
-      </c>
-      <c r="F23" s="28">
-        <v>1</v>
-      </c>
-      <c r="G23" s="9"/>
+      <c r="D23" s="16">
+        <v>1</v>
+      </c>
+      <c r="E23" s="18">
+        <v>1</v>
+      </c>
+      <c r="F23" s="17">
+        <v>1</v>
+      </c>
+      <c r="G23" s="25">
+        <v>1</v>
+      </c>
       <c r="H23" s="9"/>
       <c r="I23" s="9"/>
       <c r="J23" s="9"/>
@@ -4290,16 +4430,18 @@
         <f>Exercise!D24</f>
         <v>นายกฤษกร ศรีสัจจัง</v>
       </c>
-      <c r="D24" s="19">
-        <v>1</v>
-      </c>
-      <c r="E24" s="21">
-        <v>1</v>
-      </c>
-      <c r="F24" s="28">
-        <v>1</v>
-      </c>
-      <c r="G24" s="9"/>
+      <c r="D24" s="16">
+        <v>1</v>
+      </c>
+      <c r="E24" s="18">
+        <v>1</v>
+      </c>
+      <c r="F24" s="17">
+        <v>1</v>
+      </c>
+      <c r="G24" s="25">
+        <v>1</v>
+      </c>
       <c r="H24" s="9"/>
       <c r="I24" s="9"/>
       <c r="J24" s="9"/>
@@ -4321,16 +4463,18 @@
         <f>Exercise!D25</f>
         <v>นายกันติวัสส์ ตันตระการย์</v>
       </c>
-      <c r="D25" s="19">
-        <v>1</v>
-      </c>
-      <c r="E25" s="21">
-        <v>1</v>
-      </c>
-      <c r="F25" s="28">
-        <v>1</v>
-      </c>
-      <c r="G25" s="9"/>
+      <c r="D25" s="16">
+        <v>1</v>
+      </c>
+      <c r="E25" s="18">
+        <v>1</v>
+      </c>
+      <c r="F25" s="17">
+        <v>1</v>
+      </c>
+      <c r="G25" s="25">
+        <v>1</v>
+      </c>
       <c r="H25" s="9"/>
       <c r="I25" s="9"/>
       <c r="J25" s="9"/>
@@ -4352,16 +4496,18 @@
         <f>Exercise!D26</f>
         <v>นายเกษมโชค นชะพงษ์</v>
       </c>
-      <c r="D26" s="19">
-        <v>1</v>
-      </c>
-      <c r="E26" s="21">
-        <v>1</v>
-      </c>
-      <c r="F26" s="28">
-        <v>1</v>
-      </c>
-      <c r="G26" s="9"/>
+      <c r="D26" s="16">
+        <v>1</v>
+      </c>
+      <c r="E26" s="18">
+        <v>1</v>
+      </c>
+      <c r="F26" s="17">
+        <v>1</v>
+      </c>
+      <c r="G26" s="25">
+        <v>1</v>
+      </c>
       <c r="H26" s="9"/>
       <c r="I26" s="9"/>
       <c r="J26" s="9"/>
@@ -4383,14 +4529,16 @@
         <f>Exercise!D27</f>
         <v>นายจักรินทร์ อินทร์น้อย</v>
       </c>
-      <c r="D27" s="19"/>
-      <c r="E27" s="21">
-        <v>1</v>
-      </c>
-      <c r="F27" s="28">
-        <v>1</v>
-      </c>
-      <c r="G27" s="9"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="18">
+        <v>1</v>
+      </c>
+      <c r="F27" s="17">
+        <v>1</v>
+      </c>
+      <c r="G27" s="25">
+        <v>1</v>
+      </c>
       <c r="H27" s="9"/>
       <c r="I27" s="9"/>
       <c r="J27" s="9"/>
@@ -4412,14 +4560,16 @@
         <f>Exercise!D28</f>
         <v>นางสาวจันทร์เจ้า เทพจิตต์</v>
       </c>
-      <c r="D28" s="19"/>
-      <c r="E28" s="21">
-        <v>1</v>
-      </c>
-      <c r="F28" s="28">
-        <v>1</v>
-      </c>
-      <c r="G28" s="9"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="18">
+        <v>1</v>
+      </c>
+      <c r="F28" s="17">
+        <v>1</v>
+      </c>
+      <c r="G28" s="25">
+        <v>1</v>
+      </c>
       <c r="H28" s="9"/>
       <c r="I28" s="9"/>
       <c r="J28" s="9"/>
@@ -4441,16 +4591,18 @@
         <f>Exercise!D29</f>
         <v>นางสาวฑิฆัมพร ตรีบุสยะรัตน์</v>
       </c>
-      <c r="D29" s="19">
-        <v>1</v>
-      </c>
-      <c r="E29" s="21">
-        <v>1</v>
-      </c>
-      <c r="F29" s="28">
-        <v>1</v>
-      </c>
-      <c r="G29" s="9"/>
+      <c r="D29" s="16">
+        <v>1</v>
+      </c>
+      <c r="E29" s="18">
+        <v>1</v>
+      </c>
+      <c r="F29" s="17">
+        <v>1</v>
+      </c>
+      <c r="G29" s="25">
+        <v>1</v>
+      </c>
       <c r="H29" s="9"/>
       <c r="I29" s="9"/>
       <c r="J29" s="9"/>
@@ -4472,16 +4624,18 @@
         <f>Exercise!D30</f>
         <v>นางสาวณปภัช บุญมายศ</v>
       </c>
-      <c r="D30" s="19">
-        <v>1</v>
-      </c>
-      <c r="E30" s="21">
-        <v>1</v>
-      </c>
-      <c r="F30" s="28">
-        <v>1</v>
-      </c>
-      <c r="G30" s="9"/>
+      <c r="D30" s="16">
+        <v>1</v>
+      </c>
+      <c r="E30" s="18">
+        <v>1</v>
+      </c>
+      <c r="F30" s="17">
+        <v>1</v>
+      </c>
+      <c r="G30" s="25">
+        <v>1</v>
+      </c>
       <c r="H30" s="9"/>
       <c r="I30" s="9"/>
       <c r="J30" s="9"/>
@@ -4503,10 +4657,10 @@
         <f>Exercise!D31</f>
         <v>นายธนทัต มุทธากาญจน์</v>
       </c>
-      <c r="D31" s="19"/>
-      <c r="E31" s="21"/>
-      <c r="F31" s="28"/>
-      <c r="G31" s="9"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="17"/>
+      <c r="G31" s="25"/>
       <c r="H31" s="9"/>
       <c r="I31" s="9"/>
       <c r="J31" s="9"/>
@@ -4528,16 +4682,18 @@
         <f>Exercise!D32</f>
         <v>นายธนภูมิ เหลืองชัยพัฒนา</v>
       </c>
-      <c r="D32" s="19">
-        <v>1</v>
-      </c>
-      <c r="E32" s="21">
-        <v>1</v>
-      </c>
-      <c r="F32" s="28">
-        <v>1</v>
-      </c>
-      <c r="G32" s="9"/>
+      <c r="D32" s="16">
+        <v>1</v>
+      </c>
+      <c r="E32" s="18">
+        <v>1</v>
+      </c>
+      <c r="F32" s="17">
+        <v>1</v>
+      </c>
+      <c r="G32" s="25">
+        <v>1</v>
+      </c>
       <c r="H32" s="9"/>
       <c r="I32" s="9"/>
       <c r="J32" s="9"/>
@@ -4559,14 +4715,16 @@
         <f>Exercise!D33</f>
         <v>นายธนากร เรืองพูน</v>
       </c>
-      <c r="D33" s="19"/>
-      <c r="E33" s="21">
-        <v>1</v>
-      </c>
-      <c r="F33" s="28">
-        <v>1</v>
-      </c>
-      <c r="G33" s="9"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="18">
+        <v>1</v>
+      </c>
+      <c r="F33" s="17">
+        <v>1</v>
+      </c>
+      <c r="G33" s="25">
+        <v>1</v>
+      </c>
       <c r="H33" s="9"/>
       <c r="I33" s="9"/>
       <c r="J33" s="9"/>
@@ -4588,16 +4746,18 @@
         <f>Exercise!D34</f>
         <v>นายธรรมกร เจริญพร</v>
       </c>
-      <c r="D34" s="19">
-        <v>1</v>
-      </c>
-      <c r="E34" s="21">
-        <v>1</v>
-      </c>
-      <c r="F34" s="28">
-        <v>1</v>
-      </c>
-      <c r="G34" s="9"/>
+      <c r="D34" s="16">
+        <v>1</v>
+      </c>
+      <c r="E34" s="18">
+        <v>1</v>
+      </c>
+      <c r="F34" s="17">
+        <v>1</v>
+      </c>
+      <c r="G34" s="25">
+        <v>1</v>
+      </c>
       <c r="H34" s="9"/>
       <c r="I34" s="9"/>
       <c r="J34" s="9"/>
@@ -4619,16 +4779,18 @@
         <f>Exercise!D35</f>
         <v>นางสาวธัชตะวัน ยกโต</v>
       </c>
-      <c r="D35" s="19">
-        <v>1</v>
-      </c>
-      <c r="E35" s="21">
-        <v>1</v>
-      </c>
-      <c r="F35" s="28">
-        <v>1</v>
-      </c>
-      <c r="G35" s="9"/>
+      <c r="D35" s="16">
+        <v>1</v>
+      </c>
+      <c r="E35" s="18">
+        <v>1</v>
+      </c>
+      <c r="F35" s="17">
+        <v>1</v>
+      </c>
+      <c r="G35" s="25">
+        <v>1</v>
+      </c>
       <c r="H35" s="9"/>
       <c r="I35" s="9"/>
       <c r="J35" s="9"/>
@@ -4650,16 +4812,18 @@
         <f>Exercise!D36</f>
         <v>นายนนทกร จวนทองรักษ์</v>
       </c>
-      <c r="D36" s="19">
-        <v>1</v>
-      </c>
-      <c r="E36" s="21">
-        <v>1</v>
-      </c>
-      <c r="F36" s="28">
-        <v>1</v>
-      </c>
-      <c r="G36" s="9"/>
+      <c r="D36" s="16">
+        <v>1</v>
+      </c>
+      <c r="E36" s="18">
+        <v>1</v>
+      </c>
+      <c r="F36" s="17">
+        <v>1</v>
+      </c>
+      <c r="G36" s="25">
+        <v>1</v>
+      </c>
       <c r="H36" s="9"/>
       <c r="I36" s="9"/>
       <c r="J36" s="9"/>
@@ -4681,16 +4845,18 @@
         <f>Exercise!D37</f>
         <v>นายนภัสรพี อร่ามฉิม</v>
       </c>
-      <c r="D37" s="19">
-        <v>1</v>
-      </c>
-      <c r="E37" s="21">
-        <v>1</v>
-      </c>
-      <c r="F37" s="28">
-        <v>1</v>
-      </c>
-      <c r="G37" s="9"/>
+      <c r="D37" s="16">
+        <v>1</v>
+      </c>
+      <c r="E37" s="18">
+        <v>1</v>
+      </c>
+      <c r="F37" s="17">
+        <v>1</v>
+      </c>
+      <c r="G37" s="25">
+        <v>1</v>
+      </c>
       <c r="H37" s="9"/>
       <c r="I37" s="9"/>
       <c r="J37" s="9"/>
@@ -4712,14 +4878,16 @@
         <f>Exercise!D38</f>
         <v>นายพิชญุตม์ ลอยมา</v>
       </c>
-      <c r="D38" s="19">
-        <v>1</v>
-      </c>
-      <c r="E38" s="21"/>
-      <c r="F38" s="28">
-        <v>1</v>
-      </c>
-      <c r="G38" s="9"/>
+      <c r="D38" s="16">
+        <v>1</v>
+      </c>
+      <c r="E38" s="18"/>
+      <c r="F38" s="17">
+        <v>1</v>
+      </c>
+      <c r="G38" s="25">
+        <v>1</v>
+      </c>
       <c r="H38" s="9"/>
       <c r="I38" s="9"/>
       <c r="J38" s="9"/>
@@ -4741,16 +4909,18 @@
         <f>Exercise!D39</f>
         <v>นายภควัฒน์ พรมประโคน</v>
       </c>
-      <c r="D39" s="19">
-        <v>1</v>
-      </c>
-      <c r="E39" s="21">
-        <v>1</v>
-      </c>
-      <c r="F39" s="28">
-        <v>1</v>
-      </c>
-      <c r="G39" s="9"/>
+      <c r="D39" s="16">
+        <v>1</v>
+      </c>
+      <c r="E39" s="18">
+        <v>1</v>
+      </c>
+      <c r="F39" s="17">
+        <v>1</v>
+      </c>
+      <c r="G39" s="25">
+        <v>1</v>
+      </c>
       <c r="H39" s="9"/>
       <c r="I39" s="9"/>
       <c r="J39" s="9"/>
@@ -4772,16 +4942,18 @@
         <f>Exercise!D40</f>
         <v>นายภัคพล ลาวชัย</v>
       </c>
-      <c r="D40" s="19">
-        <v>1</v>
-      </c>
-      <c r="E40" s="21">
-        <v>1</v>
-      </c>
-      <c r="F40" s="28">
-        <v>1</v>
-      </c>
-      <c r="G40" s="9"/>
+      <c r="D40" s="16">
+        <v>1</v>
+      </c>
+      <c r="E40" s="18">
+        <v>1</v>
+      </c>
+      <c r="F40" s="17">
+        <v>1</v>
+      </c>
+      <c r="G40" s="25">
+        <v>1</v>
+      </c>
       <c r="H40" s="9"/>
       <c r="I40" s="9"/>
       <c r="J40" s="9"/>
@@ -4803,16 +4975,18 @@
         <f>Exercise!D41</f>
         <v>นายภัคพล อินทะรังษี</v>
       </c>
-      <c r="D41" s="19">
-        <v>1</v>
-      </c>
-      <c r="E41" s="21">
-        <v>1</v>
-      </c>
-      <c r="F41" s="28">
-        <v>1</v>
-      </c>
-      <c r="G41" s="9"/>
+      <c r="D41" s="16">
+        <v>1</v>
+      </c>
+      <c r="E41" s="18">
+        <v>1</v>
+      </c>
+      <c r="F41" s="17">
+        <v>1</v>
+      </c>
+      <c r="G41" s="25">
+        <v>1</v>
+      </c>
       <c r="H41" s="9"/>
       <c r="I41" s="9"/>
       <c r="J41" s="9"/>
@@ -4834,16 +5008,18 @@
         <f>Exercise!D42</f>
         <v>นายยุทธนา สุขกำเนิด</v>
       </c>
-      <c r="D42" s="19">
-        <v>1</v>
-      </c>
-      <c r="E42" s="21">
-        <v>1</v>
-      </c>
-      <c r="F42" s="28">
-        <v>1</v>
-      </c>
-      <c r="G42" s="9"/>
+      <c r="D42" s="16">
+        <v>1</v>
+      </c>
+      <c r="E42" s="18">
+        <v>1</v>
+      </c>
+      <c r="F42" s="17">
+        <v>1</v>
+      </c>
+      <c r="G42" s="25">
+        <v>1</v>
+      </c>
       <c r="H42" s="9"/>
       <c r="I42" s="9"/>
       <c r="J42" s="9"/>
@@ -4865,16 +5041,18 @@
         <f>Exercise!D43</f>
         <v>นายรพีภัทร มอยนา</v>
       </c>
-      <c r="D43" s="19">
-        <v>1</v>
-      </c>
-      <c r="E43" s="21">
-        <v>1</v>
-      </c>
-      <c r="F43" s="28">
-        <v>1</v>
-      </c>
-      <c r="G43" s="9"/>
+      <c r="D43" s="16">
+        <v>1</v>
+      </c>
+      <c r="E43" s="18">
+        <v>1</v>
+      </c>
+      <c r="F43" s="17">
+        <v>1</v>
+      </c>
+      <c r="G43" s="25">
+        <v>1</v>
+      </c>
       <c r="H43" s="9"/>
       <c r="I43" s="9"/>
       <c r="J43" s="9"/>
@@ -4896,16 +5074,18 @@
         <f>Exercise!D44</f>
         <v>นายวีรภัทร ดีมาก</v>
       </c>
-      <c r="D44" s="19">
-        <v>1</v>
-      </c>
-      <c r="E44" s="21">
-        <v>1</v>
-      </c>
-      <c r="F44" s="28">
-        <v>1</v>
-      </c>
-      <c r="G44" s="9"/>
+      <c r="D44" s="16">
+        <v>1</v>
+      </c>
+      <c r="E44" s="18">
+        <v>1</v>
+      </c>
+      <c r="F44" s="17">
+        <v>1</v>
+      </c>
+      <c r="G44" s="25">
+        <v>1</v>
+      </c>
       <c r="H44" s="9"/>
       <c r="I44" s="9"/>
       <c r="J44" s="9"/>
@@ -4927,16 +5107,18 @@
         <f>Exercise!D45</f>
         <v>นางสาวศวิตา ไชยสุนทร</v>
       </c>
-      <c r="D45" s="19">
-        <v>1</v>
-      </c>
-      <c r="E45" s="21">
-        <v>1</v>
-      </c>
-      <c r="F45" s="28">
-        <v>1</v>
-      </c>
-      <c r="G45" s="9"/>
+      <c r="D45" s="16">
+        <v>1</v>
+      </c>
+      <c r="E45" s="18">
+        <v>1</v>
+      </c>
+      <c r="F45" s="17">
+        <v>1</v>
+      </c>
+      <c r="G45" s="25">
+        <v>1</v>
+      </c>
       <c r="H45" s="9"/>
       <c r="I45" s="9"/>
       <c r="J45" s="9"/>
@@ -4958,16 +5140,18 @@
         <f>Exercise!D46</f>
         <v>นายสรศักดิ์ โคตรนาม</v>
       </c>
-      <c r="D46" s="19">
-        <v>1</v>
-      </c>
-      <c r="E46" s="21">
-        <v>1</v>
-      </c>
-      <c r="F46" s="28">
-        <v>1</v>
-      </c>
-      <c r="G46" s="9"/>
+      <c r="D46" s="16">
+        <v>1</v>
+      </c>
+      <c r="E46" s="18">
+        <v>1</v>
+      </c>
+      <c r="F46" s="17">
+        <v>1</v>
+      </c>
+      <c r="G46" s="25">
+        <v>1</v>
+      </c>
       <c r="H46" s="9"/>
       <c r="I46" s="9"/>
       <c r="J46" s="9"/>
@@ -4989,16 +5173,18 @@
         <f>Exercise!D47</f>
         <v>นายสราวุฒิ ยะโส</v>
       </c>
-      <c r="D47" s="19">
-        <v>1</v>
-      </c>
-      <c r="E47" s="21">
-        <v>1</v>
-      </c>
-      <c r="F47" s="28">
-        <v>1</v>
-      </c>
-      <c r="G47" s="9"/>
+      <c r="D47" s="16">
+        <v>1</v>
+      </c>
+      <c r="E47" s="18">
+        <v>1</v>
+      </c>
+      <c r="F47" s="17">
+        <v>1</v>
+      </c>
+      <c r="G47" s="25">
+        <v>1</v>
+      </c>
       <c r="H47" s="9"/>
       <c r="I47" s="9"/>
       <c r="J47" s="9"/>
@@ -5020,16 +5206,18 @@
         <f>Exercise!D48</f>
         <v>นายสิทชัยเลิศ ศรนรายณ์</v>
       </c>
-      <c r="D48" s="19">
-        <v>1</v>
-      </c>
-      <c r="E48" s="21">
-        <v>1</v>
-      </c>
-      <c r="F48" s="28">
-        <v>1</v>
-      </c>
-      <c r="G48" s="9"/>
+      <c r="D48" s="16">
+        <v>1</v>
+      </c>
+      <c r="E48" s="18">
+        <v>1</v>
+      </c>
+      <c r="F48" s="17">
+        <v>1</v>
+      </c>
+      <c r="G48" s="25">
+        <v>1</v>
+      </c>
       <c r="H48" s="9"/>
       <c r="I48" s="9"/>
       <c r="J48" s="9"/>
@@ -5051,16 +5239,18 @@
         <f>Exercise!D49</f>
         <v>นายสุทธิโชติ ใบเตย</v>
       </c>
-      <c r="D49" s="19">
-        <v>1</v>
-      </c>
-      <c r="E49" s="21">
-        <v>1</v>
-      </c>
-      <c r="F49" s="28">
-        <v>1</v>
-      </c>
-      <c r="G49" s="9"/>
+      <c r="D49" s="16">
+        <v>1</v>
+      </c>
+      <c r="E49" s="18">
+        <v>1</v>
+      </c>
+      <c r="F49" s="17">
+        <v>1</v>
+      </c>
+      <c r="G49" s="25">
+        <v>1</v>
+      </c>
       <c r="H49" s="9"/>
       <c r="I49" s="9"/>
       <c r="J49" s="9"/>
@@ -5082,16 +5272,18 @@
         <f>Exercise!D50</f>
         <v>นายสุเมธ อบอารีย์</v>
       </c>
-      <c r="D50" s="19">
-        <v>1</v>
-      </c>
-      <c r="E50" s="21">
-        <v>1</v>
-      </c>
-      <c r="F50" s="28">
-        <v>1</v>
-      </c>
-      <c r="G50" s="9"/>
+      <c r="D50" s="16">
+        <v>1</v>
+      </c>
+      <c r="E50" s="18">
+        <v>1</v>
+      </c>
+      <c r="F50" s="17">
+        <v>1</v>
+      </c>
+      <c r="G50" s="25">
+        <v>1</v>
+      </c>
       <c r="H50" s="9"/>
       <c r="I50" s="9"/>
       <c r="J50" s="9"/>
@@ -5113,16 +5305,18 @@
         <f>Exercise!D51</f>
         <v>นายอัสนี คงดีจันทร์</v>
       </c>
-      <c r="D51" s="19">
-        <v>1</v>
-      </c>
-      <c r="E51" s="21">
-        <v>1</v>
-      </c>
-      <c r="F51" s="28">
-        <v>1</v>
-      </c>
-      <c r="G51" s="9"/>
+      <c r="D51" s="16">
+        <v>1</v>
+      </c>
+      <c r="E51" s="18">
+        <v>1</v>
+      </c>
+      <c r="F51" s="17">
+        <v>1</v>
+      </c>
+      <c r="G51" s="25">
+        <v>1</v>
+      </c>
       <c r="H51" s="9"/>
       <c r="I51" s="9"/>
       <c r="J51" s="9"/>
@@ -5144,16 +5338,18 @@
         <f>Exercise!D52</f>
         <v>นางสาวอาทิตยา ไทยเจริญ</v>
       </c>
-      <c r="D52" s="19">
-        <v>1</v>
-      </c>
-      <c r="E52" s="21">
-        <v>1</v>
-      </c>
-      <c r="F52" s="28">
-        <v>1</v>
-      </c>
-      <c r="G52" s="9"/>
+      <c r="D52" s="16">
+        <v>1</v>
+      </c>
+      <c r="E52" s="18">
+        <v>1</v>
+      </c>
+      <c r="F52" s="17">
+        <v>1</v>
+      </c>
+      <c r="G52" s="25">
+        <v>1</v>
+      </c>
       <c r="H52" s="9"/>
       <c r="I52" s="9"/>
       <c r="J52" s="9"/>
@@ -5175,16 +5371,18 @@
         <f>Exercise!D53</f>
         <v>นางสาวอารยา แสนสุข</v>
       </c>
-      <c r="D53" s="20">
-        <v>1</v>
-      </c>
-      <c r="E53" s="21">
-        <v>1</v>
-      </c>
-      <c r="F53" s="28">
-        <v>1</v>
-      </c>
-      <c r="G53" s="9"/>
+      <c r="D53" s="17">
+        <v>1</v>
+      </c>
+      <c r="E53" s="18">
+        <v>1</v>
+      </c>
+      <c r="F53" s="17">
+        <v>1</v>
+      </c>
+      <c r="G53" s="25">
+        <v>1</v>
+      </c>
       <c r="H53" s="9"/>
       <c r="I53" s="9"/>
       <c r="J53" s="9"/>

--- a/Score_Class_2026.xlsx
+++ b/Score_Class_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Phisan\Consultancy\2569-KU_MapProjection\Admin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC171A62-CAEC-4A91-A698-BF84F0C3AE8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6169C6B2-BA00-440E-BAC7-C62A4FDDBD8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39620" yWindow="-5780" windowWidth="28800" windowHeight="15200" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="39620" yWindow="-5780" windowWidth="25130" windowHeight="19430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Exercise" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="311">
   <si>
     <t>รายงานแสดงจำนวนนิสิต จำแนกตามหมู่เรียน ภาคต้น ปีการศึกษา 2569</t>
   </si>
@@ -961,6 +961,12 @@
   </si>
   <si>
     <t>24-Aug-2026\</t>
+  </si>
+  <si>
+    <t>MidTerm</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -970,7 +976,7 @@
   <numFmts count="1">
     <numFmt numFmtId="187" formatCode="B1d\-mmm\-yy"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -1008,6 +1014,26 @@
     <font>
       <sz val="12"/>
       <color theme="1" tint="4.9989318521683403E-2"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -1095,7 +1121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1182,12 +1208,6 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1196,6 +1216,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1427,50 +1462,50 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:20" ht="16" customHeight="1">
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="32"/>
-      <c r="M2" s="32"/>
-      <c r="N2" s="32"/>
-      <c r="O2" s="32"/>
-      <c r="P2" s="32"/>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="32"/>
-      <c r="S2" s="32"/>
-      <c r="T2" s="32"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="35"/>
+      <c r="L2" s="35"/>
+      <c r="M2" s="35"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
+      <c r="T2" s="35"/>
     </row>
     <row r="3" spans="2:20" ht="18.3" customHeight="1">
-      <c r="B3" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
-      <c r="J3" s="32"/>
-      <c r="K3" s="32"/>
-      <c r="L3" s="32"/>
-      <c r="M3" s="32"/>
-      <c r="N3" s="32"/>
-      <c r="O3" s="32"/>
-      <c r="P3" s="32"/>
-      <c r="Q3" s="32"/>
-      <c r="R3" s="32"/>
-      <c r="S3" s="32"/>
-      <c r="T3" s="32"/>
+      <c r="B3" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="35"/>
+      <c r="L3" s="35"/>
+      <c r="M3" s="35"/>
+      <c r="N3" s="35"/>
+      <c r="O3" s="35"/>
+      <c r="P3" s="35"/>
+      <c r="Q3" s="35"/>
+      <c r="R3" s="35"/>
+      <c r="S3" s="35"/>
+      <c r="T3" s="35"/>
     </row>
     <row r="4" spans="2:20" ht="26.1" customHeight="1">
       <c r="B4" s="1" t="s">
@@ -1479,16 +1514,16 @@
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="M4" s="33" t="s">
+      <c r="M4" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="N4" s="33"/>
-      <c r="O4" s="33"/>
-      <c r="P4" s="33"/>
-      <c r="Q4" s="33"/>
-      <c r="R4" s="33"/>
-      <c r="S4" s="33"/>
-      <c r="T4" s="33"/>
+      <c r="N4" s="36"/>
+      <c r="O4" s="36"/>
+      <c r="P4" s="36"/>
+      <c r="Q4" s="36"/>
+      <c r="R4" s="36"/>
+      <c r="S4" s="36"/>
+      <c r="T4" s="36"/>
     </row>
     <row r="5" spans="2:20" ht="18">
       <c r="E5" s="1" t="s">
@@ -1523,7 +1558,9 @@
       <c r="P6" s="12" t="s">
         <v>306</v>
       </c>
-      <c r="Q6" s="12"/>
+      <c r="Q6" s="39" t="s">
+        <v>309</v>
+      </c>
       <c r="R6" s="10"/>
       <c r="S6" s="10"/>
       <c r="T6" s="10"/>
@@ -1559,25 +1596,27 @@
       <c r="K7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="L7" s="34">
+      <c r="L7" s="32">
         <v>12</v>
       </c>
-      <c r="M7" s="35">
-        <v>10</v>
-      </c>
-      <c r="N7" s="35">
-        <v>10</v>
-      </c>
-      <c r="O7" s="35">
-        <v>10</v>
-      </c>
-      <c r="P7" s="35">
-        <v>10</v>
-      </c>
-      <c r="Q7" s="35"/>
-      <c r="R7" s="35"/>
-      <c r="S7" s="35"/>
-      <c r="T7" s="35"/>
+      <c r="M7" s="33">
+        <v>10</v>
+      </c>
+      <c r="N7" s="33">
+        <v>10</v>
+      </c>
+      <c r="O7" s="33">
+        <v>10</v>
+      </c>
+      <c r="P7" s="33">
+        <v>10</v>
+      </c>
+      <c r="Q7" s="37">
+        <v>26</v>
+      </c>
+      <c r="R7" s="33"/>
+      <c r="S7" s="33"/>
+      <c r="T7" s="33"/>
     </row>
     <row r="8" spans="2:20" ht="18">
       <c r="B8" s="5" t="s">
@@ -1610,14 +1649,16 @@
       <c r="K8" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="L8" s="36"/>
+      <c r="L8" s="34"/>
       <c r="M8" s="10"/>
       <c r="N8" s="11">
         <v>8</v>
       </c>
       <c r="O8" s="10"/>
       <c r="P8" s="10"/>
-      <c r="Q8" s="10"/>
+      <c r="Q8" s="10">
+        <v>10</v>
+      </c>
       <c r="R8" s="10"/>
       <c r="S8" s="10"/>
       <c r="T8" s="10"/>
@@ -1653,7 +1694,7 @@
       <c r="K9" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="L9" s="36"/>
+      <c r="L9" s="34"/>
       <c r="M9" s="10">
         <v>3</v>
       </c>
@@ -1662,7 +1703,9 @@
         <v>10</v>
       </c>
       <c r="P9" s="10"/>
-      <c r="Q9" s="10"/>
+      <c r="Q9" s="10">
+        <v>4</v>
+      </c>
       <c r="R9" s="10"/>
       <c r="S9" s="10"/>
       <c r="T9" s="10"/>
@@ -1698,7 +1741,7 @@
       <c r="K10" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L10" s="36"/>
+      <c r="L10" s="34"/>
       <c r="M10" s="10">
         <v>3</v>
       </c>
@@ -1709,7 +1752,9 @@
       <c r="P10" s="10">
         <v>8</v>
       </c>
-      <c r="Q10" s="10"/>
+      <c r="Q10" s="10">
+        <v>4</v>
+      </c>
       <c r="R10" s="10"/>
       <c r="S10" s="10"/>
       <c r="T10" s="10"/>
@@ -1745,7 +1790,7 @@
       <c r="K11" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="L11" s="36">
+      <c r="L11" s="34">
         <v>11</v>
       </c>
       <c r="M11" s="10">
@@ -1760,7 +1805,9 @@
       <c r="P11" s="10">
         <v>9</v>
       </c>
-      <c r="Q11" s="10"/>
+      <c r="Q11" s="10">
+        <v>9</v>
+      </c>
       <c r="R11" s="10"/>
       <c r="S11" s="10"/>
       <c r="T11" s="10"/>
@@ -1796,7 +1843,7 @@
       <c r="K12" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="L12" s="36"/>
+      <c r="L12" s="34"/>
       <c r="M12" s="10"/>
       <c r="N12" s="11">
         <v>7</v>
@@ -1805,7 +1852,9 @@
       <c r="P12" s="10">
         <v>10</v>
       </c>
-      <c r="Q12" s="10"/>
+      <c r="Q12" s="10">
+        <v>9</v>
+      </c>
       <c r="R12" s="10"/>
       <c r="S12" s="10"/>
       <c r="T12" s="10"/>
@@ -1841,12 +1890,14 @@
       <c r="K13" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="L13" s="36"/>
+      <c r="L13" s="34"/>
       <c r="M13" s="10"/>
       <c r="N13" s="11"/>
       <c r="O13" s="10"/>
       <c r="P13" s="10"/>
-      <c r="Q13" s="10"/>
+      <c r="Q13" s="10">
+        <v>0</v>
+      </c>
       <c r="R13" s="10"/>
       <c r="S13" s="10"/>
       <c r="T13" s="10"/>
@@ -1882,7 +1933,7 @@
       <c r="K14" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="L14" s="36"/>
+      <c r="L14" s="34"/>
       <c r="M14" s="10">
         <v>4</v>
       </c>
@@ -1893,7 +1944,9 @@
       <c r="P14" s="10">
         <v>8</v>
       </c>
-      <c r="Q14" s="10"/>
+      <c r="Q14" s="10">
+        <v>2</v>
+      </c>
       <c r="R14" s="10"/>
       <c r="S14" s="10"/>
       <c r="T14" s="10"/>
@@ -1929,7 +1982,7 @@
       <c r="K15" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="L15" s="36">
+      <c r="L15" s="34">
         <v>12</v>
       </c>
       <c r="M15" s="10">
@@ -1944,7 +1997,9 @@
       <c r="P15" s="10">
         <v>8</v>
       </c>
-      <c r="Q15" s="10"/>
+      <c r="Q15" s="10">
+        <v>11</v>
+      </c>
       <c r="R15" s="10"/>
       <c r="S15" s="10"/>
       <c r="T15" s="10"/>
@@ -1980,7 +2035,7 @@
       <c r="K16" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="L16" s="36"/>
+      <c r="L16" s="34"/>
       <c r="M16" s="10">
         <v>7</v>
       </c>
@@ -1991,7 +2046,9 @@
         <v>5</v>
       </c>
       <c r="P16" s="10"/>
-      <c r="Q16" s="10"/>
+      <c r="Q16" s="10">
+        <v>14</v>
+      </c>
       <c r="R16" s="10"/>
       <c r="S16" s="10"/>
       <c r="T16" s="10"/>
@@ -2027,7 +2084,7 @@
       <c r="K17" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="L17" s="36">
+      <c r="L17" s="34">
         <v>12</v>
       </c>
       <c r="M17" s="10">
@@ -2042,7 +2099,9 @@
       <c r="P17" s="10">
         <v>10</v>
       </c>
-      <c r="Q17" s="10"/>
+      <c r="Q17" s="10">
+        <v>9</v>
+      </c>
       <c r="R17" s="10"/>
       <c r="S17" s="10"/>
       <c r="T17" s="10"/>
@@ -2078,7 +2137,7 @@
       <c r="K18" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="L18" s="36"/>
+      <c r="L18" s="34"/>
       <c r="M18" s="10">
         <v>5</v>
       </c>
@@ -2089,7 +2148,9 @@
       <c r="P18" s="10">
         <v>9</v>
       </c>
-      <c r="Q18" s="10"/>
+      <c r="Q18" s="10">
+        <v>2</v>
+      </c>
       <c r="R18" s="10"/>
       <c r="S18" s="10"/>
       <c r="T18" s="10"/>
@@ -2125,12 +2186,14 @@
       <c r="K19" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="L19" s="36"/>
+      <c r="L19" s="34"/>
       <c r="M19" s="10"/>
       <c r="N19" s="11"/>
       <c r="O19" s="10"/>
       <c r="P19" s="10"/>
-      <c r="Q19" s="10"/>
+      <c r="Q19" s="10">
+        <v>0</v>
+      </c>
       <c r="R19" s="10"/>
       <c r="S19" s="10"/>
       <c r="T19" s="10"/>
@@ -2166,7 +2229,7 @@
       <c r="K20" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="L20" s="36">
+      <c r="L20" s="34">
         <v>12</v>
       </c>
       <c r="M20" s="10">
@@ -2181,7 +2244,9 @@
       <c r="P20" s="10">
         <v>10</v>
       </c>
-      <c r="Q20" s="10"/>
+      <c r="Q20" s="10">
+        <v>5</v>
+      </c>
       <c r="R20" s="10"/>
       <c r="S20" s="10"/>
       <c r="T20" s="10"/>
@@ -2217,7 +2282,7 @@
       <c r="K21" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="L21" s="36">
+      <c r="L21" s="34">
         <v>12</v>
       </c>
       <c r="M21" s="10">
@@ -2228,7 +2293,9 @@
         <v>5</v>
       </c>
       <c r="P21" s="10"/>
-      <c r="Q21" s="10"/>
+      <c r="Q21" s="10">
+        <v>6</v>
+      </c>
       <c r="R21" s="10"/>
       <c r="S21" s="10"/>
       <c r="T21" s="10"/>
@@ -2264,7 +2331,7 @@
       <c r="K22" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="L22" s="36">
+      <c r="L22" s="34">
         <v>10</v>
       </c>
       <c r="M22" s="10">
@@ -2279,7 +2346,9 @@
       <c r="P22" s="10">
         <v>10</v>
       </c>
-      <c r="Q22" s="10"/>
+      <c r="Q22" s="10">
+        <v>2</v>
+      </c>
       <c r="R22" s="10"/>
       <c r="S22" s="10"/>
       <c r="T22" s="10"/>
@@ -2315,7 +2384,7 @@
       <c r="K23" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="L23" s="36">
+      <c r="L23" s="34">
         <v>8</v>
       </c>
       <c r="M23" s="10">
@@ -2330,7 +2399,9 @@
       <c r="P23" s="10">
         <v>10</v>
       </c>
-      <c r="Q23" s="10"/>
+      <c r="Q23" s="10">
+        <v>16</v>
+      </c>
       <c r="R23" s="10"/>
       <c r="S23" s="10"/>
       <c r="T23" s="10"/>
@@ -2366,7 +2437,7 @@
       <c r="K24" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="L24" s="36">
+      <c r="L24" s="34">
         <v>11</v>
       </c>
       <c r="M24" s="10">
@@ -2381,7 +2452,9 @@
       <c r="P24" s="10">
         <v>10</v>
       </c>
-      <c r="Q24" s="10"/>
+      <c r="Q24" s="10">
+        <v>12</v>
+      </c>
       <c r="R24" s="10"/>
       <c r="S24" s="10"/>
       <c r="T24" s="10"/>
@@ -2417,7 +2490,7 @@
       <c r="K25" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="L25" s="36">
+      <c r="L25" s="34">
         <v>6</v>
       </c>
       <c r="M25" s="10">
@@ -2432,7 +2505,9 @@
       <c r="P25" s="10">
         <v>10</v>
       </c>
-      <c r="Q25" s="10"/>
+      <c r="Q25" s="10">
+        <v>9</v>
+      </c>
       <c r="R25" s="10"/>
       <c r="S25" s="10"/>
       <c r="T25" s="10"/>
@@ -2468,7 +2543,7 @@
       <c r="K26" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="L26" s="36">
+      <c r="L26" s="34">
         <v>12</v>
       </c>
       <c r="M26" s="10">
@@ -2483,7 +2558,9 @@
       <c r="P26" s="10">
         <v>10</v>
       </c>
-      <c r="Q26" s="10"/>
+      <c r="Q26" s="10">
+        <v>1</v>
+      </c>
       <c r="R26" s="10"/>
       <c r="S26" s="10"/>
       <c r="T26" s="10"/>
@@ -2519,7 +2596,7 @@
       <c r="K27" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="L27" s="36">
+      <c r="L27" s="34">
         <v>7</v>
       </c>
       <c r="M27" s="10">
@@ -2532,7 +2609,9 @@
       <c r="P27" s="10">
         <v>10</v>
       </c>
-      <c r="Q27" s="10"/>
+      <c r="Q27" s="10">
+        <v>1</v>
+      </c>
       <c r="R27" s="10"/>
       <c r="S27" s="10"/>
       <c r="T27" s="10"/>
@@ -2568,7 +2647,7 @@
       <c r="K28" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="L28" s="36">
+      <c r="L28" s="34">
         <v>7</v>
       </c>
       <c r="M28" s="10"/>
@@ -2579,7 +2658,9 @@
         <v>4</v>
       </c>
       <c r="P28" s="10"/>
-      <c r="Q28" s="10"/>
+      <c r="Q28" s="10">
+        <v>8</v>
+      </c>
       <c r="R28" s="10"/>
       <c r="S28" s="10"/>
       <c r="T28" s="10"/>
@@ -2615,7 +2696,7 @@
       <c r="K29" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="L29" s="36">
+      <c r="L29" s="34">
         <v>6</v>
       </c>
       <c r="M29" s="10">
@@ -2630,7 +2711,9 @@
       <c r="P29" s="10">
         <v>10</v>
       </c>
-      <c r="Q29" s="10"/>
+      <c r="Q29" s="10">
+        <v>9</v>
+      </c>
       <c r="R29" s="10"/>
       <c r="S29" s="10"/>
       <c r="T29" s="10"/>
@@ -2666,7 +2749,7 @@
       <c r="K30" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="L30" s="36">
+      <c r="L30" s="34">
         <v>12</v>
       </c>
       <c r="M30" s="10">
@@ -2681,7 +2764,9 @@
       <c r="P30" s="10">
         <v>10</v>
       </c>
-      <c r="Q30" s="10"/>
+      <c r="Q30" s="10">
+        <v>11</v>
+      </c>
       <c r="R30" s="10"/>
       <c r="S30" s="10"/>
       <c r="T30" s="10"/>
@@ -2717,7 +2802,7 @@
       <c r="K31" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="L31" s="36"/>
+      <c r="L31" s="34"/>
       <c r="M31" s="10"/>
       <c r="N31" s="11"/>
       <c r="O31" s="10"/>
@@ -2758,7 +2843,7 @@
       <c r="K32" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="L32" s="36">
+      <c r="L32" s="34">
         <v>12</v>
       </c>
       <c r="M32" s="10">
@@ -2773,7 +2858,9 @@
       <c r="P32" s="10">
         <v>10</v>
       </c>
-      <c r="Q32" s="10"/>
+      <c r="Q32" s="10">
+        <v>14</v>
+      </c>
       <c r="R32" s="10"/>
       <c r="S32" s="10"/>
       <c r="T32" s="10"/>
@@ -2809,7 +2896,7 @@
       <c r="K33" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="L33" s="36">
+      <c r="L33" s="34">
         <v>5</v>
       </c>
       <c r="M33" s="10">
@@ -2822,7 +2909,9 @@
       <c r="P33" s="10">
         <v>10</v>
       </c>
-      <c r="Q33" s="10"/>
+      <c r="Q33" s="10">
+        <v>3</v>
+      </c>
       <c r="R33" s="10"/>
       <c r="S33" s="10"/>
       <c r="T33" s="10"/>
@@ -2871,7 +2960,9 @@
       <c r="P34" s="31">
         <v>10</v>
       </c>
-      <c r="Q34" s="31"/>
+      <c r="Q34" s="31">
+        <v>25</v>
+      </c>
       <c r="R34" s="31"/>
       <c r="S34" s="31"/>
       <c r="T34" s="31"/>
@@ -2907,7 +2998,7 @@
       <c r="K35" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="L35" s="36">
+      <c r="L35" s="34">
         <v>8</v>
       </c>
       <c r="M35" s="10">
@@ -2922,7 +3013,9 @@
       <c r="P35" s="10">
         <v>10</v>
       </c>
-      <c r="Q35" s="10"/>
+      <c r="Q35" s="10">
+        <v>17</v>
+      </c>
       <c r="R35" s="10"/>
       <c r="S35" s="10"/>
       <c r="T35" s="10"/>
@@ -2958,7 +3051,7 @@
       <c r="K36" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="L36" s="36">
+      <c r="L36" s="34">
         <v>12</v>
       </c>
       <c r="M36" s="10">
@@ -2973,7 +3066,9 @@
       <c r="P36" s="10">
         <v>10</v>
       </c>
-      <c r="Q36" s="10"/>
+      <c r="Q36" s="10">
+        <v>7</v>
+      </c>
       <c r="R36" s="10"/>
       <c r="S36" s="10"/>
       <c r="T36" s="10"/>
@@ -3009,7 +3104,7 @@
       <c r="K37" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="L37" s="36">
+      <c r="L37" s="34">
         <v>11</v>
       </c>
       <c r="M37" s="10">
@@ -3024,7 +3119,9 @@
       <c r="P37" s="10">
         <v>9</v>
       </c>
-      <c r="Q37" s="10"/>
+      <c r="Q37" s="10">
+        <v>17</v>
+      </c>
       <c r="R37" s="10"/>
       <c r="S37" s="10"/>
       <c r="T37" s="10"/>
@@ -3060,7 +3157,7 @@
       <c r="K38" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="L38" s="36"/>
+      <c r="L38" s="34"/>
       <c r="M38" s="10">
         <v>5</v>
       </c>
@@ -3073,7 +3170,9 @@
       <c r="P38" s="10">
         <v>10</v>
       </c>
-      <c r="Q38" s="10"/>
+      <c r="Q38" s="10">
+        <v>16</v>
+      </c>
       <c r="R38" s="10"/>
       <c r="S38" s="10"/>
       <c r="T38" s="10"/>
@@ -3109,7 +3208,7 @@
       <c r="K39" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="L39" s="36">
+      <c r="L39" s="34">
         <v>12</v>
       </c>
       <c r="M39" s="10">
@@ -3124,7 +3223,9 @@
       <c r="P39" s="10">
         <v>10</v>
       </c>
-      <c r="Q39" s="10"/>
+      <c r="Q39" s="10">
+        <v>22</v>
+      </c>
       <c r="R39" s="10"/>
       <c r="S39" s="10"/>
       <c r="T39" s="10"/>
@@ -3160,7 +3261,7 @@
       <c r="K40" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="L40" s="36">
+      <c r="L40" s="34">
         <v>11</v>
       </c>
       <c r="M40" s="10">
@@ -3175,7 +3276,9 @@
       <c r="P40" s="10">
         <v>10</v>
       </c>
-      <c r="Q40" s="10"/>
+      <c r="Q40" s="10">
+        <v>15</v>
+      </c>
       <c r="R40" s="10"/>
       <c r="S40" s="10"/>
       <c r="T40" s="10"/>
@@ -3211,7 +3314,7 @@
       <c r="K41" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="L41" s="36">
+      <c r="L41" s="34">
         <v>10</v>
       </c>
       <c r="M41" s="10">
@@ -3226,7 +3329,9 @@
       <c r="P41" s="10">
         <v>10</v>
       </c>
-      <c r="Q41" s="10"/>
+      <c r="Q41" s="10">
+        <v>6</v>
+      </c>
       <c r="R41" s="10"/>
       <c r="S41" s="10"/>
       <c r="T41" s="10"/>
@@ -3262,7 +3367,7 @@
       <c r="K42" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="L42" s="36">
+      <c r="L42" s="34">
         <v>10</v>
       </c>
       <c r="M42" s="10">
@@ -3275,7 +3380,9 @@
         <v>10</v>
       </c>
       <c r="P42" s="10"/>
-      <c r="Q42" s="10"/>
+      <c r="Q42" s="10">
+        <v>4</v>
+      </c>
       <c r="R42" s="10"/>
       <c r="S42" s="10"/>
       <c r="T42" s="10"/>
@@ -3311,7 +3418,7 @@
       <c r="K43" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="L43" s="36">
+      <c r="L43" s="34">
         <v>8</v>
       </c>
       <c r="M43" s="10">
@@ -3326,7 +3433,9 @@
       <c r="P43" s="10">
         <v>9</v>
       </c>
-      <c r="Q43" s="10"/>
+      <c r="Q43" s="10">
+        <v>4</v>
+      </c>
       <c r="R43" s="10"/>
       <c r="S43" s="10"/>
       <c r="T43" s="10"/>
@@ -3362,7 +3471,7 @@
       <c r="K44" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="L44" s="36">
+      <c r="L44" s="34">
         <v>5</v>
       </c>
       <c r="M44" s="10">
@@ -3377,7 +3486,9 @@
       <c r="P44" s="10">
         <v>5</v>
       </c>
-      <c r="Q44" s="10"/>
+      <c r="Q44" s="10">
+        <v>4</v>
+      </c>
       <c r="R44" s="10"/>
       <c r="S44" s="10"/>
       <c r="T44" s="10"/>
@@ -3413,7 +3524,7 @@
       <c r="K45" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="L45" s="36">
+      <c r="L45" s="34">
         <v>8</v>
       </c>
       <c r="M45" s="10">
@@ -3428,7 +3539,9 @@
       <c r="P45" s="10">
         <v>9</v>
       </c>
-      <c r="Q45" s="10"/>
+      <c r="Q45" s="10">
+        <v>18</v>
+      </c>
       <c r="R45" s="10"/>
       <c r="S45" s="10"/>
       <c r="T45" s="10"/>
@@ -3464,7 +3577,7 @@
       <c r="K46" s="7" t="s">
         <v>258</v>
       </c>
-      <c r="L46" s="36">
+      <c r="L46" s="34">
         <v>8</v>
       </c>
       <c r="M46" s="10">
@@ -3479,7 +3592,9 @@
       <c r="P46" s="10">
         <v>10</v>
       </c>
-      <c r="Q46" s="10"/>
+      <c r="Q46" s="10">
+        <v>3</v>
+      </c>
       <c r="R46" s="10"/>
       <c r="S46" s="10"/>
       <c r="T46" s="10"/>
@@ -3515,7 +3630,7 @@
       <c r="K47" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="L47" s="36">
+      <c r="L47" s="34">
         <v>10</v>
       </c>
       <c r="M47" s="10">
@@ -3530,7 +3645,9 @@
       <c r="P47" s="10">
         <v>10</v>
       </c>
-      <c r="Q47" s="10"/>
+      <c r="Q47" s="10">
+        <v>13</v>
+      </c>
       <c r="R47" s="10"/>
       <c r="S47" s="10"/>
       <c r="T47" s="10"/>
@@ -3566,7 +3683,7 @@
       <c r="K48" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="L48" s="36">
+      <c r="L48" s="34">
         <v>10</v>
       </c>
       <c r="M48" s="10">
@@ -3581,7 +3698,9 @@
       <c r="P48" s="10">
         <v>10</v>
       </c>
-      <c r="Q48" s="10"/>
+      <c r="Q48" s="10">
+        <v>6</v>
+      </c>
       <c r="R48" s="10"/>
       <c r="S48" s="10"/>
       <c r="T48" s="10"/>
@@ -3617,7 +3736,7 @@
       <c r="K49" s="7" t="s">
         <v>276</v>
       </c>
-      <c r="L49" s="36">
+      <c r="L49" s="34">
         <v>11</v>
       </c>
       <c r="M49" s="10">
@@ -3632,7 +3751,9 @@
       <c r="P49" s="10">
         <v>10</v>
       </c>
-      <c r="Q49" s="10"/>
+      <c r="Q49" s="10">
+        <v>21</v>
+      </c>
       <c r="R49" s="10"/>
       <c r="S49" s="10"/>
       <c r="T49" s="10"/>
@@ -3668,7 +3789,7 @@
       <c r="K50" s="7" t="s">
         <v>282</v>
       </c>
-      <c r="L50" s="36">
+      <c r="L50" s="34">
         <v>11</v>
       </c>
       <c r="M50" s="10">
@@ -3683,7 +3804,9 @@
       <c r="P50" s="10">
         <v>10</v>
       </c>
-      <c r="Q50" s="10"/>
+      <c r="Q50" s="10">
+        <v>20</v>
+      </c>
       <c r="R50" s="10"/>
       <c r="S50" s="10"/>
       <c r="T50" s="10"/>
@@ -3719,7 +3842,7 @@
       <c r="K51" s="7" t="s">
         <v>288</v>
       </c>
-      <c r="L51" s="36">
+      <c r="L51" s="34">
         <v>7</v>
       </c>
       <c r="M51" s="10">
@@ -3732,7 +3855,9 @@
         <v>10</v>
       </c>
       <c r="P51" s="10"/>
-      <c r="Q51" s="10"/>
+      <c r="Q51" s="10">
+        <v>4</v>
+      </c>
       <c r="R51" s="10"/>
       <c r="S51" s="10"/>
       <c r="T51" s="10"/>
@@ -3768,7 +3893,7 @@
       <c r="K52" s="7" t="s">
         <v>294</v>
       </c>
-      <c r="L52" s="36">
+      <c r="L52" s="34">
         <v>12</v>
       </c>
       <c r="M52" s="10">
@@ -3783,7 +3908,9 @@
       <c r="P52" s="10">
         <v>8</v>
       </c>
-      <c r="Q52" s="10"/>
+      <c r="Q52" s="10">
+        <v>22</v>
+      </c>
       <c r="R52" s="10"/>
       <c r="S52" s="10"/>
       <c r="T52" s="10"/>
@@ -3819,7 +3946,7 @@
       <c r="K53" s="7" t="s">
         <v>300</v>
       </c>
-      <c r="L53" s="36">
+      <c r="L53" s="34">
         <v>8</v>
       </c>
       <c r="M53" s="10">
@@ -3834,10 +3961,17 @@
       <c r="P53" s="10">
         <v>10</v>
       </c>
-      <c r="Q53" s="10"/>
+      <c r="Q53" s="10">
+        <v>19</v>
+      </c>
       <c r="R53" s="10"/>
       <c r="S53" s="10"/>
       <c r="T53" s="10"/>
+    </row>
+    <row r="54" spans="2:20">
+      <c r="Q54" s="38" t="s">
+        <v>310</v>
+      </c>
     </row>
     <row r="56" spans="2:20" ht="18">
       <c r="B56" s="1"/>
@@ -3852,7 +3986,8 @@
     <mergeCell ref="M4:T4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/Score_Class_2026.xlsx
+++ b/Score_Class_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Phisan\Consultancy\2569-KU_MapProjection\Admin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6169C6B2-BA00-440E-BAC7-C62A4FDDBD8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{472144FF-D389-466B-B6B3-C152740D2249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39620" yWindow="-5780" windowWidth="25130" windowHeight="19430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43480" yWindow="-5060" windowWidth="25130" windowHeight="19430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Exercise" sheetId="1" r:id="rId1"/>
@@ -960,13 +960,13 @@
     <t>06-10/8/1969</t>
   </si>
   <si>
-    <t>24-Aug-2026\</t>
-  </si>
-  <si>
     <t>MidTerm</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Ex.7 Lambert Conformal Conic</t>
   </si>
 </sst>
 </file>
@@ -1038,23 +1038,12 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1070,13 +1059,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.499984740745262"/>
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1121,7 +1116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1149,72 +1144,73 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="187" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="187" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="187" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1222,15 +1218,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1447,7 +1434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:T56"/>
+  <dimension ref="B2:Z56"/>
   <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="1" customWidth="1"/>
@@ -1458,74 +1445,74 @@
     <col min="7" max="8" width="10" hidden="1" customWidth="1"/>
     <col min="9" max="11" width="10.796875" hidden="1" customWidth="1"/>
     <col min="12" max="20" width="4.6484375" style="8" customWidth="1"/>
-    <col min="21" max="21" width="10.796875" customWidth="1"/>
+    <col min="21" max="26" width="4.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:20" ht="16" customHeight="1">
-      <c r="B2" s="35" t="s">
+    <row r="2" spans="2:26" ht="16" customHeight="1">
+      <c r="B2" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="35"/>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
-      <c r="P2" s="35"/>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
-      <c r="T2" s="35"/>
-    </row>
-    <row r="3" spans="2:20" ht="18.3" customHeight="1">
-      <c r="B3" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="35"/>
-      <c r="H3" s="35"/>
-      <c r="I3" s="35"/>
-      <c r="J3" s="35"/>
-      <c r="K3" s="35"/>
-      <c r="L3" s="35"/>
-      <c r="M3" s="35"/>
-      <c r="N3" s="35"/>
-      <c r="O3" s="35"/>
-      <c r="P3" s="35"/>
-      <c r="Q3" s="35"/>
-      <c r="R3" s="35"/>
-      <c r="S3" s="35"/>
-      <c r="T3" s="35"/>
-    </row>
-    <row r="4" spans="2:20" ht="26.1" customHeight="1">
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="36"/>
+      <c r="J2" s="36"/>
+      <c r="K2" s="36"/>
+      <c r="L2" s="36"/>
+      <c r="M2" s="36"/>
+      <c r="N2" s="36"/>
+      <c r="O2" s="36"/>
+      <c r="P2" s="36"/>
+      <c r="Q2" s="36"/>
+      <c r="R2" s="36"/>
+      <c r="S2" s="36"/>
+      <c r="T2" s="36"/>
+    </row>
+    <row r="3" spans="2:26" ht="18.3" customHeight="1">
+      <c r="B3" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="36"/>
+      <c r="I3" s="36"/>
+      <c r="J3" s="36"/>
+      <c r="K3" s="36"/>
+      <c r="L3" s="36"/>
+      <c r="M3" s="36"/>
+      <c r="N3" s="36"/>
+      <c r="O3" s="36"/>
+      <c r="P3" s="36"/>
+      <c r="Q3" s="36"/>
+      <c r="R3" s="36"/>
+      <c r="S3" s="36"/>
+      <c r="T3" s="36"/>
+    </row>
+    <row r="4" spans="2:26" ht="26.1" customHeight="1">
       <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="M4" s="36" t="s">
+      <c r="M4" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="N4" s="36"/>
-      <c r="O4" s="36"/>
-      <c r="P4" s="36"/>
-      <c r="Q4" s="36"/>
-      <c r="R4" s="36"/>
-      <c r="S4" s="36"/>
-      <c r="T4" s="36"/>
-    </row>
-    <row r="5" spans="2:20" ht="18">
+      <c r="N4" s="37"/>
+      <c r="O4" s="37"/>
+      <c r="P4" s="37"/>
+      <c r="Q4" s="37"/>
+      <c r="R4" s="37"/>
+      <c r="S4" s="37"/>
+      <c r="T4" s="37"/>
+    </row>
+    <row r="5" spans="2:26" ht="18">
       <c r="E5" s="1" t="s">
         <v>5</v>
       </c>
@@ -1536,36 +1523,44 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="2:20" ht="156.9" customHeight="1">
+    <row r="6" spans="2:26" ht="156.9" customHeight="1">
       <c r="B6" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L6" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="M6" s="12" t="s">
+      <c r="L6" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="M6" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="N6" s="13" t="s">
+      <c r="N6" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="O6" s="12" t="s">
+      <c r="O6" s="11" t="s">
         <v>305</v>
       </c>
-      <c r="P6" s="12" t="s">
+      <c r="P6" s="11" t="s">
         <v>306</v>
       </c>
-      <c r="Q6" s="39" t="s">
-        <v>309</v>
-      </c>
-      <c r="R6" s="10"/>
+      <c r="Q6" s="33" t="s">
+        <v>308</v>
+      </c>
+      <c r="R6" s="11" t="s">
+        <v>310</v>
+      </c>
       <c r="S6" s="10"/>
       <c r="T6" s="10"/>
-    </row>
-    <row r="7" spans="2:20" ht="20.399999999999999">
+      <c r="U6" s="9"/>
+      <c r="V6" s="9"/>
+      <c r="W6" s="9"/>
+      <c r="X6" s="9"/>
+      <c r="Y6" s="9"/>
+      <c r="Z6" s="9"/>
+    </row>
+    <row r="7" spans="2:26" ht="20.399999999999999">
       <c r="B7" s="3" t="s">
         <v>13</v>
       </c>
@@ -1596,29 +1591,37 @@
       <c r="K7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="L7" s="32">
+      <c r="L7" s="26">
         <v>12</v>
       </c>
-      <c r="M7" s="33">
-        <v>10</v>
-      </c>
-      <c r="N7" s="33">
-        <v>10</v>
-      </c>
-      <c r="O7" s="33">
-        <v>10</v>
-      </c>
-      <c r="P7" s="33">
-        <v>10</v>
-      </c>
-      <c r="Q7" s="37">
+      <c r="M7" s="26">
+        <v>10</v>
+      </c>
+      <c r="N7" s="26">
+        <v>10</v>
+      </c>
+      <c r="O7" s="26">
+        <v>10</v>
+      </c>
+      <c r="P7" s="26">
+        <v>10</v>
+      </c>
+      <c r="Q7" s="34">
         <v>26</v>
       </c>
-      <c r="R7" s="33"/>
-      <c r="S7" s="33"/>
-      <c r="T7" s="33"/>
-    </row>
-    <row r="8" spans="2:20" ht="18">
+      <c r="R7" s="26">
+        <v>10</v>
+      </c>
+      <c r="S7" s="26"/>
+      <c r="T7" s="26"/>
+      <c r="U7" s="9"/>
+      <c r="V7" s="9"/>
+      <c r="W7" s="9"/>
+      <c r="X7" s="9"/>
+      <c r="Y7" s="9"/>
+      <c r="Z7" s="9"/>
+    </row>
+    <row r="8" spans="2:26" ht="18">
       <c r="B8" s="5" t="s">
         <v>22</v>
       </c>
@@ -1649,21 +1652,29 @@
       <c r="K8" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="L8" s="34"/>
+      <c r="L8" s="10"/>
       <c r="M8" s="10"/>
-      <c r="N8" s="11">
+      <c r="N8" s="10">
         <v>8</v>
       </c>
       <c r="O8" s="10"/>
       <c r="P8" s="10"/>
-      <c r="Q8" s="10">
-        <v>10</v>
-      </c>
-      <c r="R8" s="10"/>
+      <c r="Q8" s="35">
+        <v>10</v>
+      </c>
+      <c r="R8" s="10">
+        <v>5</v>
+      </c>
       <c r="S8" s="10"/>
       <c r="T8" s="10"/>
-    </row>
-    <row r="9" spans="2:20" ht="18">
+      <c r="U8" s="9"/>
+      <c r="V8" s="9"/>
+      <c r="W8" s="9"/>
+      <c r="X8" s="9"/>
+      <c r="Y8" s="9"/>
+      <c r="Z8" s="9"/>
+    </row>
+    <row r="9" spans="2:26" ht="18">
       <c r="B9" s="5" t="s">
         <v>32</v>
       </c>
@@ -1694,23 +1705,31 @@
       <c r="K9" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="L9" s="34"/>
+      <c r="L9" s="10"/>
       <c r="M9" s="10">
         <v>3</v>
       </c>
-      <c r="N9" s="11"/>
+      <c r="N9" s="10"/>
       <c r="O9" s="10">
         <v>10</v>
       </c>
       <c r="P9" s="10"/>
-      <c r="Q9" s="10">
+      <c r="Q9" s="35">
         <v>4</v>
       </c>
-      <c r="R9" s="10"/>
+      <c r="R9" s="10">
+        <v>10</v>
+      </c>
       <c r="S9" s="10"/>
       <c r="T9" s="10"/>
-    </row>
-    <row r="10" spans="2:20" ht="18">
+      <c r="U9" s="9"/>
+      <c r="V9" s="9"/>
+      <c r="W9" s="9"/>
+      <c r="X9" s="9"/>
+      <c r="Y9" s="9"/>
+      <c r="Z9" s="9"/>
+    </row>
+    <row r="10" spans="2:26" ht="18">
       <c r="B10" s="5" t="s">
         <v>38</v>
       </c>
@@ -1741,25 +1760,31 @@
       <c r="K10" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L10" s="34"/>
+      <c r="L10" s="10"/>
       <c r="M10" s="10">
         <v>3</v>
       </c>
-      <c r="N10" s="11"/>
+      <c r="N10" s="10"/>
       <c r="O10" s="10">
         <v>5</v>
       </c>
       <c r="P10" s="10">
         <v>8</v>
       </c>
-      <c r="Q10" s="10">
+      <c r="Q10" s="35">
         <v>4</v>
       </c>
       <c r="R10" s="10"/>
       <c r="S10" s="10"/>
       <c r="T10" s="10"/>
-    </row>
-    <row r="11" spans="2:20" ht="18">
+      <c r="U10" s="9"/>
+      <c r="V10" s="9"/>
+      <c r="W10" s="9"/>
+      <c r="X10" s="9"/>
+      <c r="Y10" s="9"/>
+      <c r="Z10" s="9"/>
+    </row>
+    <row r="11" spans="2:26" ht="18">
       <c r="B11" s="5" t="s">
         <v>44</v>
       </c>
@@ -1790,13 +1815,13 @@
       <c r="K11" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="L11" s="34">
+      <c r="L11" s="10">
         <v>11</v>
       </c>
       <c r="M11" s="10">
         <v>3</v>
       </c>
-      <c r="N11" s="11">
+      <c r="N11" s="10">
         <v>7</v>
       </c>
       <c r="O11" s="10">
@@ -1805,14 +1830,22 @@
       <c r="P11" s="10">
         <v>9</v>
       </c>
-      <c r="Q11" s="10">
+      <c r="Q11" s="35">
         <v>9</v>
       </c>
-      <c r="R11" s="10"/>
+      <c r="R11" s="10">
+        <v>10</v>
+      </c>
       <c r="S11" s="10"/>
       <c r="T11" s="10"/>
-    </row>
-    <row r="12" spans="2:20" ht="18">
+      <c r="U11" s="9"/>
+      <c r="V11" s="9"/>
+      <c r="W11" s="9"/>
+      <c r="X11" s="9"/>
+      <c r="Y11" s="9"/>
+      <c r="Z11" s="9"/>
+    </row>
+    <row r="12" spans="2:26" ht="18">
       <c r="B12" s="5" t="s">
         <v>50</v>
       </c>
@@ -1843,23 +1876,31 @@
       <c r="K12" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="L12" s="34"/>
+      <c r="L12" s="10"/>
       <c r="M12" s="10"/>
-      <c r="N12" s="11">
+      <c r="N12" s="10">
         <v>7</v>
       </c>
       <c r="O12" s="10"/>
       <c r="P12" s="10">
         <v>10</v>
       </c>
-      <c r="Q12" s="10">
+      <c r="Q12" s="35">
         <v>9</v>
       </c>
-      <c r="R12" s="10"/>
+      <c r="R12" s="10">
+        <v>10</v>
+      </c>
       <c r="S12" s="10"/>
       <c r="T12" s="10"/>
-    </row>
-    <row r="13" spans="2:20" ht="18">
+      <c r="U12" s="9"/>
+      <c r="V12" s="9"/>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+    </row>
+    <row r="13" spans="2:26" ht="18">
       <c r="B13" s="5" t="s">
         <v>56</v>
       </c>
@@ -1890,19 +1931,27 @@
       <c r="K13" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="L13" s="34"/>
+      <c r="L13" s="10"/>
       <c r="M13" s="10"/>
-      <c r="N13" s="11"/>
+      <c r="N13" s="10"/>
       <c r="O13" s="10"/>
       <c r="P13" s="10"/>
-      <c r="Q13" s="10">
+      <c r="Q13" s="35">
         <v>0</v>
       </c>
-      <c r="R13" s="10"/>
+      <c r="R13" s="10">
+        <v>5</v>
+      </c>
       <c r="S13" s="10"/>
       <c r="T13" s="10"/>
-    </row>
-    <row r="14" spans="2:20" ht="18">
+      <c r="U13" s="9"/>
+      <c r="V13" s="9"/>
+      <c r="W13" s="9"/>
+      <c r="X13" s="9"/>
+      <c r="Y13" s="9"/>
+      <c r="Z13" s="9"/>
+    </row>
+    <row r="14" spans="2:26" ht="18">
       <c r="B14" s="5" t="s">
         <v>62</v>
       </c>
@@ -1933,25 +1982,33 @@
       <c r="K14" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="L14" s="34"/>
+      <c r="L14" s="10"/>
       <c r="M14" s="10">
         <v>4</v>
       </c>
-      <c r="N14" s="11"/>
+      <c r="N14" s="10"/>
       <c r="O14" s="10">
         <v>5</v>
       </c>
       <c r="P14" s="10">
         <v>8</v>
       </c>
-      <c r="Q14" s="10">
+      <c r="Q14" s="35">
         <v>2</v>
       </c>
-      <c r="R14" s="10"/>
+      <c r="R14" s="10">
+        <v>10</v>
+      </c>
       <c r="S14" s="10"/>
       <c r="T14" s="10"/>
-    </row>
-    <row r="15" spans="2:20" ht="18">
+      <c r="U14" s="9"/>
+      <c r="V14" s="9"/>
+      <c r="W14" s="9"/>
+      <c r="X14" s="9"/>
+      <c r="Y14" s="9"/>
+      <c r="Z14" s="9"/>
+    </row>
+    <row r="15" spans="2:26" ht="18">
       <c r="B15" s="5" t="s">
         <v>68</v>
       </c>
@@ -1982,13 +2039,13 @@
       <c r="K15" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="L15" s="34">
+      <c r="L15" s="10">
         <v>12</v>
       </c>
       <c r="M15" s="10">
         <v>2</v>
       </c>
-      <c r="N15" s="11">
+      <c r="N15" s="10">
         <v>8</v>
       </c>
       <c r="O15" s="10">
@@ -1997,14 +2054,22 @@
       <c r="P15" s="10">
         <v>8</v>
       </c>
-      <c r="Q15" s="10">
+      <c r="Q15" s="35">
         <v>11</v>
       </c>
-      <c r="R15" s="10"/>
+      <c r="R15" s="10">
+        <v>8</v>
+      </c>
       <c r="S15" s="10"/>
       <c r="T15" s="10"/>
-    </row>
-    <row r="16" spans="2:20" ht="18">
+      <c r="U15" s="9"/>
+      <c r="V15" s="9"/>
+      <c r="W15" s="9"/>
+      <c r="X15" s="9"/>
+      <c r="Y15" s="9"/>
+      <c r="Z15" s="9"/>
+    </row>
+    <row r="16" spans="2:26" ht="18">
       <c r="B16" s="5" t="s">
         <v>74</v>
       </c>
@@ -2035,25 +2100,33 @@
       <c r="K16" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="L16" s="34"/>
+      <c r="L16" s="10"/>
       <c r="M16" s="10">
         <v>7</v>
       </c>
-      <c r="N16" s="11">
+      <c r="N16" s="10">
         <v>10</v>
       </c>
       <c r="O16" s="10">
         <v>5</v>
       </c>
       <c r="P16" s="10"/>
-      <c r="Q16" s="10">
+      <c r="Q16" s="35">
         <v>14</v>
       </c>
-      <c r="R16" s="10"/>
+      <c r="R16" s="10">
+        <v>3</v>
+      </c>
       <c r="S16" s="10"/>
       <c r="T16" s="10"/>
-    </row>
-    <row r="17" spans="2:20" ht="18">
+      <c r="U16" s="9"/>
+      <c r="V16" s="9"/>
+      <c r="W16" s="9"/>
+      <c r="X16" s="9"/>
+      <c r="Y16" s="9"/>
+      <c r="Z16" s="9"/>
+    </row>
+    <row r="17" spans="2:26" ht="18">
       <c r="B17" s="5" t="s">
         <v>80</v>
       </c>
@@ -2084,13 +2157,13 @@
       <c r="K17" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="L17" s="34">
+      <c r="L17" s="10">
         <v>12</v>
       </c>
       <c r="M17" s="10">
         <v>3</v>
       </c>
-      <c r="N17" s="11">
+      <c r="N17" s="10">
         <v>8</v>
       </c>
       <c r="O17" s="10">
@@ -2099,14 +2172,22 @@
       <c r="P17" s="10">
         <v>10</v>
       </c>
-      <c r="Q17" s="10">
+      <c r="Q17" s="35">
         <v>9</v>
       </c>
-      <c r="R17" s="10"/>
+      <c r="R17" s="10">
+        <v>10</v>
+      </c>
       <c r="S17" s="10"/>
       <c r="T17" s="10"/>
-    </row>
-    <row r="18" spans="2:20" ht="18">
+      <c r="U17" s="9"/>
+      <c r="V17" s="9"/>
+      <c r="W17" s="9"/>
+      <c r="X17" s="9"/>
+      <c r="Y17" s="9"/>
+      <c r="Z17" s="9"/>
+    </row>
+    <row r="18" spans="2:26" ht="18">
       <c r="B18" s="5" t="s">
         <v>86</v>
       </c>
@@ -2137,25 +2218,33 @@
       <c r="K18" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="L18" s="34"/>
+      <c r="L18" s="10"/>
       <c r="M18" s="10">
         <v>5</v>
       </c>
-      <c r="N18" s="11"/>
+      <c r="N18" s="10"/>
       <c r="O18" s="10">
         <v>5</v>
       </c>
       <c r="P18" s="10">
         <v>9</v>
       </c>
-      <c r="Q18" s="10">
+      <c r="Q18" s="35">
         <v>2</v>
       </c>
-      <c r="R18" s="10"/>
+      <c r="R18" s="10">
+        <v>10</v>
+      </c>
       <c r="S18" s="10"/>
       <c r="T18" s="10"/>
-    </row>
-    <row r="19" spans="2:20" ht="18">
+      <c r="U18" s="9"/>
+      <c r="V18" s="9"/>
+      <c r="W18" s="9"/>
+      <c r="X18" s="9"/>
+      <c r="Y18" s="9"/>
+      <c r="Z18" s="9"/>
+    </row>
+    <row r="19" spans="2:26" ht="18">
       <c r="B19" s="5" t="s">
         <v>92</v>
       </c>
@@ -2186,19 +2275,27 @@
       <c r="K19" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="L19" s="34"/>
+      <c r="L19" s="10"/>
       <c r="M19" s="10"/>
-      <c r="N19" s="11"/>
+      <c r="N19" s="10"/>
       <c r="O19" s="10"/>
       <c r="P19" s="10"/>
-      <c r="Q19" s="10">
+      <c r="Q19" s="35">
         <v>0</v>
       </c>
-      <c r="R19" s="10"/>
+      <c r="R19" s="10">
+        <v>10</v>
+      </c>
       <c r="S19" s="10"/>
       <c r="T19" s="10"/>
-    </row>
-    <row r="20" spans="2:20" ht="18">
+      <c r="U19" s="9"/>
+      <c r="V19" s="9"/>
+      <c r="W19" s="9"/>
+      <c r="X19" s="9"/>
+      <c r="Y19" s="9"/>
+      <c r="Z19" s="9"/>
+    </row>
+    <row r="20" spans="2:26" ht="18">
       <c r="B20" s="5" t="s">
         <v>98</v>
       </c>
@@ -2229,13 +2326,13 @@
       <c r="K20" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="L20" s="34">
+      <c r="L20" s="10">
         <v>12</v>
       </c>
       <c r="M20" s="10">
         <v>4</v>
       </c>
-      <c r="N20" s="11">
+      <c r="N20" s="10">
         <v>9</v>
       </c>
       <c r="O20" s="10">
@@ -2244,14 +2341,22 @@
       <c r="P20" s="10">
         <v>10</v>
       </c>
-      <c r="Q20" s="10">
+      <c r="Q20" s="35">
         <v>5</v>
       </c>
-      <c r="R20" s="10"/>
+      <c r="R20" s="10">
+        <v>5</v>
+      </c>
       <c r="S20" s="10"/>
       <c r="T20" s="10"/>
-    </row>
-    <row r="21" spans="2:20" ht="18">
+      <c r="U20" s="9"/>
+      <c r="V20" s="9"/>
+      <c r="W20" s="9"/>
+      <c r="X20" s="9"/>
+      <c r="Y20" s="9"/>
+      <c r="Z20" s="9"/>
+    </row>
+    <row r="21" spans="2:26" ht="18">
       <c r="B21" s="5" t="s">
         <v>104</v>
       </c>
@@ -2282,25 +2387,31 @@
       <c r="K21" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="L21" s="34">
+      <c r="L21" s="10">
         <v>12</v>
       </c>
       <c r="M21" s="10">
         <v>5</v>
       </c>
-      <c r="N21" s="11"/>
+      <c r="N21" s="10"/>
       <c r="O21" s="10">
         <v>5</v>
       </c>
       <c r="P21" s="10"/>
-      <c r="Q21" s="10">
+      <c r="Q21" s="35">
         <v>6</v>
       </c>
       <c r="R21" s="10"/>
       <c r="S21" s="10"/>
       <c r="T21" s="10"/>
-    </row>
-    <row r="22" spans="2:20" ht="18">
+      <c r="U21" s="9"/>
+      <c r="V21" s="9"/>
+      <c r="W21" s="9"/>
+      <c r="X21" s="9"/>
+      <c r="Y21" s="9"/>
+      <c r="Z21" s="9"/>
+    </row>
+    <row r="22" spans="2:26" ht="18">
       <c r="B22" s="5" t="s">
         <v>110</v>
       </c>
@@ -2331,13 +2442,13 @@
       <c r="K22" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="L22" s="34">
+      <c r="L22" s="10">
         <v>10</v>
       </c>
       <c r="M22" s="10">
         <v>7</v>
       </c>
-      <c r="N22" s="11">
+      <c r="N22" s="10">
         <v>7</v>
       </c>
       <c r="O22" s="10">
@@ -2346,14 +2457,22 @@
       <c r="P22" s="10">
         <v>10</v>
       </c>
-      <c r="Q22" s="10">
+      <c r="Q22" s="35">
         <v>2</v>
       </c>
-      <c r="R22" s="10"/>
+      <c r="R22" s="10">
+        <v>10</v>
+      </c>
       <c r="S22" s="10"/>
       <c r="T22" s="10"/>
-    </row>
-    <row r="23" spans="2:20" ht="18">
+      <c r="U22" s="9"/>
+      <c r="V22" s="9"/>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+    </row>
+    <row r="23" spans="2:26" ht="18">
       <c r="B23" s="5" t="s">
         <v>116</v>
       </c>
@@ -2384,13 +2503,13 @@
       <c r="K23" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="L23" s="34">
+      <c r="L23" s="10">
         <v>8</v>
       </c>
       <c r="M23" s="10">
         <v>7</v>
       </c>
-      <c r="N23" s="11">
+      <c r="N23" s="10">
         <v>10</v>
       </c>
       <c r="O23" s="10">
@@ -2399,14 +2518,22 @@
       <c r="P23" s="10">
         <v>10</v>
       </c>
-      <c r="Q23" s="10">
+      <c r="Q23" s="35">
         <v>16</v>
       </c>
-      <c r="R23" s="10"/>
+      <c r="R23" s="10">
+        <v>10</v>
+      </c>
       <c r="S23" s="10"/>
       <c r="T23" s="10"/>
-    </row>
-    <row r="24" spans="2:20" ht="18">
+      <c r="U23" s="9"/>
+      <c r="V23" s="9"/>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+    </row>
+    <row r="24" spans="2:26" ht="18">
       <c r="B24" s="5" t="s">
         <v>122</v>
       </c>
@@ -2437,13 +2564,13 @@
       <c r="K24" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="L24" s="34">
+      <c r="L24" s="10">
         <v>11</v>
       </c>
       <c r="M24" s="10">
         <v>10</v>
       </c>
-      <c r="N24" s="11">
+      <c r="N24" s="10">
         <v>7</v>
       </c>
       <c r="O24" s="10">
@@ -2452,14 +2579,22 @@
       <c r="P24" s="10">
         <v>10</v>
       </c>
-      <c r="Q24" s="10">
+      <c r="Q24" s="35">
         <v>12</v>
       </c>
-      <c r="R24" s="10"/>
+      <c r="R24" s="10">
+        <v>10</v>
+      </c>
       <c r="S24" s="10"/>
       <c r="T24" s="10"/>
-    </row>
-    <row r="25" spans="2:20" ht="18">
+      <c r="U24" s="9"/>
+      <c r="V24" s="9"/>
+      <c r="W24" s="9"/>
+      <c r="X24" s="9"/>
+      <c r="Y24" s="9"/>
+      <c r="Z24" s="9"/>
+    </row>
+    <row r="25" spans="2:26" ht="18">
       <c r="B25" s="5" t="s">
         <v>128</v>
       </c>
@@ -2490,13 +2625,13 @@
       <c r="K25" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="L25" s="34">
+      <c r="L25" s="10">
         <v>6</v>
       </c>
       <c r="M25" s="10">
         <v>7</v>
       </c>
-      <c r="N25" s="11">
+      <c r="N25" s="10">
         <v>7</v>
       </c>
       <c r="O25" s="10">
@@ -2505,14 +2640,22 @@
       <c r="P25" s="10">
         <v>10</v>
       </c>
-      <c r="Q25" s="10">
+      <c r="Q25" s="35">
         <v>9</v>
       </c>
-      <c r="R25" s="10"/>
+      <c r="R25" s="10">
+        <v>10</v>
+      </c>
       <c r="S25" s="10"/>
       <c r="T25" s="10"/>
-    </row>
-    <row r="26" spans="2:20" ht="18">
+      <c r="U25" s="9"/>
+      <c r="V25" s="9"/>
+      <c r="W25" s="9"/>
+      <c r="X25" s="9"/>
+      <c r="Y25" s="9"/>
+      <c r="Z25" s="9"/>
+    </row>
+    <row r="26" spans="2:26" ht="18">
       <c r="B26" s="5" t="s">
         <v>134</v>
       </c>
@@ -2543,13 +2686,13 @@
       <c r="K26" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="L26" s="34">
+      <c r="L26" s="10">
         <v>12</v>
       </c>
       <c r="M26" s="10">
         <v>5</v>
       </c>
-      <c r="N26" s="11">
+      <c r="N26" s="10">
         <v>10</v>
       </c>
       <c r="O26" s="10">
@@ -2558,14 +2701,22 @@
       <c r="P26" s="10">
         <v>10</v>
       </c>
-      <c r="Q26" s="10">
-        <v>1</v>
-      </c>
-      <c r="R26" s="10"/>
+      <c r="Q26" s="35">
+        <v>1</v>
+      </c>
+      <c r="R26" s="10">
+        <v>10</v>
+      </c>
       <c r="S26" s="10"/>
       <c r="T26" s="10"/>
-    </row>
-    <row r="27" spans="2:20" ht="18">
+      <c r="U26" s="9"/>
+      <c r="V26" s="9"/>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+    </row>
+    <row r="27" spans="2:26" ht="18">
       <c r="B27" s="5" t="s">
         <v>140</v>
       </c>
@@ -2596,27 +2747,35 @@
       <c r="K27" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="L27" s="34">
+      <c r="L27" s="10">
         <v>7</v>
       </c>
       <c r="M27" s="10">
         <v>5</v>
       </c>
-      <c r="N27" s="11"/>
+      <c r="N27" s="10"/>
       <c r="O27" s="10">
         <v>10</v>
       </c>
       <c r="P27" s="10">
         <v>10</v>
       </c>
-      <c r="Q27" s="10">
-        <v>1</v>
-      </c>
-      <c r="R27" s="10"/>
+      <c r="Q27" s="35">
+        <v>1</v>
+      </c>
+      <c r="R27" s="10">
+        <v>10</v>
+      </c>
       <c r="S27" s="10"/>
       <c r="T27" s="10"/>
-    </row>
-    <row r="28" spans="2:20" ht="18">
+      <c r="U27" s="9"/>
+      <c r="V27" s="9"/>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
+    </row>
+    <row r="28" spans="2:26" ht="18">
       <c r="B28" s="5" t="s">
         <v>146</v>
       </c>
@@ -2647,25 +2806,33 @@
       <c r="K28" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="L28" s="34">
+      <c r="L28" s="10">
         <v>7</v>
       </c>
       <c r="M28" s="10"/>
-      <c r="N28" s="11">
+      <c r="N28" s="10">
         <v>7</v>
       </c>
       <c r="O28" s="10">
         <v>4</v>
       </c>
       <c r="P28" s="10"/>
-      <c r="Q28" s="10">
+      <c r="Q28" s="35">
         <v>8</v>
       </c>
-      <c r="R28" s="10"/>
+      <c r="R28" s="10">
+        <v>10</v>
+      </c>
       <c r="S28" s="10"/>
       <c r="T28" s="10"/>
-    </row>
-    <row r="29" spans="2:20" ht="18">
+      <c r="U28" s="9"/>
+      <c r="V28" s="9"/>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+    </row>
+    <row r="29" spans="2:26" ht="18">
       <c r="B29" s="5" t="s">
         <v>152</v>
       </c>
@@ -2696,13 +2863,13 @@
       <c r="K29" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="L29" s="34">
+      <c r="L29" s="10">
         <v>6</v>
       </c>
       <c r="M29" s="10">
         <v>8</v>
       </c>
-      <c r="N29" s="11">
+      <c r="N29" s="10">
         <v>10</v>
       </c>
       <c r="O29" s="10">
@@ -2711,14 +2878,22 @@
       <c r="P29" s="10">
         <v>10</v>
       </c>
-      <c r="Q29" s="10">
+      <c r="Q29" s="35">
         <v>9</v>
       </c>
-      <c r="R29" s="10"/>
+      <c r="R29" s="10">
+        <v>10</v>
+      </c>
       <c r="S29" s="10"/>
       <c r="T29" s="10"/>
-    </row>
-    <row r="30" spans="2:20" ht="18">
+      <c r="U29" s="9"/>
+      <c r="V29" s="9"/>
+      <c r="W29" s="9"/>
+      <c r="X29" s="9"/>
+      <c r="Y29" s="9"/>
+      <c r="Z29" s="9"/>
+    </row>
+    <row r="30" spans="2:26" ht="18">
       <c r="B30" s="5" t="s">
         <v>158</v>
       </c>
@@ -2749,13 +2924,13 @@
       <c r="K30" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="L30" s="34">
+      <c r="L30" s="10">
         <v>12</v>
       </c>
       <c r="M30" s="10">
         <v>10</v>
       </c>
-      <c r="N30" s="11">
+      <c r="N30" s="10">
         <v>10</v>
       </c>
       <c r="O30" s="10">
@@ -2764,14 +2939,22 @@
       <c r="P30" s="10">
         <v>10</v>
       </c>
-      <c r="Q30" s="10">
+      <c r="Q30" s="35">
         <v>11</v>
       </c>
-      <c r="R30" s="10"/>
+      <c r="R30" s="10">
+        <v>10</v>
+      </c>
       <c r="S30" s="10"/>
       <c r="T30" s="10"/>
-    </row>
-    <row r="31" spans="2:20" ht="18">
+      <c r="U30" s="9"/>
+      <c r="V30" s="9"/>
+      <c r="W30" s="9"/>
+      <c r="X30" s="9"/>
+      <c r="Y30" s="9"/>
+      <c r="Z30" s="9"/>
+    </row>
+    <row r="31" spans="2:26" ht="18">
       <c r="B31" s="5" t="s">
         <v>164</v>
       </c>
@@ -2802,17 +2985,23 @@
       <c r="K31" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="L31" s="34"/>
+      <c r="L31" s="10"/>
       <c r="M31" s="10"/>
-      <c r="N31" s="11"/>
+      <c r="N31" s="10"/>
       <c r="O31" s="10"/>
       <c r="P31" s="10"/>
-      <c r="Q31" s="10"/>
+      <c r="Q31" s="35"/>
       <c r="R31" s="10"/>
       <c r="S31" s="10"/>
       <c r="T31" s="10"/>
-    </row>
-    <row r="32" spans="2:20" ht="18">
+      <c r="U31" s="9"/>
+      <c r="V31" s="9"/>
+      <c r="W31" s="9"/>
+      <c r="X31" s="9"/>
+      <c r="Y31" s="9"/>
+      <c r="Z31" s="9"/>
+    </row>
+    <row r="32" spans="2:26" ht="18">
       <c r="B32" s="5" t="s">
         <v>29</v>
       </c>
@@ -2843,13 +3032,13 @@
       <c r="K32" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="L32" s="34">
+      <c r="L32" s="10">
         <v>12</v>
       </c>
       <c r="M32" s="10">
         <v>9</v>
       </c>
-      <c r="N32" s="11">
+      <c r="N32" s="10">
         <v>10</v>
       </c>
       <c r="O32" s="10">
@@ -2858,14 +3047,22 @@
       <c r="P32" s="10">
         <v>10</v>
       </c>
-      <c r="Q32" s="10">
+      <c r="Q32" s="35">
         <v>14</v>
       </c>
-      <c r="R32" s="10"/>
+      <c r="R32" s="10">
+        <v>5</v>
+      </c>
       <c r="S32" s="10"/>
       <c r="T32" s="10"/>
-    </row>
-    <row r="33" spans="2:20" ht="18">
+      <c r="U32" s="9"/>
+      <c r="V32" s="9"/>
+      <c r="W32" s="9"/>
+      <c r="X32" s="9"/>
+      <c r="Y32" s="9"/>
+      <c r="Z32" s="9"/>
+    </row>
+    <row r="33" spans="2:26" ht="18">
       <c r="B33" s="5" t="s">
         <v>175</v>
       </c>
@@ -2896,78 +3093,94 @@
       <c r="K33" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="L33" s="34">
+      <c r="L33" s="10">
         <v>5</v>
       </c>
       <c r="M33" s="10">
         <v>10</v>
       </c>
-      <c r="N33" s="11"/>
+      <c r="N33" s="10"/>
       <c r="O33" s="10">
         <v>10</v>
       </c>
       <c r="P33" s="10">
         <v>10</v>
       </c>
-      <c r="Q33" s="10">
+      <c r="Q33" s="35">
         <v>3</v>
       </c>
-      <c r="R33" s="10"/>
+      <c r="R33" s="10">
+        <v>10</v>
+      </c>
       <c r="S33" s="10"/>
       <c r="T33" s="10"/>
-    </row>
-    <row r="34" spans="2:20" ht="18">
-      <c r="B34" s="28" t="s">
+      <c r="U33" s="9"/>
+      <c r="V33" s="9"/>
+      <c r="W33" s="9"/>
+      <c r="X33" s="9"/>
+      <c r="Y33" s="9"/>
+      <c r="Z33" s="9"/>
+    </row>
+    <row r="34" spans="2:26" ht="18">
+      <c r="B34" s="22" t="s">
         <v>181</v>
       </c>
-      <c r="C34" s="29" t="s">
+      <c r="C34" s="23" t="s">
         <v>182</v>
       </c>
-      <c r="D34" s="29" t="s">
+      <c r="D34" s="23" t="s">
         <v>183</v>
       </c>
-      <c r="E34" s="29" t="s">
+      <c r="E34" s="23" t="s">
         <v>184</v>
       </c>
-      <c r="F34" s="29" t="s">
+      <c r="F34" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="G34" s="29" t="s">
+      <c r="G34" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="H34" s="29" t="s">
+      <c r="H34" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="I34" s="29" t="s">
+      <c r="I34" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="J34" s="29" t="s">
+      <c r="J34" s="23" t="s">
         <v>185</v>
       </c>
-      <c r="K34" s="30" t="s">
+      <c r="K34" s="24" t="s">
         <v>186</v>
       </c>
-      <c r="L34" s="31">
+      <c r="L34" s="10">
         <v>12</v>
       </c>
-      <c r="M34" s="31">
+      <c r="M34" s="25">
         <v>4</v>
       </c>
-      <c r="N34" s="31"/>
-      <c r="O34" s="31">
-        <v>10</v>
-      </c>
-      <c r="P34" s="31">
-        <v>10</v>
-      </c>
-      <c r="Q34" s="31">
+      <c r="N34" s="10"/>
+      <c r="O34" s="25">
+        <v>10</v>
+      </c>
+      <c r="P34" s="25">
+        <v>10</v>
+      </c>
+      <c r="Q34" s="35">
         <v>25</v>
       </c>
-      <c r="R34" s="31"/>
-      <c r="S34" s="31"/>
-      <c r="T34" s="31"/>
-    </row>
-    <row r="35" spans="2:20" ht="18">
+      <c r="R34" s="25">
+        <v>10</v>
+      </c>
+      <c r="S34" s="25"/>
+      <c r="T34" s="25"/>
+      <c r="U34" s="9"/>
+      <c r="V34" s="9"/>
+      <c r="W34" s="9"/>
+      <c r="X34" s="9"/>
+      <c r="Y34" s="9"/>
+      <c r="Z34" s="9"/>
+    </row>
+    <row r="35" spans="2:26" ht="18">
       <c r="B35" s="5" t="s">
         <v>187</v>
       </c>
@@ -2998,13 +3211,13 @@
       <c r="K35" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="L35" s="34">
+      <c r="L35" s="10">
         <v>8</v>
       </c>
       <c r="M35" s="10">
         <v>10</v>
       </c>
-      <c r="N35" s="11">
+      <c r="N35" s="10">
         <v>10</v>
       </c>
       <c r="O35" s="10">
@@ -3013,14 +3226,22 @@
       <c r="P35" s="10">
         <v>10</v>
       </c>
-      <c r="Q35" s="10">
+      <c r="Q35" s="35">
         <v>17</v>
       </c>
-      <c r="R35" s="10"/>
+      <c r="R35" s="10">
+        <v>7</v>
+      </c>
       <c r="S35" s="10"/>
       <c r="T35" s="10"/>
-    </row>
-    <row r="36" spans="2:20" ht="18">
+      <c r="U35" s="9"/>
+      <c r="V35" s="9"/>
+      <c r="W35" s="9"/>
+      <c r="X35" s="9"/>
+      <c r="Y35" s="9"/>
+      <c r="Z35" s="9"/>
+    </row>
+    <row r="36" spans="2:26" ht="18">
       <c r="B36" s="5" t="s">
         <v>193</v>
       </c>
@@ -3051,13 +3272,13 @@
       <c r="K36" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="L36" s="34">
+      <c r="L36" s="10">
         <v>12</v>
       </c>
       <c r="M36" s="10">
         <v>8</v>
       </c>
-      <c r="N36" s="11">
+      <c r="N36" s="10">
         <v>7</v>
       </c>
       <c r="O36" s="10">
@@ -3066,14 +3287,22 @@
       <c r="P36" s="10">
         <v>10</v>
       </c>
-      <c r="Q36" s="10">
+      <c r="Q36" s="35">
         <v>7</v>
       </c>
-      <c r="R36" s="10"/>
+      <c r="R36" s="10">
+        <v>10</v>
+      </c>
       <c r="S36" s="10"/>
       <c r="T36" s="10"/>
-    </row>
-    <row r="37" spans="2:20" ht="18">
+      <c r="U36" s="9"/>
+      <c r="V36" s="9"/>
+      <c r="W36" s="9"/>
+      <c r="X36" s="9"/>
+      <c r="Y36" s="9"/>
+      <c r="Z36" s="9"/>
+    </row>
+    <row r="37" spans="2:26" ht="18">
       <c r="B37" s="5" t="s">
         <v>199</v>
       </c>
@@ -3104,13 +3333,13 @@
       <c r="K37" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="L37" s="34">
+      <c r="L37" s="10">
         <v>11</v>
       </c>
       <c r="M37" s="10">
         <v>8</v>
       </c>
-      <c r="N37" s="11">
+      <c r="N37" s="10">
         <v>10</v>
       </c>
       <c r="O37" s="10">
@@ -3119,14 +3348,22 @@
       <c r="P37" s="10">
         <v>9</v>
       </c>
-      <c r="Q37" s="10">
+      <c r="Q37" s="35">
         <v>17</v>
       </c>
-      <c r="R37" s="10"/>
+      <c r="R37" s="10">
+        <v>10</v>
+      </c>
       <c r="S37" s="10"/>
       <c r="T37" s="10"/>
-    </row>
-    <row r="38" spans="2:20" ht="18">
+      <c r="U37" s="9"/>
+      <c r="V37" s="9"/>
+      <c r="W37" s="9"/>
+      <c r="X37" s="9"/>
+      <c r="Y37" s="9"/>
+      <c r="Z37" s="9"/>
+    </row>
+    <row r="38" spans="2:26" ht="18">
       <c r="B38" s="5" t="s">
         <v>205</v>
       </c>
@@ -3157,11 +3394,11 @@
       <c r="K38" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="L38" s="34"/>
+      <c r="L38" s="10"/>
       <c r="M38" s="10">
         <v>5</v>
       </c>
-      <c r="N38" s="11">
+      <c r="N38" s="10">
         <v>10</v>
       </c>
       <c r="O38" s="10">
@@ -3170,14 +3407,22 @@
       <c r="P38" s="10">
         <v>10</v>
       </c>
-      <c r="Q38" s="10">
+      <c r="Q38" s="35">
         <v>16</v>
       </c>
-      <c r="R38" s="10"/>
+      <c r="R38" s="10">
+        <v>5</v>
+      </c>
       <c r="S38" s="10"/>
       <c r="T38" s="10"/>
-    </row>
-    <row r="39" spans="2:20" ht="18">
+      <c r="U38" s="9"/>
+      <c r="V38" s="9"/>
+      <c r="W38" s="9"/>
+      <c r="X38" s="9"/>
+      <c r="Y38" s="9"/>
+      <c r="Z38" s="9"/>
+    </row>
+    <row r="39" spans="2:26" ht="18">
       <c r="B39" s="5" t="s">
         <v>211</v>
       </c>
@@ -3208,13 +3453,13 @@
       <c r="K39" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="L39" s="34">
+      <c r="L39" s="10">
         <v>12</v>
       </c>
       <c r="M39" s="10">
         <v>10</v>
       </c>
-      <c r="N39" s="11">
+      <c r="N39" s="10">
         <v>10</v>
       </c>
       <c r="O39" s="10">
@@ -3223,14 +3468,22 @@
       <c r="P39" s="10">
         <v>10</v>
       </c>
-      <c r="Q39" s="10">
+      <c r="Q39" s="35">
         <v>22</v>
       </c>
-      <c r="R39" s="10"/>
+      <c r="R39" s="10">
+        <v>10</v>
+      </c>
       <c r="S39" s="10"/>
       <c r="T39" s="10"/>
-    </row>
-    <row r="40" spans="2:20" ht="18">
+      <c r="U39" s="9"/>
+      <c r="V39" s="9"/>
+      <c r="W39" s="9"/>
+      <c r="X39" s="9"/>
+      <c r="Y39" s="9"/>
+      <c r="Z39" s="9"/>
+    </row>
+    <row r="40" spans="2:26" ht="18">
       <c r="B40" s="5" t="s">
         <v>217</v>
       </c>
@@ -3261,13 +3514,13 @@
       <c r="K40" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="L40" s="34">
+      <c r="L40" s="10">
         <v>11</v>
       </c>
       <c r="M40" s="10">
         <v>9</v>
       </c>
-      <c r="N40" s="11">
+      <c r="N40" s="10">
         <v>9</v>
       </c>
       <c r="O40" s="10">
@@ -3276,14 +3529,22 @@
       <c r="P40" s="10">
         <v>10</v>
       </c>
-      <c r="Q40" s="10">
+      <c r="Q40" s="35">
         <v>15</v>
       </c>
-      <c r="R40" s="10"/>
+      <c r="R40" s="10">
+        <v>5</v>
+      </c>
       <c r="S40" s="10"/>
       <c r="T40" s="10"/>
-    </row>
-    <row r="41" spans="2:20" ht="18">
+      <c r="U40" s="9"/>
+      <c r="V40" s="9"/>
+      <c r="W40" s="9"/>
+      <c r="X40" s="9"/>
+      <c r="Y40" s="9"/>
+      <c r="Z40" s="9"/>
+    </row>
+    <row r="41" spans="2:26" ht="18">
       <c r="B41" s="5" t="s">
         <v>223</v>
       </c>
@@ -3314,13 +3575,13 @@
       <c r="K41" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="L41" s="34">
+      <c r="L41" s="10">
         <v>10</v>
       </c>
       <c r="M41" s="10">
         <v>9</v>
       </c>
-      <c r="N41" s="11">
+      <c r="N41" s="10">
         <v>10</v>
       </c>
       <c r="O41" s="10">
@@ -3329,14 +3590,22 @@
       <c r="P41" s="10">
         <v>10</v>
       </c>
-      <c r="Q41" s="10">
+      <c r="Q41" s="35">
         <v>6</v>
       </c>
-      <c r="R41" s="10"/>
+      <c r="R41" s="10">
+        <v>5</v>
+      </c>
       <c r="S41" s="10"/>
       <c r="T41" s="10"/>
-    </row>
-    <row r="42" spans="2:20" ht="18">
+      <c r="U41" s="9"/>
+      <c r="V41" s="9"/>
+      <c r="W41" s="9"/>
+      <c r="X41" s="9"/>
+      <c r="Y41" s="9"/>
+      <c r="Z41" s="9"/>
+    </row>
+    <row r="42" spans="2:26" ht="18">
       <c r="B42" s="5" t="s">
         <v>229</v>
       </c>
@@ -3367,27 +3636,35 @@
       <c r="K42" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="L42" s="34">
+      <c r="L42" s="10">
         <v>10</v>
       </c>
       <c r="M42" s="10">
         <v>7</v>
       </c>
-      <c r="N42" s="11">
+      <c r="N42" s="10">
         <v>7</v>
       </c>
       <c r="O42" s="10">
         <v>10</v>
       </c>
       <c r="P42" s="10"/>
-      <c r="Q42" s="10">
+      <c r="Q42" s="35">
         <v>4</v>
       </c>
-      <c r="R42" s="10"/>
+      <c r="R42" s="10">
+        <v>10</v>
+      </c>
       <c r="S42" s="10"/>
       <c r="T42" s="10"/>
-    </row>
-    <row r="43" spans="2:20" ht="18">
+      <c r="U42" s="9"/>
+      <c r="V42" s="9"/>
+      <c r="W42" s="9"/>
+      <c r="X42" s="9"/>
+      <c r="Y42" s="9"/>
+      <c r="Z42" s="9"/>
+    </row>
+    <row r="43" spans="2:26" ht="18">
       <c r="B43" s="5" t="s">
         <v>235</v>
       </c>
@@ -3418,13 +3695,13 @@
       <c r="K43" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="L43" s="34">
+      <c r="L43" s="10">
         <v>8</v>
       </c>
       <c r="M43" s="10">
         <v>6</v>
       </c>
-      <c r="N43" s="11">
+      <c r="N43" s="10">
         <v>10</v>
       </c>
       <c r="O43" s="10">
@@ -3433,14 +3710,22 @@
       <c r="P43" s="10">
         <v>9</v>
       </c>
-      <c r="Q43" s="10">
+      <c r="Q43" s="35">
         <v>4</v>
       </c>
-      <c r="R43" s="10"/>
+      <c r="R43" s="10">
+        <v>7</v>
+      </c>
       <c r="S43" s="10"/>
       <c r="T43" s="10"/>
-    </row>
-    <row r="44" spans="2:20" ht="18">
+      <c r="U43" s="9"/>
+      <c r="V43" s="9"/>
+      <c r="W43" s="9"/>
+      <c r="X43" s="9"/>
+      <c r="Y43" s="9"/>
+      <c r="Z43" s="9"/>
+    </row>
+    <row r="44" spans="2:26" ht="18">
       <c r="B44" s="5" t="s">
         <v>241</v>
       </c>
@@ -3471,13 +3756,13 @@
       <c r="K44" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="L44" s="34">
+      <c r="L44" s="10">
         <v>5</v>
       </c>
       <c r="M44" s="10">
         <v>10</v>
       </c>
-      <c r="N44" s="11">
+      <c r="N44" s="10">
         <v>7</v>
       </c>
       <c r="O44" s="10">
@@ -3486,14 +3771,22 @@
       <c r="P44" s="10">
         <v>5</v>
       </c>
-      <c r="Q44" s="10">
+      <c r="Q44" s="35">
         <v>4</v>
       </c>
-      <c r="R44" s="10"/>
+      <c r="R44" s="10">
+        <v>7</v>
+      </c>
       <c r="S44" s="10"/>
       <c r="T44" s="10"/>
-    </row>
-    <row r="45" spans="2:20" ht="18">
+      <c r="U44" s="9"/>
+      <c r="V44" s="9"/>
+      <c r="W44" s="9"/>
+      <c r="X44" s="9"/>
+      <c r="Y44" s="9"/>
+      <c r="Z44" s="9"/>
+    </row>
+    <row r="45" spans="2:26" ht="18">
       <c r="B45" s="5" t="s">
         <v>247</v>
       </c>
@@ -3524,13 +3817,13 @@
       <c r="K45" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="L45" s="34">
+      <c r="L45" s="10">
         <v>8</v>
       </c>
       <c r="M45" s="10">
         <v>10</v>
       </c>
-      <c r="N45" s="11">
+      <c r="N45" s="10">
         <v>10</v>
       </c>
       <c r="O45" s="10">
@@ -3539,14 +3832,22 @@
       <c r="P45" s="10">
         <v>9</v>
       </c>
-      <c r="Q45" s="10">
+      <c r="Q45" s="35">
         <v>18</v>
       </c>
-      <c r="R45" s="10"/>
+      <c r="R45" s="10">
+        <v>10</v>
+      </c>
       <c r="S45" s="10"/>
       <c r="T45" s="10"/>
-    </row>
-    <row r="46" spans="2:20" ht="18">
+      <c r="U45" s="9"/>
+      <c r="V45" s="9"/>
+      <c r="W45" s="9"/>
+      <c r="X45" s="9"/>
+      <c r="Y45" s="9"/>
+      <c r="Z45" s="9"/>
+    </row>
+    <row r="46" spans="2:26" ht="18">
       <c r="B46" s="5" t="s">
         <v>253</v>
       </c>
@@ -3577,13 +3878,13 @@
       <c r="K46" s="7" t="s">
         <v>258</v>
       </c>
-      <c r="L46" s="34">
+      <c r="L46" s="10">
         <v>8</v>
       </c>
       <c r="M46" s="10">
         <v>10</v>
       </c>
-      <c r="N46" s="11">
+      <c r="N46" s="10">
         <v>7</v>
       </c>
       <c r="O46" s="10">
@@ -3592,14 +3893,22 @@
       <c r="P46" s="10">
         <v>10</v>
       </c>
-      <c r="Q46" s="10">
+      <c r="Q46" s="35">
         <v>3</v>
       </c>
-      <c r="R46" s="10"/>
+      <c r="R46" s="10">
+        <v>10</v>
+      </c>
       <c r="S46" s="10"/>
       <c r="T46" s="10"/>
-    </row>
-    <row r="47" spans="2:20" ht="18">
+      <c r="U46" s="9"/>
+      <c r="V46" s="9"/>
+      <c r="W46" s="9"/>
+      <c r="X46" s="9"/>
+      <c r="Y46" s="9"/>
+      <c r="Z46" s="9"/>
+    </row>
+    <row r="47" spans="2:26" ht="18">
       <c r="B47" s="5" t="s">
         <v>259</v>
       </c>
@@ -3630,13 +3939,13 @@
       <c r="K47" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="L47" s="34">
+      <c r="L47" s="10">
         <v>10</v>
       </c>
       <c r="M47" s="10">
         <v>10</v>
       </c>
-      <c r="N47" s="11">
+      <c r="N47" s="10">
         <v>7</v>
       </c>
       <c r="O47" s="10">
@@ -3645,14 +3954,22 @@
       <c r="P47" s="10">
         <v>10</v>
       </c>
-      <c r="Q47" s="10">
+      <c r="Q47" s="35">
         <v>13</v>
       </c>
-      <c r="R47" s="10"/>
+      <c r="R47" s="10">
+        <v>7</v>
+      </c>
       <c r="S47" s="10"/>
       <c r="T47" s="10"/>
-    </row>
-    <row r="48" spans="2:20" ht="18">
+      <c r="U47" s="9"/>
+      <c r="V47" s="9"/>
+      <c r="W47" s="9"/>
+      <c r="X47" s="9"/>
+      <c r="Y47" s="9"/>
+      <c r="Z47" s="9"/>
+    </row>
+    <row r="48" spans="2:26" ht="18">
       <c r="B48" s="5" t="s">
         <v>265</v>
       </c>
@@ -3683,13 +4000,13 @@
       <c r="K48" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="L48" s="34">
+      <c r="L48" s="10">
         <v>10</v>
       </c>
       <c r="M48" s="10">
         <v>8</v>
       </c>
-      <c r="N48" s="11">
+      <c r="N48" s="10">
         <v>7</v>
       </c>
       <c r="O48" s="10">
@@ -3698,14 +4015,22 @@
       <c r="P48" s="10">
         <v>10</v>
       </c>
-      <c r="Q48" s="10">
+      <c r="Q48" s="35">
         <v>6</v>
       </c>
-      <c r="R48" s="10"/>
+      <c r="R48" s="10">
+        <v>10</v>
+      </c>
       <c r="S48" s="10"/>
       <c r="T48" s="10"/>
-    </row>
-    <row r="49" spans="2:20" ht="18">
+      <c r="U48" s="9"/>
+      <c r="V48" s="9"/>
+      <c r="W48" s="9"/>
+      <c r="X48" s="9"/>
+      <c r="Y48" s="9"/>
+      <c r="Z48" s="9"/>
+    </row>
+    <row r="49" spans="2:26" ht="18">
       <c r="B49" s="5" t="s">
         <v>271</v>
       </c>
@@ -3736,13 +4061,13 @@
       <c r="K49" s="7" t="s">
         <v>276</v>
       </c>
-      <c r="L49" s="34">
+      <c r="L49" s="10">
         <v>11</v>
       </c>
       <c r="M49" s="10">
         <v>9</v>
       </c>
-      <c r="N49" s="11">
+      <c r="N49" s="10">
         <v>10</v>
       </c>
       <c r="O49" s="10">
@@ -3751,14 +4076,22 @@
       <c r="P49" s="10">
         <v>10</v>
       </c>
-      <c r="Q49" s="10">
+      <c r="Q49" s="35">
         <v>21</v>
       </c>
-      <c r="R49" s="10"/>
+      <c r="R49" s="10">
+        <v>6</v>
+      </c>
       <c r="S49" s="10"/>
       <c r="T49" s="10"/>
-    </row>
-    <row r="50" spans="2:20" ht="18">
+      <c r="U49" s="9"/>
+      <c r="V49" s="9"/>
+      <c r="W49" s="9"/>
+      <c r="X49" s="9"/>
+      <c r="Y49" s="9"/>
+      <c r="Z49" s="9"/>
+    </row>
+    <row r="50" spans="2:26" ht="18">
       <c r="B50" s="5" t="s">
         <v>277</v>
       </c>
@@ -3789,13 +4122,13 @@
       <c r="K50" s="7" t="s">
         <v>282</v>
       </c>
-      <c r="L50" s="34">
+      <c r="L50" s="10">
         <v>11</v>
       </c>
       <c r="M50" s="10">
         <v>10</v>
       </c>
-      <c r="N50" s="11">
+      <c r="N50" s="10">
         <v>10</v>
       </c>
       <c r="O50" s="10">
@@ -3804,14 +4137,22 @@
       <c r="P50" s="10">
         <v>10</v>
       </c>
-      <c r="Q50" s="10">
+      <c r="Q50" s="35">
         <v>20</v>
       </c>
-      <c r="R50" s="10"/>
+      <c r="R50" s="10">
+        <v>10</v>
+      </c>
       <c r="S50" s="10"/>
       <c r="T50" s="10"/>
-    </row>
-    <row r="51" spans="2:20" ht="18">
+      <c r="U50" s="9"/>
+      <c r="V50" s="9"/>
+      <c r="W50" s="9"/>
+      <c r="X50" s="9"/>
+      <c r="Y50" s="9"/>
+      <c r="Z50" s="9"/>
+    </row>
+    <row r="51" spans="2:26" ht="18">
       <c r="B51" s="5" t="s">
         <v>283</v>
       </c>
@@ -3842,27 +4183,35 @@
       <c r="K51" s="7" t="s">
         <v>288</v>
       </c>
-      <c r="L51" s="34">
+      <c r="L51" s="10">
         <v>7</v>
       </c>
       <c r="M51" s="10">
         <v>10</v>
       </c>
-      <c r="N51" s="11">
+      <c r="N51" s="10">
         <v>7</v>
       </c>
       <c r="O51" s="10">
         <v>10</v>
       </c>
       <c r="P51" s="10"/>
-      <c r="Q51" s="10">
+      <c r="Q51" s="35">
         <v>4</v>
       </c>
-      <c r="R51" s="10"/>
+      <c r="R51" s="10">
+        <v>4</v>
+      </c>
       <c r="S51" s="10"/>
       <c r="T51" s="10"/>
-    </row>
-    <row r="52" spans="2:20" ht="18">
+      <c r="U51" s="9"/>
+      <c r="V51" s="9"/>
+      <c r="W51" s="9"/>
+      <c r="X51" s="9"/>
+      <c r="Y51" s="9"/>
+      <c r="Z51" s="9"/>
+    </row>
+    <row r="52" spans="2:26" ht="18">
       <c r="B52" s="5" t="s">
         <v>289</v>
       </c>
@@ -3893,13 +4242,13 @@
       <c r="K52" s="7" t="s">
         <v>294</v>
       </c>
-      <c r="L52" s="34">
+      <c r="L52" s="10">
         <v>12</v>
       </c>
       <c r="M52" s="10">
         <v>10</v>
       </c>
-      <c r="N52" s="11">
+      <c r="N52" s="10">
         <v>10</v>
       </c>
       <c r="O52" s="10">
@@ -3908,14 +4257,22 @@
       <c r="P52" s="10">
         <v>8</v>
       </c>
-      <c r="Q52" s="10">
+      <c r="Q52" s="35">
         <v>22</v>
       </c>
-      <c r="R52" s="10"/>
+      <c r="R52" s="10">
+        <v>10</v>
+      </c>
       <c r="S52" s="10"/>
       <c r="T52" s="10"/>
-    </row>
-    <row r="53" spans="2:20" ht="18">
+      <c r="U52" s="9"/>
+      <c r="V52" s="9"/>
+      <c r="W52" s="9"/>
+      <c r="X52" s="9"/>
+      <c r="Y52" s="9"/>
+      <c r="Z52" s="9"/>
+    </row>
+    <row r="53" spans="2:26" ht="18">
       <c r="B53" s="5" t="s">
         <v>295</v>
       </c>
@@ -3946,13 +4303,13 @@
       <c r="K53" s="7" t="s">
         <v>300</v>
       </c>
-      <c r="L53" s="34">
+      <c r="L53" s="10">
         <v>8</v>
       </c>
       <c r="M53" s="10">
         <v>9</v>
       </c>
-      <c r="N53" s="11">
+      <c r="N53" s="10">
         <v>10</v>
       </c>
       <c r="O53" s="10">
@@ -3961,19 +4318,27 @@
       <c r="P53" s="10">
         <v>10</v>
       </c>
-      <c r="Q53" s="10">
+      <c r="Q53" s="35">
         <v>19</v>
       </c>
-      <c r="R53" s="10"/>
+      <c r="R53" s="10">
+        <v>10</v>
+      </c>
       <c r="S53" s="10"/>
       <c r="T53" s="10"/>
-    </row>
-    <row r="54" spans="2:20">
-      <c r="Q54" s="38" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="56" spans="2:20" ht="18">
+      <c r="U53" s="9"/>
+      <c r="V53" s="9"/>
+      <c r="W53" s="9"/>
+      <c r="X53" s="9"/>
+      <c r="Y53" s="9"/>
+      <c r="Z53" s="9"/>
+    </row>
+    <row r="54" spans="2:26">
+      <c r="Q54" s="27" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="56" spans="2:26" ht="18">
       <c r="B56" s="1"/>
       <c r="G56" s="2" t="s">
         <v>301</v>
@@ -3999,10 +4364,10 @@
     <col min="1" max="1" width="6.94921875" customWidth="1"/>
     <col min="2" max="2" width="16.19921875" customWidth="1"/>
     <col min="3" max="3" width="31.046875" customWidth="1"/>
-    <col min="4" max="4" width="3.796875" style="15" customWidth="1"/>
+    <col min="4" max="4" width="3.796875" style="12" customWidth="1"/>
     <col min="5" max="5" width="3.796875" customWidth="1"/>
-    <col min="6" max="6" width="3.796875" style="21" customWidth="1"/>
-    <col min="7" max="7" width="3.796875" style="24" customWidth="1"/>
+    <col min="6" max="6" width="3.796875" style="18" customWidth="1"/>
+    <col min="7" max="7" width="3.796875" style="20" customWidth="1"/>
     <col min="8" max="14" width="3.796875" customWidth="1"/>
     <col min="15" max="15" width="8.796875" customWidth="1"/>
     <col min="16" max="26" width="4.6484375" customWidth="1"/>
@@ -4015,50 +4380,50 @@
       <c r="C6" s="10" t="s">
         <v>302</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="16" t="s">
         <v>303</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="17" t="s">
         <v>304</v>
       </c>
-      <c r="F6" s="22" t="s">
+      <c r="F6" s="19" t="s">
         <v>307</v>
       </c>
-      <c r="G6" s="23" t="s">
-        <v>308</v>
-      </c>
-      <c r="H6" s="20"/>
-      <c r="I6" s="20"/>
-      <c r="J6" s="20"/>
-      <c r="K6" s="20"/>
-      <c r="L6" s="20"/>
-      <c r="M6" s="20"/>
-      <c r="N6" s="20"/>
+      <c r="G6" s="28">
+        <v>46258</v>
+      </c>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="17"/>
+      <c r="N6" s="17"/>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" s="9" t="str">
+      <c r="A7" s="29" t="str">
         <f>Exercise!B7</f>
         <v>ลำดับที่</v>
       </c>
-      <c r="B7" s="9" t="str">
+      <c r="B7" s="29" t="str">
         <f>Exercise!C7</f>
         <v>รหัสนิสิต</v>
       </c>
-      <c r="C7" s="9" t="str">
+      <c r="C7" s="29" t="str">
         <f>Exercise!D7</f>
         <v>ชื่อ-นามสกุล</v>
       </c>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="27"/>
-      <c r="H7" s="26"/>
-      <c r="I7" s="26"/>
-      <c r="J7" s="26"/>
-      <c r="K7" s="26"/>
-      <c r="L7" s="26"/>
-      <c r="M7" s="26"/>
-      <c r="N7" s="26"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="30"/>
+      <c r="K7" s="30"/>
+      <c r="L7" s="30"/>
+      <c r="M7" s="30"/>
+      <c r="N7" s="30"/>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="9" t="str">
@@ -4073,14 +4438,14 @@
         <f>Exercise!D8</f>
         <v>นายธีรพัส แก้วงาม</v>
       </c>
-      <c r="D8" s="16">
-        <v>1</v>
-      </c>
-      <c r="E8" s="18"/>
-      <c r="F8" s="17">
-        <v>1</v>
-      </c>
-      <c r="G8" s="25"/>
+      <c r="D8" s="13">
+        <v>1</v>
+      </c>
+      <c r="E8" s="15"/>
+      <c r="F8" s="14">
+        <v>1</v>
+      </c>
+      <c r="G8" s="21"/>
       <c r="H8" s="9"/>
       <c r="I8" s="9"/>
       <c r="J8" s="9"/>
@@ -4102,12 +4467,12 @@
         <f>Exercise!D9</f>
         <v>นางสาวนภัสสร นูมหันต์</v>
       </c>
-      <c r="D9" s="16"/>
-      <c r="E9" s="18">
-        <v>1</v>
-      </c>
-      <c r="F9" s="17"/>
-      <c r="G9" s="25">
+      <c r="D9" s="13"/>
+      <c r="E9" s="15">
+        <v>1</v>
+      </c>
+      <c r="F9" s="14"/>
+      <c r="G9" s="21">
         <v>1</v>
       </c>
       <c r="H9" s="9"/>
@@ -4131,12 +4496,12 @@
         <f>Exercise!D10</f>
         <v>นางสาวนรภร เจริญสลุง</v>
       </c>
-      <c r="D10" s="16"/>
-      <c r="E10" s="18">
-        <v>1</v>
-      </c>
-      <c r="F10" s="17"/>
-      <c r="G10" s="25"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="15">
+        <v>1</v>
+      </c>
+      <c r="F10" s="14"/>
+      <c r="G10" s="21"/>
       <c r="H10" s="9"/>
       <c r="I10" s="9"/>
       <c r="J10" s="9"/>
@@ -4158,16 +4523,16 @@
         <f>Exercise!D11</f>
         <v>นายบุนยามีน มะสง</v>
       </c>
-      <c r="D11" s="16">
-        <v>1</v>
-      </c>
-      <c r="E11" s="18">
-        <v>1</v>
-      </c>
-      <c r="F11" s="17">
-        <v>1</v>
-      </c>
-      <c r="G11" s="25">
+      <c r="D11" s="13">
+        <v>1</v>
+      </c>
+      <c r="E11" s="15">
+        <v>1</v>
+      </c>
+      <c r="F11" s="14">
+        <v>1</v>
+      </c>
+      <c r="G11" s="21">
         <v>1</v>
       </c>
       <c r="H11" s="9"/>
@@ -4191,16 +4556,16 @@
         <f>Exercise!D12</f>
         <v>นายปัญญานันท์ ทองแก้วเกิด</v>
       </c>
-      <c r="D12" s="16">
-        <v>1</v>
-      </c>
-      <c r="E12" s="18">
-        <v>1</v>
-      </c>
-      <c r="F12" s="17">
-        <v>1</v>
-      </c>
-      <c r="G12" s="25">
+      <c r="D12" s="13">
+        <v>1</v>
+      </c>
+      <c r="E12" s="15">
+        <v>1</v>
+      </c>
+      <c r="F12" s="14">
+        <v>1</v>
+      </c>
+      <c r="G12" s="21">
         <v>1</v>
       </c>
       <c r="H12" s="9"/>
@@ -4224,12 +4589,12 @@
         <f>Exercise!D13</f>
         <v>นางสาวภิญยดา ศรีแนน</v>
       </c>
-      <c r="D13" s="16"/>
-      <c r="E13" s="18">
-        <v>1</v>
-      </c>
-      <c r="F13" s="17"/>
-      <c r="G13" s="25">
+      <c r="D13" s="13"/>
+      <c r="E13" s="15">
+        <v>1</v>
+      </c>
+      <c r="F13" s="14"/>
+      <c r="G13" s="21">
         <v>1</v>
       </c>
       <c r="H13" s="9"/>
@@ -4253,14 +4618,14 @@
         <f>Exercise!D14</f>
         <v>นายภูริณ มานหมัด</v>
       </c>
-      <c r="D14" s="16">
-        <v>1</v>
-      </c>
-      <c r="E14" s="18"/>
-      <c r="F14" s="17">
-        <v>1</v>
-      </c>
-      <c r="G14" s="25">
+      <c r="D14" s="13">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15"/>
+      <c r="F14" s="14">
+        <v>1</v>
+      </c>
+      <c r="G14" s="21">
         <v>1</v>
       </c>
       <c r="H14" s="9"/>
@@ -4284,16 +4649,16 @@
         <f>Exercise!D15</f>
         <v>นายรัชชานนท์ สาคะเรศ</v>
       </c>
-      <c r="D15" s="16">
-        <v>1</v>
-      </c>
-      <c r="E15" s="18">
-        <v>1</v>
-      </c>
-      <c r="F15" s="17">
-        <v>1</v>
-      </c>
-      <c r="G15" s="25">
+      <c r="D15" s="13">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>1</v>
+      </c>
+      <c r="F15" s="14">
+        <v>1</v>
+      </c>
+      <c r="G15" s="21">
         <v>1</v>
       </c>
       <c r="H15" s="9"/>
@@ -4317,16 +4682,16 @@
         <f>Exercise!D16</f>
         <v>นายวรพล พลอยชัด</v>
       </c>
-      <c r="D16" s="16">
-        <v>1</v>
-      </c>
-      <c r="E16" s="18">
-        <v>1</v>
-      </c>
-      <c r="F16" s="17">
-        <v>1</v>
-      </c>
-      <c r="G16" s="25">
+      <c r="D16" s="13">
+        <v>1</v>
+      </c>
+      <c r="E16" s="15">
+        <v>1</v>
+      </c>
+      <c r="F16" s="14">
+        <v>1</v>
+      </c>
+      <c r="G16" s="21">
         <v>1</v>
       </c>
       <c r="H16" s="9"/>
@@ -4350,16 +4715,16 @@
         <f>Exercise!D17</f>
         <v>นายศุภณัฐ จันทรังษี</v>
       </c>
-      <c r="D17" s="16">
-        <v>1</v>
-      </c>
-      <c r="E17" s="18">
-        <v>1</v>
-      </c>
-      <c r="F17" s="17">
-        <v>1</v>
-      </c>
-      <c r="G17" s="25">
+      <c r="D17" s="13">
+        <v>1</v>
+      </c>
+      <c r="E17" s="15">
+        <v>1</v>
+      </c>
+      <c r="F17" s="14">
+        <v>1</v>
+      </c>
+      <c r="G17" s="21">
         <v>1</v>
       </c>
       <c r="H17" s="9"/>
@@ -4383,14 +4748,14 @@
         <f>Exercise!D18</f>
         <v>นางสาวเศรษฐกมล วังออมทรัพย์</v>
       </c>
-      <c r="D18" s="16"/>
-      <c r="E18" s="18">
-        <v>1</v>
-      </c>
-      <c r="F18" s="17">
-        <v>1</v>
-      </c>
-      <c r="G18" s="25">
+      <c r="D18" s="13"/>
+      <c r="E18" s="15">
+        <v>1</v>
+      </c>
+      <c r="F18" s="14">
+        <v>1</v>
+      </c>
+      <c r="G18" s="21">
         <v>1</v>
       </c>
       <c r="H18" s="9"/>
@@ -4414,10 +4779,10 @@
         <f>Exercise!D19</f>
         <v>นางสาวอริศรา เล่งกูล</v>
       </c>
-      <c r="D19" s="16"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="25">
+      <c r="D19" s="13"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="21">
         <v>1</v>
       </c>
       <c r="H19" s="9"/>
@@ -4441,12 +4806,12 @@
         <f>Exercise!D20</f>
         <v>นายภัทรพล ดิษฐาพร</v>
       </c>
-      <c r="D20" s="16"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="17">
-        <v>1</v>
-      </c>
-      <c r="G20" s="25">
+      <c r="D20" s="13"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="14">
+        <v>1</v>
+      </c>
+      <c r="G20" s="21">
         <v>1</v>
       </c>
       <c r="H20" s="9"/>
@@ -4470,14 +4835,14 @@
         <f>Exercise!D21</f>
         <v>นายภาคิน แซ่โง้ว</v>
       </c>
-      <c r="D21" s="16">
-        <v>1</v>
-      </c>
-      <c r="E21" s="18">
-        <v>1</v>
-      </c>
-      <c r="F21" s="17"/>
-      <c r="G21" s="25"/>
+      <c r="D21" s="13">
+        <v>1</v>
+      </c>
+      <c r="E21" s="15">
+        <v>1</v>
+      </c>
+      <c r="F21" s="14"/>
+      <c r="G21" s="21"/>
       <c r="H21" s="9"/>
       <c r="I21" s="9"/>
       <c r="J21" s="9"/>
@@ -4499,16 +4864,16 @@
         <f>Exercise!D22</f>
         <v>นายกนล แสงเดช</v>
       </c>
-      <c r="D22" s="16">
-        <v>1</v>
-      </c>
-      <c r="E22" s="18">
-        <v>1</v>
-      </c>
-      <c r="F22" s="17">
-        <v>1</v>
-      </c>
-      <c r="G22" s="25">
+      <c r="D22" s="13">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>1</v>
+      </c>
+      <c r="F22" s="14">
+        <v>1</v>
+      </c>
+      <c r="G22" s="21">
         <v>1</v>
       </c>
       <c r="H22" s="9"/>
@@ -4532,16 +4897,16 @@
         <f>Exercise!D23</f>
         <v>นางสาวกมลนิตย์ โตอยู่</v>
       </c>
-      <c r="D23" s="16">
-        <v>1</v>
-      </c>
-      <c r="E23" s="18">
-        <v>1</v>
-      </c>
-      <c r="F23" s="17">
-        <v>1</v>
-      </c>
-      <c r="G23" s="25">
+      <c r="D23" s="13">
+        <v>1</v>
+      </c>
+      <c r="E23" s="15">
+        <v>1</v>
+      </c>
+      <c r="F23" s="14">
+        <v>1</v>
+      </c>
+      <c r="G23" s="21">
         <v>1</v>
       </c>
       <c r="H23" s="9"/>
@@ -4565,16 +4930,16 @@
         <f>Exercise!D24</f>
         <v>นายกฤษกร ศรีสัจจัง</v>
       </c>
-      <c r="D24" s="16">
-        <v>1</v>
-      </c>
-      <c r="E24" s="18">
-        <v>1</v>
-      </c>
-      <c r="F24" s="17">
-        <v>1</v>
-      </c>
-      <c r="G24" s="25">
+      <c r="D24" s="13">
+        <v>1</v>
+      </c>
+      <c r="E24" s="15">
+        <v>1</v>
+      </c>
+      <c r="F24" s="14">
+        <v>1</v>
+      </c>
+      <c r="G24" s="21">
         <v>1</v>
       </c>
       <c r="H24" s="9"/>
@@ -4598,16 +4963,16 @@
         <f>Exercise!D25</f>
         <v>นายกันติวัสส์ ตันตระการย์</v>
       </c>
-      <c r="D25" s="16">
-        <v>1</v>
-      </c>
-      <c r="E25" s="18">
-        <v>1</v>
-      </c>
-      <c r="F25" s="17">
-        <v>1</v>
-      </c>
-      <c r="G25" s="25">
+      <c r="D25" s="13">
+        <v>1</v>
+      </c>
+      <c r="E25" s="15">
+        <v>1</v>
+      </c>
+      <c r="F25" s="14">
+        <v>1</v>
+      </c>
+      <c r="G25" s="21">
         <v>1</v>
       </c>
       <c r="H25" s="9"/>
@@ -4631,16 +4996,16 @@
         <f>Exercise!D26</f>
         <v>นายเกษมโชค นชะพงษ์</v>
       </c>
-      <c r="D26" s="16">
-        <v>1</v>
-      </c>
-      <c r="E26" s="18">
-        <v>1</v>
-      </c>
-      <c r="F26" s="17">
-        <v>1</v>
-      </c>
-      <c r="G26" s="25">
+      <c r="D26" s="13">
+        <v>1</v>
+      </c>
+      <c r="E26" s="15">
+        <v>1</v>
+      </c>
+      <c r="F26" s="14">
+        <v>1</v>
+      </c>
+      <c r="G26" s="21">
         <v>1</v>
       </c>
       <c r="H26" s="9"/>
@@ -4664,14 +5029,14 @@
         <f>Exercise!D27</f>
         <v>นายจักรินทร์ อินทร์น้อย</v>
       </c>
-      <c r="D27" s="16"/>
-      <c r="E27" s="18">
-        <v>1</v>
-      </c>
-      <c r="F27" s="17">
-        <v>1</v>
-      </c>
-      <c r="G27" s="25">
+      <c r="D27" s="13"/>
+      <c r="E27" s="15">
+        <v>1</v>
+      </c>
+      <c r="F27" s="14">
+        <v>1</v>
+      </c>
+      <c r="G27" s="21">
         <v>1</v>
       </c>
       <c r="H27" s="9"/>
@@ -4695,14 +5060,14 @@
         <f>Exercise!D28</f>
         <v>นางสาวจันทร์เจ้า เทพจิตต์</v>
       </c>
-      <c r="D28" s="16"/>
-      <c r="E28" s="18">
-        <v>1</v>
-      </c>
-      <c r="F28" s="17">
-        <v>1</v>
-      </c>
-      <c r="G28" s="25">
+      <c r="D28" s="13"/>
+      <c r="E28" s="15">
+        <v>1</v>
+      </c>
+      <c r="F28" s="14">
+        <v>1</v>
+      </c>
+      <c r="G28" s="21">
         <v>1</v>
       </c>
       <c r="H28" s="9"/>
@@ -4726,16 +5091,16 @@
         <f>Exercise!D29</f>
         <v>นางสาวฑิฆัมพร ตรีบุสยะรัตน์</v>
       </c>
-      <c r="D29" s="16">
-        <v>1</v>
-      </c>
-      <c r="E29" s="18">
-        <v>1</v>
-      </c>
-      <c r="F29" s="17">
-        <v>1</v>
-      </c>
-      <c r="G29" s="25">
+      <c r="D29" s="13">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>1</v>
+      </c>
+      <c r="F29" s="14">
+        <v>1</v>
+      </c>
+      <c r="G29" s="21">
         <v>1</v>
       </c>
       <c r="H29" s="9"/>
@@ -4759,16 +5124,16 @@
         <f>Exercise!D30</f>
         <v>นางสาวณปภัช บุญมายศ</v>
       </c>
-      <c r="D30" s="16">
-        <v>1</v>
-      </c>
-      <c r="E30" s="18">
-        <v>1</v>
-      </c>
-      <c r="F30" s="17">
-        <v>1</v>
-      </c>
-      <c r="G30" s="25">
+      <c r="D30" s="13">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>1</v>
+      </c>
+      <c r="F30" s="14">
+        <v>1</v>
+      </c>
+      <c r="G30" s="21">
         <v>1</v>
       </c>
       <c r="H30" s="9"/>
@@ -4792,10 +5157,10 @@
         <f>Exercise!D31</f>
         <v>นายธนทัต มุทธากาญจน์</v>
       </c>
-      <c r="D31" s="16"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="25"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="21"/>
       <c r="H31" s="9"/>
       <c r="I31" s="9"/>
       <c r="J31" s="9"/>
@@ -4817,16 +5182,16 @@
         <f>Exercise!D32</f>
         <v>นายธนภูมิ เหลืองชัยพัฒนา</v>
       </c>
-      <c r="D32" s="16">
-        <v>1</v>
-      </c>
-      <c r="E32" s="18">
-        <v>1</v>
-      </c>
-      <c r="F32" s="17">
-        <v>1</v>
-      </c>
-      <c r="G32" s="25">
+      <c r="D32" s="13">
+        <v>1</v>
+      </c>
+      <c r="E32" s="15">
+        <v>1</v>
+      </c>
+      <c r="F32" s="14">
+        <v>1</v>
+      </c>
+      <c r="G32" s="21">
         <v>1</v>
       </c>
       <c r="H32" s="9"/>
@@ -4850,14 +5215,14 @@
         <f>Exercise!D33</f>
         <v>นายธนากร เรืองพูน</v>
       </c>
-      <c r="D33" s="16"/>
-      <c r="E33" s="18">
-        <v>1</v>
-      </c>
-      <c r="F33" s="17">
-        <v>1</v>
-      </c>
-      <c r="G33" s="25">
+      <c r="D33" s="13"/>
+      <c r="E33" s="15">
+        <v>1</v>
+      </c>
+      <c r="F33" s="14">
+        <v>1</v>
+      </c>
+      <c r="G33" s="21">
         <v>1</v>
       </c>
       <c r="H33" s="9"/>
@@ -4881,16 +5246,16 @@
         <f>Exercise!D34</f>
         <v>นายธรรมกร เจริญพร</v>
       </c>
-      <c r="D34" s="16">
-        <v>1</v>
-      </c>
-      <c r="E34" s="18">
-        <v>1</v>
-      </c>
-      <c r="F34" s="17">
-        <v>1</v>
-      </c>
-      <c r="G34" s="25">
+      <c r="D34" s="13">
+        <v>1</v>
+      </c>
+      <c r="E34" s="15">
+        <v>1</v>
+      </c>
+      <c r="F34" s="14">
+        <v>1</v>
+      </c>
+      <c r="G34" s="21">
         <v>1</v>
       </c>
       <c r="H34" s="9"/>
@@ -4914,16 +5279,16 @@
         <f>Exercise!D35</f>
         <v>นางสาวธัชตะวัน ยกโต</v>
       </c>
-      <c r="D35" s="16">
-        <v>1</v>
-      </c>
-      <c r="E35" s="18">
-        <v>1</v>
-      </c>
-      <c r="F35" s="17">
-        <v>1</v>
-      </c>
-      <c r="G35" s="25">
+      <c r="D35" s="13">
+        <v>1</v>
+      </c>
+      <c r="E35" s="15">
+        <v>1</v>
+      </c>
+      <c r="F35" s="14">
+        <v>1</v>
+      </c>
+      <c r="G35" s="21">
         <v>1</v>
       </c>
       <c r="H35" s="9"/>
@@ -4947,16 +5312,16 @@
         <f>Exercise!D36</f>
         <v>นายนนทกร จวนทองรักษ์</v>
       </c>
-      <c r="D36" s="16">
-        <v>1</v>
-      </c>
-      <c r="E36" s="18">
-        <v>1</v>
-      </c>
-      <c r="F36" s="17">
-        <v>1</v>
-      </c>
-      <c r="G36" s="25">
+      <c r="D36" s="13">
+        <v>1</v>
+      </c>
+      <c r="E36" s="15">
+        <v>1</v>
+      </c>
+      <c r="F36" s="14">
+        <v>1</v>
+      </c>
+      <c r="G36" s="21">
         <v>1</v>
       </c>
       <c r="H36" s="9"/>
@@ -4980,16 +5345,16 @@
         <f>Exercise!D37</f>
         <v>นายนภัสรพี อร่ามฉิม</v>
       </c>
-      <c r="D37" s="16">
-        <v>1</v>
-      </c>
-      <c r="E37" s="18">
-        <v>1</v>
-      </c>
-      <c r="F37" s="17">
-        <v>1</v>
-      </c>
-      <c r="G37" s="25">
+      <c r="D37" s="13">
+        <v>1</v>
+      </c>
+      <c r="E37" s="15">
+        <v>1</v>
+      </c>
+      <c r="F37" s="14">
+        <v>1</v>
+      </c>
+      <c r="G37" s="21">
         <v>1</v>
       </c>
       <c r="H37" s="9"/>
@@ -5013,14 +5378,14 @@
         <f>Exercise!D38</f>
         <v>นายพิชญุตม์ ลอยมา</v>
       </c>
-      <c r="D38" s="16">
-        <v>1</v>
-      </c>
-      <c r="E38" s="18"/>
-      <c r="F38" s="17">
-        <v>1</v>
-      </c>
-      <c r="G38" s="25">
+      <c r="D38" s="13">
+        <v>1</v>
+      </c>
+      <c r="E38" s="15"/>
+      <c r="F38" s="14">
+        <v>1</v>
+      </c>
+      <c r="G38" s="21">
         <v>1</v>
       </c>
       <c r="H38" s="9"/>
@@ -5044,16 +5409,16 @@
         <f>Exercise!D39</f>
         <v>นายภควัฒน์ พรมประโคน</v>
       </c>
-      <c r="D39" s="16">
-        <v>1</v>
-      </c>
-      <c r="E39" s="18">
-        <v>1</v>
-      </c>
-      <c r="F39" s="17">
-        <v>1</v>
-      </c>
-      <c r="G39" s="25">
+      <c r="D39" s="13">
+        <v>1</v>
+      </c>
+      <c r="E39" s="15">
+        <v>1</v>
+      </c>
+      <c r="F39" s="14">
+        <v>1</v>
+      </c>
+      <c r="G39" s="21">
         <v>1</v>
       </c>
       <c r="H39" s="9"/>
@@ -5077,16 +5442,16 @@
         <f>Exercise!D40</f>
         <v>นายภัคพล ลาวชัย</v>
       </c>
-      <c r="D40" s="16">
-        <v>1</v>
-      </c>
-      <c r="E40" s="18">
-        <v>1</v>
-      </c>
-      <c r="F40" s="17">
-        <v>1</v>
-      </c>
-      <c r="G40" s="25">
+      <c r="D40" s="13">
+        <v>1</v>
+      </c>
+      <c r="E40" s="15">
+        <v>1</v>
+      </c>
+      <c r="F40" s="14">
+        <v>1</v>
+      </c>
+      <c r="G40" s="21">
         <v>1</v>
       </c>
       <c r="H40" s="9"/>
@@ -5110,16 +5475,16 @@
         <f>Exercise!D41</f>
         <v>นายภัคพล อินทะรังษี</v>
       </c>
-      <c r="D41" s="16">
-        <v>1</v>
-      </c>
-      <c r="E41" s="18">
-        <v>1</v>
-      </c>
-      <c r="F41" s="17">
-        <v>1</v>
-      </c>
-      <c r="G41" s="25">
+      <c r="D41" s="13">
+        <v>1</v>
+      </c>
+      <c r="E41" s="15">
+        <v>1</v>
+      </c>
+      <c r="F41" s="14">
+        <v>1</v>
+      </c>
+      <c r="G41" s="21">
         <v>1</v>
       </c>
       <c r="H41" s="9"/>
@@ -5143,16 +5508,16 @@
         <f>Exercise!D42</f>
         <v>นายยุทธนา สุขกำเนิด</v>
       </c>
-      <c r="D42" s="16">
-        <v>1</v>
-      </c>
-      <c r="E42" s="18">
-        <v>1</v>
-      </c>
-      <c r="F42" s="17">
-        <v>1</v>
-      </c>
-      <c r="G42" s="25">
+      <c r="D42" s="13">
+        <v>1</v>
+      </c>
+      <c r="E42" s="15">
+        <v>1</v>
+      </c>
+      <c r="F42" s="14">
+        <v>1</v>
+      </c>
+      <c r="G42" s="21">
         <v>1</v>
       </c>
       <c r="H42" s="9"/>
@@ -5176,16 +5541,16 @@
         <f>Exercise!D43</f>
         <v>นายรพีภัทร มอยนา</v>
       </c>
-      <c r="D43" s="16">
-        <v>1</v>
-      </c>
-      <c r="E43" s="18">
-        <v>1</v>
-      </c>
-      <c r="F43" s="17">
-        <v>1</v>
-      </c>
-      <c r="G43" s="25">
+      <c r="D43" s="13">
+        <v>1</v>
+      </c>
+      <c r="E43" s="15">
+        <v>1</v>
+      </c>
+      <c r="F43" s="14">
+        <v>1</v>
+      </c>
+      <c r="G43" s="21">
         <v>1</v>
       </c>
       <c r="H43" s="9"/>
@@ -5209,16 +5574,16 @@
         <f>Exercise!D44</f>
         <v>นายวีรภัทร ดีมาก</v>
       </c>
-      <c r="D44" s="16">
-        <v>1</v>
-      </c>
-      <c r="E44" s="18">
-        <v>1</v>
-      </c>
-      <c r="F44" s="17">
-        <v>1</v>
-      </c>
-      <c r="G44" s="25">
+      <c r="D44" s="13">
+        <v>1</v>
+      </c>
+      <c r="E44" s="15">
+        <v>1</v>
+      </c>
+      <c r="F44" s="14">
+        <v>1</v>
+      </c>
+      <c r="G44" s="21">
         <v>1</v>
       </c>
       <c r="H44" s="9"/>
@@ -5242,16 +5607,16 @@
         <f>Exercise!D45</f>
         <v>นางสาวศวิตา ไชยสุนทร</v>
       </c>
-      <c r="D45" s="16">
-        <v>1</v>
-      </c>
-      <c r="E45" s="18">
-        <v>1</v>
-      </c>
-      <c r="F45" s="17">
-        <v>1</v>
-      </c>
-      <c r="G45" s="25">
+      <c r="D45" s="13">
+        <v>1</v>
+      </c>
+      <c r="E45" s="15">
+        <v>1</v>
+      </c>
+      <c r="F45" s="14">
+        <v>1</v>
+      </c>
+      <c r="G45" s="21">
         <v>1</v>
       </c>
       <c r="H45" s="9"/>
@@ -5275,16 +5640,16 @@
         <f>Exercise!D46</f>
         <v>นายสรศักดิ์ โคตรนาม</v>
       </c>
-      <c r="D46" s="16">
-        <v>1</v>
-      </c>
-      <c r="E46" s="18">
-        <v>1</v>
-      </c>
-      <c r="F46" s="17">
-        <v>1</v>
-      </c>
-      <c r="G46" s="25">
+      <c r="D46" s="13">
+        <v>1</v>
+      </c>
+      <c r="E46" s="15">
+        <v>1</v>
+      </c>
+      <c r="F46" s="14">
+        <v>1</v>
+      </c>
+      <c r="G46" s="21">
         <v>1</v>
       </c>
       <c r="H46" s="9"/>
@@ -5308,16 +5673,16 @@
         <f>Exercise!D47</f>
         <v>นายสราวุฒิ ยะโส</v>
       </c>
-      <c r="D47" s="16">
-        <v>1</v>
-      </c>
-      <c r="E47" s="18">
-        <v>1</v>
-      </c>
-      <c r="F47" s="17">
-        <v>1</v>
-      </c>
-      <c r="G47" s="25">
+      <c r="D47" s="13">
+        <v>1</v>
+      </c>
+      <c r="E47" s="15">
+        <v>1</v>
+      </c>
+      <c r="F47" s="14">
+        <v>1</v>
+      </c>
+      <c r="G47" s="21">
         <v>1</v>
       </c>
       <c r="H47" s="9"/>
@@ -5341,16 +5706,16 @@
         <f>Exercise!D48</f>
         <v>นายสิทชัยเลิศ ศรนรายณ์</v>
       </c>
-      <c r="D48" s="16">
-        <v>1</v>
-      </c>
-      <c r="E48" s="18">
-        <v>1</v>
-      </c>
-      <c r="F48" s="17">
-        <v>1</v>
-      </c>
-      <c r="G48" s="25">
+      <c r="D48" s="13">
+        <v>1</v>
+      </c>
+      <c r="E48" s="15">
+        <v>1</v>
+      </c>
+      <c r="F48" s="14">
+        <v>1</v>
+      </c>
+      <c r="G48" s="21">
         <v>1</v>
       </c>
       <c r="H48" s="9"/>
@@ -5374,16 +5739,16 @@
         <f>Exercise!D49</f>
         <v>นายสุทธิโชติ ใบเตย</v>
       </c>
-      <c r="D49" s="16">
-        <v>1</v>
-      </c>
-      <c r="E49" s="18">
-        <v>1</v>
-      </c>
-      <c r="F49" s="17">
-        <v>1</v>
-      </c>
-      <c r="G49" s="25">
+      <c r="D49" s="13">
+        <v>1</v>
+      </c>
+      <c r="E49" s="15">
+        <v>1</v>
+      </c>
+      <c r="F49" s="14">
+        <v>1</v>
+      </c>
+      <c r="G49" s="21">
         <v>1</v>
       </c>
       <c r="H49" s="9"/>
@@ -5407,16 +5772,16 @@
         <f>Exercise!D50</f>
         <v>นายสุเมธ อบอารีย์</v>
       </c>
-      <c r="D50" s="16">
-        <v>1</v>
-      </c>
-      <c r="E50" s="18">
-        <v>1</v>
-      </c>
-      <c r="F50" s="17">
-        <v>1</v>
-      </c>
-      <c r="G50" s="25">
+      <c r="D50" s="13">
+        <v>1</v>
+      </c>
+      <c r="E50" s="15">
+        <v>1</v>
+      </c>
+      <c r="F50" s="14">
+        <v>1</v>
+      </c>
+      <c r="G50" s="21">
         <v>1</v>
       </c>
       <c r="H50" s="9"/>
@@ -5440,16 +5805,16 @@
         <f>Exercise!D51</f>
         <v>นายอัสนี คงดีจันทร์</v>
       </c>
-      <c r="D51" s="16">
-        <v>1</v>
-      </c>
-      <c r="E51" s="18">
-        <v>1</v>
-      </c>
-      <c r="F51" s="17">
-        <v>1</v>
-      </c>
-      <c r="G51" s="25">
+      <c r="D51" s="13">
+        <v>1</v>
+      </c>
+      <c r="E51" s="15">
+        <v>1</v>
+      </c>
+      <c r="F51" s="14">
+        <v>1</v>
+      </c>
+      <c r="G51" s="21">
         <v>1</v>
       </c>
       <c r="H51" s="9"/>
@@ -5473,16 +5838,16 @@
         <f>Exercise!D52</f>
         <v>นางสาวอาทิตยา ไทยเจริญ</v>
       </c>
-      <c r="D52" s="16">
-        <v>1</v>
-      </c>
-      <c r="E52" s="18">
-        <v>1</v>
-      </c>
-      <c r="F52" s="17">
-        <v>1</v>
-      </c>
-      <c r="G52" s="25">
+      <c r="D52" s="13">
+        <v>1</v>
+      </c>
+      <c r="E52" s="15">
+        <v>1</v>
+      </c>
+      <c r="F52" s="14">
+        <v>1</v>
+      </c>
+      <c r="G52" s="21">
         <v>1</v>
       </c>
       <c r="H52" s="9"/>
@@ -5506,16 +5871,16 @@
         <f>Exercise!D53</f>
         <v>นางสาวอารยา แสนสุข</v>
       </c>
-      <c r="D53" s="17">
-        <v>1</v>
-      </c>
-      <c r="E53" s="18">
-        <v>1</v>
-      </c>
-      <c r="F53" s="17">
-        <v>1</v>
-      </c>
-      <c r="G53" s="25">
+      <c r="D53" s="14">
+        <v>1</v>
+      </c>
+      <c r="E53" s="15">
+        <v>1</v>
+      </c>
+      <c r="F53" s="14">
+        <v>1</v>
+      </c>
+      <c r="G53" s="21">
         <v>1</v>
       </c>
       <c r="H53" s="9"/>

--- a/Score_Class_2026.xlsx
+++ b/Score_Class_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Phisan\Consultancy\2569-KU_MapProjection\Admin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{472144FF-D389-466B-B6B3-C152740D2249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9F95260-3310-4AD7-9563-9FBF5D5245AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43480" yWindow="-5060" windowWidth="25130" windowHeight="19430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38300" yWindow="-7000" windowWidth="18380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Exercise" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="312">
   <si>
     <t>รายงานแสดงจำนวนนิสิต จำแนกตามหมู่เรียน ภาคต้น ปีการศึกษา 2569</t>
   </si>
@@ -967,6 +967,9 @@
   </si>
   <si>
     <t>Ex.7 Lambert Conformal Conic</t>
+  </si>
+  <si>
+    <t>Ex.8 Planar Map Projection</t>
   </si>
 </sst>
 </file>
@@ -1059,12 +1062,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="0" tint="-4.9989318521683403E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1072,6 +1069,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1116,7 +1119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1175,18 +1178,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1196,22 +1187,38 @@
     <xf numFmtId="187" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="187" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1449,50 +1456,50 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:26" ht="16" customHeight="1">
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36"/>
-      <c r="J2" s="36"/>
-      <c r="K2" s="36"/>
-      <c r="L2" s="36"/>
-      <c r="M2" s="36"/>
-      <c r="N2" s="36"/>
-      <c r="O2" s="36"/>
-      <c r="P2" s="36"/>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="36"/>
-      <c r="S2" s="36"/>
-      <c r="T2" s="36"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
+      <c r="L2" s="38"/>
+      <c r="M2" s="38"/>
+      <c r="N2" s="38"/>
+      <c r="O2" s="38"/>
+      <c r="P2" s="38"/>
+      <c r="Q2" s="38"/>
+      <c r="R2" s="38"/>
+      <c r="S2" s="38"/>
+      <c r="T2" s="38"/>
     </row>
     <row r="3" spans="2:26" ht="18.3" customHeight="1">
-      <c r="B3" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="36"/>
-      <c r="J3" s="36"/>
-      <c r="K3" s="36"/>
-      <c r="L3" s="36"/>
-      <c r="M3" s="36"/>
-      <c r="N3" s="36"/>
-      <c r="O3" s="36"/>
-      <c r="P3" s="36"/>
-      <c r="Q3" s="36"/>
-      <c r="R3" s="36"/>
-      <c r="S3" s="36"/>
-      <c r="T3" s="36"/>
+      <c r="B3" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="38"/>
+      <c r="K3" s="38"/>
+      <c r="L3" s="38"/>
+      <c r="M3" s="38"/>
+      <c r="N3" s="38"/>
+      <c r="O3" s="38"/>
+      <c r="P3" s="38"/>
+      <c r="Q3" s="38"/>
+      <c r="R3" s="38"/>
+      <c r="S3" s="38"/>
+      <c r="T3" s="38"/>
     </row>
     <row r="4" spans="2:26" ht="26.1" customHeight="1">
       <c r="B4" s="1" t="s">
@@ -1501,16 +1508,16 @@
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="M4" s="37" t="s">
+      <c r="M4" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="N4" s="37"/>
-      <c r="O4" s="37"/>
-      <c r="P4" s="37"/>
-      <c r="Q4" s="37"/>
-      <c r="R4" s="37"/>
-      <c r="S4" s="37"/>
-      <c r="T4" s="37"/>
+      <c r="N4" s="39"/>
+      <c r="O4" s="39"/>
+      <c r="P4" s="39"/>
+      <c r="Q4" s="39"/>
+      <c r="R4" s="39"/>
+      <c r="S4" s="39"/>
+      <c r="T4" s="39"/>
     </row>
     <row r="5" spans="2:26" ht="18">
       <c r="E5" s="1" t="s">
@@ -1536,7 +1543,7 @@
       <c r="M6" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="N6" s="32" t="s">
+      <c r="N6" s="28" t="s">
         <v>12</v>
       </c>
       <c r="O6" s="11" t="s">
@@ -1545,13 +1552,15 @@
       <c r="P6" s="11" t="s">
         <v>306</v>
       </c>
-      <c r="Q6" s="33" t="s">
+      <c r="Q6" s="29" t="s">
         <v>308</v>
       </c>
       <c r="R6" s="11" t="s">
         <v>310</v>
       </c>
-      <c r="S6" s="10"/>
+      <c r="S6" s="11" t="s">
+        <v>311</v>
+      </c>
       <c r="T6" s="10"/>
       <c r="U6" s="9"/>
       <c r="V6" s="9"/>
@@ -1591,29 +1600,31 @@
       <c r="K7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="L7" s="26">
+      <c r="L7" s="22">
         <v>12</v>
       </c>
-      <c r="M7" s="26">
-        <v>10</v>
-      </c>
-      <c r="N7" s="26">
-        <v>10</v>
-      </c>
-      <c r="O7" s="26">
-        <v>10</v>
-      </c>
-      <c r="P7" s="26">
-        <v>10</v>
-      </c>
-      <c r="Q7" s="34">
+      <c r="M7" s="22">
+        <v>10</v>
+      </c>
+      <c r="N7" s="22">
+        <v>10</v>
+      </c>
+      <c r="O7" s="22">
+        <v>10</v>
+      </c>
+      <c r="P7" s="22">
+        <v>10</v>
+      </c>
+      <c r="Q7" s="30">
         <v>26</v>
       </c>
-      <c r="R7" s="26">
-        <v>10</v>
-      </c>
-      <c r="S7" s="26"/>
-      <c r="T7" s="26"/>
+      <c r="R7" s="22">
+        <v>10</v>
+      </c>
+      <c r="S7" s="22">
+        <v>10</v>
+      </c>
+      <c r="T7" s="22"/>
       <c r="U7" s="9"/>
       <c r="V7" s="9"/>
       <c r="W7" s="9"/>
@@ -1658,14 +1669,18 @@
         <v>8</v>
       </c>
       <c r="O8" s="10"/>
-      <c r="P8" s="10"/>
-      <c r="Q8" s="35">
+      <c r="P8" s="10">
+        <v>8</v>
+      </c>
+      <c r="Q8" s="31">
         <v>10</v>
       </c>
       <c r="R8" s="10">
         <v>5</v>
       </c>
-      <c r="S8" s="10"/>
+      <c r="S8" s="10">
+        <v>0</v>
+      </c>
       <c r="T8" s="10"/>
       <c r="U8" s="9"/>
       <c r="V8" s="9"/>
@@ -1714,13 +1729,15 @@
         <v>10</v>
       </c>
       <c r="P9" s="10"/>
-      <c r="Q9" s="35">
+      <c r="Q9" s="31">
         <v>4</v>
       </c>
       <c r="R9" s="10">
         <v>10</v>
       </c>
-      <c r="S9" s="10"/>
+      <c r="S9" s="10">
+        <v>10</v>
+      </c>
       <c r="T9" s="10"/>
       <c r="U9" s="9"/>
       <c r="V9" s="9"/>
@@ -1771,11 +1788,13 @@
       <c r="P10" s="10">
         <v>8</v>
       </c>
-      <c r="Q10" s="35">
+      <c r="Q10" s="31">
         <v>4</v>
       </c>
       <c r="R10" s="10"/>
-      <c r="S10" s="10"/>
+      <c r="S10" s="10">
+        <v>10</v>
+      </c>
       <c r="T10" s="10"/>
       <c r="U10" s="9"/>
       <c r="V10" s="9"/>
@@ -1830,13 +1849,15 @@
       <c r="P11" s="10">
         <v>9</v>
       </c>
-      <c r="Q11" s="35">
+      <c r="Q11" s="31">
         <v>9</v>
       </c>
       <c r="R11" s="10">
         <v>10</v>
       </c>
-      <c r="S11" s="10"/>
+      <c r="S11" s="10">
+        <v>10</v>
+      </c>
       <c r="T11" s="10"/>
       <c r="U11" s="9"/>
       <c r="V11" s="9"/>
@@ -1885,13 +1906,15 @@
       <c r="P12" s="10">
         <v>10</v>
       </c>
-      <c r="Q12" s="35">
+      <c r="Q12" s="31">
         <v>9</v>
       </c>
       <c r="R12" s="10">
         <v>10</v>
       </c>
-      <c r="S12" s="10"/>
+      <c r="S12" s="10">
+        <v>10</v>
+      </c>
       <c r="T12" s="10"/>
       <c r="U12" s="9"/>
       <c r="V12" s="9"/>
@@ -1936,13 +1959,15 @@
       <c r="N13" s="10"/>
       <c r="O13" s="10"/>
       <c r="P13" s="10"/>
-      <c r="Q13" s="35">
+      <c r="Q13" s="31">
         <v>0</v>
       </c>
       <c r="R13" s="10">
         <v>5</v>
       </c>
-      <c r="S13" s="10"/>
+      <c r="S13" s="10">
+        <v>10</v>
+      </c>
       <c r="T13" s="10"/>
       <c r="U13" s="9"/>
       <c r="V13" s="9"/>
@@ -1993,13 +2018,15 @@
       <c r="P14" s="10">
         <v>8</v>
       </c>
-      <c r="Q14" s="35">
+      <c r="Q14" s="31">
         <v>2</v>
       </c>
       <c r="R14" s="10">
         <v>10</v>
       </c>
-      <c r="S14" s="10"/>
+      <c r="S14" s="10">
+        <v>3</v>
+      </c>
       <c r="T14" s="10"/>
       <c r="U14" s="9"/>
       <c r="V14" s="9"/>
@@ -2054,13 +2081,15 @@
       <c r="P15" s="10">
         <v>8</v>
       </c>
-      <c r="Q15" s="35">
+      <c r="Q15" s="31">
         <v>11</v>
       </c>
       <c r="R15" s="10">
         <v>8</v>
       </c>
-      <c r="S15" s="10"/>
+      <c r="S15" s="10">
+        <v>8</v>
+      </c>
       <c r="T15" s="10"/>
       <c r="U15" s="9"/>
       <c r="V15" s="9"/>
@@ -2111,13 +2140,15 @@
         <v>5</v>
       </c>
       <c r="P16" s="10"/>
-      <c r="Q16" s="35">
+      <c r="Q16" s="31">
         <v>14</v>
       </c>
       <c r="R16" s="10">
         <v>3</v>
       </c>
-      <c r="S16" s="10"/>
+      <c r="S16" s="10">
+        <v>10</v>
+      </c>
       <c r="T16" s="10"/>
       <c r="U16" s="9"/>
       <c r="V16" s="9"/>
@@ -2172,13 +2203,15 @@
       <c r="P17" s="10">
         <v>10</v>
       </c>
-      <c r="Q17" s="35">
+      <c r="Q17" s="31">
         <v>9</v>
       </c>
       <c r="R17" s="10">
         <v>10</v>
       </c>
-      <c r="S17" s="10"/>
+      <c r="S17" s="10">
+        <v>10</v>
+      </c>
       <c r="T17" s="10"/>
       <c r="U17" s="9"/>
       <c r="V17" s="9"/>
@@ -2229,13 +2262,15 @@
       <c r="P18" s="10">
         <v>9</v>
       </c>
-      <c r="Q18" s="35">
+      <c r="Q18" s="31">
         <v>2</v>
       </c>
       <c r="R18" s="10">
         <v>10</v>
       </c>
-      <c r="S18" s="10"/>
+      <c r="S18" s="10">
+        <v>10</v>
+      </c>
       <c r="T18" s="10"/>
       <c r="U18" s="9"/>
       <c r="V18" s="9"/>
@@ -2280,13 +2315,15 @@
       <c r="N19" s="10"/>
       <c r="O19" s="10"/>
       <c r="P19" s="10"/>
-      <c r="Q19" s="35">
+      <c r="Q19" s="31">
         <v>0</v>
       </c>
       <c r="R19" s="10">
         <v>10</v>
       </c>
-      <c r="S19" s="10"/>
+      <c r="S19" s="10">
+        <v>10</v>
+      </c>
       <c r="T19" s="10"/>
       <c r="U19" s="9"/>
       <c r="V19" s="9"/>
@@ -2341,7 +2378,7 @@
       <c r="P20" s="10">
         <v>10</v>
       </c>
-      <c r="Q20" s="35">
+      <c r="Q20" s="31">
         <v>5</v>
       </c>
       <c r="R20" s="10">
@@ -2398,11 +2435,13 @@
         <v>5</v>
       </c>
       <c r="P21" s="10"/>
-      <c r="Q21" s="35">
+      <c r="Q21" s="31">
         <v>6</v>
       </c>
       <c r="R21" s="10"/>
-      <c r="S21" s="10"/>
+      <c r="S21" s="10">
+        <v>10</v>
+      </c>
       <c r="T21" s="10"/>
       <c r="U21" s="9"/>
       <c r="V21" s="9"/>
@@ -2457,13 +2496,15 @@
       <c r="P22" s="10">
         <v>10</v>
       </c>
-      <c r="Q22" s="35">
+      <c r="Q22" s="31">
         <v>2</v>
       </c>
       <c r="R22" s="10">
         <v>10</v>
       </c>
-      <c r="S22" s="10"/>
+      <c r="S22" s="10">
+        <v>9</v>
+      </c>
       <c r="T22" s="10"/>
       <c r="U22" s="9"/>
       <c r="V22" s="9"/>
@@ -2518,13 +2559,15 @@
       <c r="P23" s="10">
         <v>10</v>
       </c>
-      <c r="Q23" s="35">
+      <c r="Q23" s="31">
         <v>16</v>
       </c>
       <c r="R23" s="10">
         <v>10</v>
       </c>
-      <c r="S23" s="10"/>
+      <c r="S23" s="10">
+        <v>10</v>
+      </c>
       <c r="T23" s="10"/>
       <c r="U23" s="9"/>
       <c r="V23" s="9"/>
@@ -2579,13 +2622,15 @@
       <c r="P24" s="10">
         <v>10</v>
       </c>
-      <c r="Q24" s="35">
+      <c r="Q24" s="31">
         <v>12</v>
       </c>
       <c r="R24" s="10">
         <v>10</v>
       </c>
-      <c r="S24" s="10"/>
+      <c r="S24" s="10">
+        <v>10</v>
+      </c>
       <c r="T24" s="10"/>
       <c r="U24" s="9"/>
       <c r="V24" s="9"/>
@@ -2640,13 +2685,15 @@
       <c r="P25" s="10">
         <v>10</v>
       </c>
-      <c r="Q25" s="35">
+      <c r="Q25" s="31">
         <v>9</v>
       </c>
       <c r="R25" s="10">
         <v>10</v>
       </c>
-      <c r="S25" s="10"/>
+      <c r="S25" s="10">
+        <v>5</v>
+      </c>
       <c r="T25" s="10"/>
       <c r="U25" s="9"/>
       <c r="V25" s="9"/>
@@ -2701,13 +2748,15 @@
       <c r="P26" s="10">
         <v>10</v>
       </c>
-      <c r="Q26" s="35">
+      <c r="Q26" s="31">
         <v>1</v>
       </c>
       <c r="R26" s="10">
         <v>10</v>
       </c>
-      <c r="S26" s="10"/>
+      <c r="S26" s="10">
+        <v>10</v>
+      </c>
       <c r="T26" s="10"/>
       <c r="U26" s="9"/>
       <c r="V26" s="9"/>
@@ -2760,13 +2809,15 @@
       <c r="P27" s="10">
         <v>10</v>
       </c>
-      <c r="Q27" s="35">
+      <c r="Q27" s="31">
         <v>1</v>
       </c>
       <c r="R27" s="10">
         <v>10</v>
       </c>
-      <c r="S27" s="10"/>
+      <c r="S27" s="10">
+        <v>10</v>
+      </c>
       <c r="T27" s="10"/>
       <c r="U27" s="9"/>
       <c r="V27" s="9"/>
@@ -2817,13 +2868,15 @@
         <v>4</v>
       </c>
       <c r="P28" s="10"/>
-      <c r="Q28" s="35">
+      <c r="Q28" s="31">
         <v>8</v>
       </c>
       <c r="R28" s="10">
         <v>10</v>
       </c>
-      <c r="S28" s="10"/>
+      <c r="S28" s="10">
+        <v>10</v>
+      </c>
       <c r="T28" s="10"/>
       <c r="U28" s="9"/>
       <c r="V28" s="9"/>
@@ -2878,13 +2931,15 @@
       <c r="P29" s="10">
         <v>10</v>
       </c>
-      <c r="Q29" s="35">
+      <c r="Q29" s="31">
         <v>9</v>
       </c>
       <c r="R29" s="10">
         <v>10</v>
       </c>
-      <c r="S29" s="10"/>
+      <c r="S29" s="10">
+        <v>10</v>
+      </c>
       <c r="T29" s="10"/>
       <c r="U29" s="9"/>
       <c r="V29" s="9"/>
@@ -2939,13 +2994,15 @@
       <c r="P30" s="10">
         <v>10</v>
       </c>
-      <c r="Q30" s="35">
+      <c r="Q30" s="31">
         <v>11</v>
       </c>
       <c r="R30" s="10">
         <v>10</v>
       </c>
-      <c r="S30" s="10"/>
+      <c r="S30" s="10">
+        <v>10</v>
+      </c>
       <c r="T30" s="10"/>
       <c r="U30" s="9"/>
       <c r="V30" s="9"/>
@@ -2955,51 +3012,51 @@
       <c r="Z30" s="9"/>
     </row>
     <row r="31" spans="2:26" ht="18">
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="32" t="s">
         <v>164</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="33" t="s">
         <v>165</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="33" t="s">
         <v>166</v>
       </c>
-      <c r="E31" s="4" t="s">
+      <c r="E31" s="33" t="s">
         <v>167</v>
       </c>
-      <c r="F31" s="4" t="s">
+      <c r="F31" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="G31" s="4" t="s">
+      <c r="G31" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="H31" s="4" t="s">
+      <c r="H31" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="I31" s="4" t="s">
+      <c r="I31" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="J31" s="4" t="s">
+      <c r="J31" s="33" t="s">
         <v>168</v>
       </c>
-      <c r="K31" s="7" t="s">
+      <c r="K31" s="34" t="s">
         <v>169</v>
       </c>
-      <c r="L31" s="10"/>
-      <c r="M31" s="10"/>
-      <c r="N31" s="10"/>
-      <c r="O31" s="10"/>
-      <c r="P31" s="10"/>
+      <c r="L31" s="35"/>
+      <c r="M31" s="35"/>
+      <c r="N31" s="35"/>
+      <c r="O31" s="35"/>
+      <c r="P31" s="35"/>
       <c r="Q31" s="35"/>
-      <c r="R31" s="10"/>
-      <c r="S31" s="10"/>
-      <c r="T31" s="10"/>
-      <c r="U31" s="9"/>
-      <c r="V31" s="9"/>
-      <c r="W31" s="9"/>
-      <c r="X31" s="9"/>
-      <c r="Y31" s="9"/>
-      <c r="Z31" s="9"/>
+      <c r="R31" s="35"/>
+      <c r="S31" s="35"/>
+      <c r="T31" s="35"/>
+      <c r="U31" s="36"/>
+      <c r="V31" s="36"/>
+      <c r="W31" s="36"/>
+      <c r="X31" s="36"/>
+      <c r="Y31" s="36"/>
+      <c r="Z31" s="36"/>
     </row>
     <row r="32" spans="2:26" ht="18">
       <c r="B32" s="5" t="s">
@@ -3047,13 +3104,15 @@
       <c r="P32" s="10">
         <v>10</v>
       </c>
-      <c r="Q32" s="35">
+      <c r="Q32" s="31">
         <v>14</v>
       </c>
       <c r="R32" s="10">
         <v>5</v>
       </c>
-      <c r="S32" s="10"/>
+      <c r="S32" s="10">
+        <v>10</v>
+      </c>
       <c r="T32" s="10"/>
       <c r="U32" s="9"/>
       <c r="V32" s="9"/>
@@ -3106,13 +3165,15 @@
       <c r="P33" s="10">
         <v>10</v>
       </c>
-      <c r="Q33" s="35">
+      <c r="Q33" s="31">
         <v>3</v>
       </c>
       <c r="R33" s="10">
         <v>10</v>
       </c>
-      <c r="S33" s="10"/>
+      <c r="S33" s="10">
+        <v>10</v>
+      </c>
       <c r="T33" s="10"/>
       <c r="U33" s="9"/>
       <c r="V33" s="9"/>
@@ -3122,57 +3183,61 @@
       <c r="Z33" s="9"/>
     </row>
     <row r="34" spans="2:26" ht="18">
-      <c r="B34" s="22" t="s">
+      <c r="B34" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="C34" s="23" t="s">
+      <c r="C34" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="D34" s="23" t="s">
+      <c r="D34" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="E34" s="23" t="s">
+      <c r="E34" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="F34" s="23" t="s">
+      <c r="F34" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="G34" s="23" t="s">
+      <c r="G34" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H34" s="23" t="s">
+      <c r="H34" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="I34" s="23" t="s">
+      <c r="I34" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="J34" s="23" t="s">
+      <c r="J34" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="K34" s="24" t="s">
+      <c r="K34" s="7" t="s">
         <v>186</v>
       </c>
       <c r="L34" s="10">
         <v>12</v>
       </c>
-      <c r="M34" s="25">
-        <v>4</v>
-      </c>
-      <c r="N34" s="10"/>
-      <c r="O34" s="25">
-        <v>10</v>
-      </c>
-      <c r="P34" s="25">
-        <v>10</v>
-      </c>
-      <c r="Q34" s="35">
+      <c r="M34" s="10">
+        <v>8</v>
+      </c>
+      <c r="N34" s="10">
+        <v>10</v>
+      </c>
+      <c r="O34" s="10">
+        <v>10</v>
+      </c>
+      <c r="P34" s="10">
+        <v>10</v>
+      </c>
+      <c r="Q34" s="10">
         <v>25</v>
       </c>
-      <c r="R34" s="25">
-        <v>10</v>
-      </c>
-      <c r="S34" s="25"/>
-      <c r="T34" s="25"/>
+      <c r="R34" s="10">
+        <v>10</v>
+      </c>
+      <c r="S34" s="10">
+        <v>10</v>
+      </c>
+      <c r="T34" s="10"/>
       <c r="U34" s="9"/>
       <c r="V34" s="9"/>
       <c r="W34" s="9"/>
@@ -3226,13 +3291,15 @@
       <c r="P35" s="10">
         <v>10</v>
       </c>
-      <c r="Q35" s="35">
+      <c r="Q35" s="31">
         <v>17</v>
       </c>
       <c r="R35" s="10">
         <v>7</v>
       </c>
-      <c r="S35" s="10"/>
+      <c r="S35" s="10">
+        <v>10</v>
+      </c>
       <c r="T35" s="10"/>
       <c r="U35" s="9"/>
       <c r="V35" s="9"/>
@@ -3287,13 +3354,15 @@
       <c r="P36" s="10">
         <v>10</v>
       </c>
-      <c r="Q36" s="35">
+      <c r="Q36" s="31">
         <v>7</v>
       </c>
       <c r="R36" s="10">
         <v>10</v>
       </c>
-      <c r="S36" s="10"/>
+      <c r="S36" s="10">
+        <v>10</v>
+      </c>
       <c r="T36" s="10"/>
       <c r="U36" s="9"/>
       <c r="V36" s="9"/>
@@ -3348,13 +3417,15 @@
       <c r="P37" s="10">
         <v>9</v>
       </c>
-      <c r="Q37" s="35">
+      <c r="Q37" s="31">
         <v>17</v>
       </c>
       <c r="R37" s="10">
         <v>10</v>
       </c>
-      <c r="S37" s="10"/>
+      <c r="S37" s="10">
+        <v>10</v>
+      </c>
       <c r="T37" s="10"/>
       <c r="U37" s="9"/>
       <c r="V37" s="9"/>
@@ -3407,13 +3478,15 @@
       <c r="P38" s="10">
         <v>10</v>
       </c>
-      <c r="Q38" s="35">
+      <c r="Q38" s="31">
         <v>16</v>
       </c>
       <c r="R38" s="10">
         <v>5</v>
       </c>
-      <c r="S38" s="10"/>
+      <c r="S38" s="10">
+        <v>10</v>
+      </c>
       <c r="T38" s="10"/>
       <c r="U38" s="9"/>
       <c r="V38" s="9"/>
@@ -3468,13 +3541,15 @@
       <c r="P39" s="10">
         <v>10</v>
       </c>
-      <c r="Q39" s="35">
+      <c r="Q39" s="31">
         <v>22</v>
       </c>
       <c r="R39" s="10">
         <v>10</v>
       </c>
-      <c r="S39" s="10"/>
+      <c r="S39" s="10">
+        <v>10</v>
+      </c>
       <c r="T39" s="10"/>
       <c r="U39" s="9"/>
       <c r="V39" s="9"/>
@@ -3529,13 +3604,15 @@
       <c r="P40" s="10">
         <v>10</v>
       </c>
-      <c r="Q40" s="35">
+      <c r="Q40" s="31">
         <v>15</v>
       </c>
       <c r="R40" s="10">
         <v>5</v>
       </c>
-      <c r="S40" s="10"/>
+      <c r="S40" s="10">
+        <v>10</v>
+      </c>
       <c r="T40" s="10"/>
       <c r="U40" s="9"/>
       <c r="V40" s="9"/>
@@ -3590,13 +3667,15 @@
       <c r="P41" s="10">
         <v>10</v>
       </c>
-      <c r="Q41" s="35">
+      <c r="Q41" s="31">
         <v>6</v>
       </c>
       <c r="R41" s="10">
         <v>5</v>
       </c>
-      <c r="S41" s="10"/>
+      <c r="S41" s="10">
+        <v>10</v>
+      </c>
       <c r="T41" s="10"/>
       <c r="U41" s="9"/>
       <c r="V41" s="9"/>
@@ -3649,7 +3728,7 @@
         <v>10</v>
       </c>
       <c r="P42" s="10"/>
-      <c r="Q42" s="35">
+      <c r="Q42" s="31">
         <v>4</v>
       </c>
       <c r="R42" s="10">
@@ -3710,13 +3789,15 @@
       <c r="P43" s="10">
         <v>9</v>
       </c>
-      <c r="Q43" s="35">
+      <c r="Q43" s="31">
         <v>4</v>
       </c>
       <c r="R43" s="10">
         <v>7</v>
       </c>
-      <c r="S43" s="10"/>
+      <c r="S43" s="10">
+        <v>5</v>
+      </c>
       <c r="T43" s="10"/>
       <c r="U43" s="9"/>
       <c r="V43" s="9"/>
@@ -3771,13 +3852,15 @@
       <c r="P44" s="10">
         <v>5</v>
       </c>
-      <c r="Q44" s="35">
+      <c r="Q44" s="31">
         <v>4</v>
       </c>
       <c r="R44" s="10">
         <v>7</v>
       </c>
-      <c r="S44" s="10"/>
+      <c r="S44" s="10">
+        <v>10</v>
+      </c>
       <c r="T44" s="10"/>
       <c r="U44" s="9"/>
       <c r="V44" s="9"/>
@@ -3832,13 +3915,15 @@
       <c r="P45" s="10">
         <v>9</v>
       </c>
-      <c r="Q45" s="35">
+      <c r="Q45" s="31">
         <v>18</v>
       </c>
       <c r="R45" s="10">
         <v>10</v>
       </c>
-      <c r="S45" s="10"/>
+      <c r="S45" s="10">
+        <v>10</v>
+      </c>
       <c r="T45" s="10"/>
       <c r="U45" s="9"/>
       <c r="V45" s="9"/>
@@ -3893,13 +3978,15 @@
       <c r="P46" s="10">
         <v>10</v>
       </c>
-      <c r="Q46" s="35">
+      <c r="Q46" s="31">
         <v>3</v>
       </c>
       <c r="R46" s="10">
         <v>10</v>
       </c>
-      <c r="S46" s="10"/>
+      <c r="S46" s="10">
+        <v>10</v>
+      </c>
       <c r="T46" s="10"/>
       <c r="U46" s="9"/>
       <c r="V46" s="9"/>
@@ -3954,13 +4041,15 @@
       <c r="P47" s="10">
         <v>10</v>
       </c>
-      <c r="Q47" s="35">
+      <c r="Q47" s="31">
         <v>13</v>
       </c>
       <c r="R47" s="10">
         <v>7</v>
       </c>
-      <c r="S47" s="10"/>
+      <c r="S47" s="10">
+        <v>10</v>
+      </c>
       <c r="T47" s="10"/>
       <c r="U47" s="9"/>
       <c r="V47" s="9"/>
@@ -4015,13 +4104,15 @@
       <c r="P48" s="10">
         <v>10</v>
       </c>
-      <c r="Q48" s="35">
+      <c r="Q48" s="31">
         <v>6</v>
       </c>
       <c r="R48" s="10">
         <v>10</v>
       </c>
-      <c r="S48" s="10"/>
+      <c r="S48" s="10">
+        <v>10</v>
+      </c>
       <c r="T48" s="10"/>
       <c r="U48" s="9"/>
       <c r="V48" s="9"/>
@@ -4076,13 +4167,15 @@
       <c r="P49" s="10">
         <v>10</v>
       </c>
-      <c r="Q49" s="35">
+      <c r="Q49" s="31">
         <v>21</v>
       </c>
       <c r="R49" s="10">
         <v>6</v>
       </c>
-      <c r="S49" s="10"/>
+      <c r="S49" s="10">
+        <v>10</v>
+      </c>
       <c r="T49" s="10"/>
       <c r="U49" s="9"/>
       <c r="V49" s="9"/>
@@ -4137,13 +4230,15 @@
       <c r="P50" s="10">
         <v>10</v>
       </c>
-      <c r="Q50" s="35">
+      <c r="Q50" s="31">
         <v>20</v>
       </c>
       <c r="R50" s="10">
         <v>10</v>
       </c>
-      <c r="S50" s="10"/>
+      <c r="S50" s="10">
+        <v>10</v>
+      </c>
       <c r="T50" s="10"/>
       <c r="U50" s="9"/>
       <c r="V50" s="9"/>
@@ -4196,7 +4291,7 @@
         <v>10</v>
       </c>
       <c r="P51" s="10"/>
-      <c r="Q51" s="35">
+      <c r="Q51" s="31">
         <v>4</v>
       </c>
       <c r="R51" s="10">
@@ -4257,13 +4352,15 @@
       <c r="P52" s="10">
         <v>8</v>
       </c>
-      <c r="Q52" s="35">
+      <c r="Q52" s="31">
         <v>22</v>
       </c>
       <c r="R52" s="10">
         <v>10</v>
       </c>
-      <c r="S52" s="10"/>
+      <c r="S52" s="10">
+        <v>10</v>
+      </c>
       <c r="T52" s="10"/>
       <c r="U52" s="9"/>
       <c r="V52" s="9"/>
@@ -4318,13 +4415,15 @@
       <c r="P53" s="10">
         <v>10</v>
       </c>
-      <c r="Q53" s="35">
+      <c r="Q53" s="31">
         <v>19</v>
       </c>
       <c r="R53" s="10">
         <v>10</v>
       </c>
-      <c r="S53" s="10"/>
+      <c r="S53" s="10">
+        <v>10</v>
+      </c>
       <c r="T53" s="10"/>
       <c r="U53" s="9"/>
       <c r="V53" s="9"/>
@@ -4334,7 +4433,7 @@
       <c r="Z53" s="9"/>
     </row>
     <row r="54" spans="2:26">
-      <c r="Q54" s="27" t="s">
+      <c r="Q54" s="23" t="s">
         <v>309</v>
       </c>
     </row>
@@ -4389,10 +4488,12 @@
       <c r="F6" s="19" t="s">
         <v>307</v>
       </c>
-      <c r="G6" s="28">
+      <c r="G6" s="24">
         <v>46258</v>
       </c>
-      <c r="H6" s="17"/>
+      <c r="H6" s="37">
+        <v>46265</v>
+      </c>
       <c r="I6" s="17"/>
       <c r="J6" s="17"/>
       <c r="K6" s="17"/>
@@ -4401,29 +4502,29 @@
       <c r="N6" s="17"/>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" s="29" t="str">
+      <c r="A7" s="25" t="str">
         <f>Exercise!B7</f>
         <v>ลำดับที่</v>
       </c>
-      <c r="B7" s="29" t="str">
+      <c r="B7" s="25" t="str">
         <f>Exercise!C7</f>
         <v>รหัสนิสิต</v>
       </c>
-      <c r="C7" s="29" t="str">
+      <c r="C7" s="25" t="str">
         <f>Exercise!D7</f>
         <v>ชื่อ-นามสกุล</v>
       </c>
-      <c r="D7" s="30"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="31"/>
-      <c r="G7" s="31"/>
-      <c r="H7" s="30"/>
-      <c r="I7" s="30"/>
-      <c r="J7" s="30"/>
-      <c r="K7" s="30"/>
-      <c r="L7" s="30"/>
-      <c r="M7" s="30"/>
-      <c r="N7" s="30"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="26"/>
+      <c r="I7" s="26"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="26"/>
+      <c r="L7" s="26"/>
+      <c r="M7" s="26"/>
+      <c r="N7" s="26"/>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="9" t="str">
@@ -4446,7 +4547,9 @@
         <v>1</v>
       </c>
       <c r="G8" s="21"/>
-      <c r="H8" s="9"/>
+      <c r="H8" s="9">
+        <v>1</v>
+      </c>
       <c r="I8" s="9"/>
       <c r="J8" s="9"/>
       <c r="K8" s="9"/>
@@ -4475,7 +4578,9 @@
       <c r="G9" s="21">
         <v>1</v>
       </c>
-      <c r="H9" s="9"/>
+      <c r="H9" s="9">
+        <v>1</v>
+      </c>
       <c r="I9" s="9"/>
       <c r="J9" s="9"/>
       <c r="K9" s="9"/>
@@ -4502,7 +4607,9 @@
       </c>
       <c r="F10" s="14"/>
       <c r="G10" s="21"/>
-      <c r="H10" s="9"/>
+      <c r="H10" s="9">
+        <v>1</v>
+      </c>
       <c r="I10" s="9"/>
       <c r="J10" s="9"/>
       <c r="K10" s="9"/>
@@ -4535,7 +4642,9 @@
       <c r="G11" s="21">
         <v>1</v>
       </c>
-      <c r="H11" s="9"/>
+      <c r="H11" s="9">
+        <v>1</v>
+      </c>
       <c r="I11" s="9"/>
       <c r="J11" s="9"/>
       <c r="K11" s="9"/>
@@ -4568,7 +4677,9 @@
       <c r="G12" s="21">
         <v>1</v>
       </c>
-      <c r="H12" s="9"/>
+      <c r="H12" s="9">
+        <v>1</v>
+      </c>
       <c r="I12" s="9"/>
       <c r="J12" s="9"/>
       <c r="K12" s="9"/>
@@ -4597,7 +4708,9 @@
       <c r="G13" s="21">
         <v>1</v>
       </c>
-      <c r="H13" s="9"/>
+      <c r="H13" s="9">
+        <v>1</v>
+      </c>
       <c r="I13" s="9"/>
       <c r="J13" s="9"/>
       <c r="K13" s="9"/>
@@ -4661,7 +4774,9 @@
       <c r="G15" s="21">
         <v>1</v>
       </c>
-      <c r="H15" s="9"/>
+      <c r="H15" s="9">
+        <v>1</v>
+      </c>
       <c r="I15" s="9"/>
       <c r="J15" s="9"/>
       <c r="K15" s="9"/>
@@ -4694,7 +4809,9 @@
       <c r="G16" s="21">
         <v>1</v>
       </c>
-      <c r="H16" s="9"/>
+      <c r="H16" s="9">
+        <v>1</v>
+      </c>
       <c r="I16" s="9"/>
       <c r="J16" s="9"/>
       <c r="K16" s="9"/>
@@ -4727,7 +4844,9 @@
       <c r="G17" s="21">
         <v>1</v>
       </c>
-      <c r="H17" s="9"/>
+      <c r="H17" s="9">
+        <v>1</v>
+      </c>
       <c r="I17" s="9"/>
       <c r="J17" s="9"/>
       <c r="K17" s="9"/>
@@ -4758,7 +4877,9 @@
       <c r="G18" s="21">
         <v>1</v>
       </c>
-      <c r="H18" s="9"/>
+      <c r="H18" s="9">
+        <v>1</v>
+      </c>
       <c r="I18" s="9"/>
       <c r="J18" s="9"/>
       <c r="K18" s="9"/>
@@ -4780,12 +4901,16 @@
         <v>นางสาวอริศรา เล่งกูล</v>
       </c>
       <c r="D19" s="13"/>
-      <c r="E19" s="15"/>
+      <c r="E19" s="15">
+        <v>1</v>
+      </c>
       <c r="F19" s="14"/>
       <c r="G19" s="21">
         <v>1</v>
       </c>
-      <c r="H19" s="9"/>
+      <c r="H19" s="9">
+        <v>1</v>
+      </c>
       <c r="I19" s="9"/>
       <c r="J19" s="9"/>
       <c r="K19" s="9"/>
@@ -4814,7 +4939,9 @@
       <c r="G20" s="21">
         <v>1</v>
       </c>
-      <c r="H20" s="9"/>
+      <c r="H20" s="9">
+        <v>1</v>
+      </c>
       <c r="I20" s="9"/>
       <c r="J20" s="9"/>
       <c r="K20" s="9"/>
@@ -4876,7 +5003,9 @@
       <c r="G22" s="21">
         <v>1</v>
       </c>
-      <c r="H22" s="9"/>
+      <c r="H22" s="9">
+        <v>1</v>
+      </c>
       <c r="I22" s="9"/>
       <c r="J22" s="9"/>
       <c r="K22" s="9"/>
@@ -4909,7 +5038,9 @@
       <c r="G23" s="21">
         <v>1</v>
       </c>
-      <c r="H23" s="9"/>
+      <c r="H23" s="9">
+        <v>1</v>
+      </c>
       <c r="I23" s="9"/>
       <c r="J23" s="9"/>
       <c r="K23" s="9"/>
@@ -4942,7 +5073,9 @@
       <c r="G24" s="21">
         <v>1</v>
       </c>
-      <c r="H24" s="9"/>
+      <c r="H24" s="9">
+        <v>1</v>
+      </c>
       <c r="I24" s="9"/>
       <c r="J24" s="9"/>
       <c r="K24" s="9"/>
@@ -4975,7 +5108,9 @@
       <c r="G25" s="21">
         <v>1</v>
       </c>
-      <c r="H25" s="9"/>
+      <c r="H25" s="9">
+        <v>1</v>
+      </c>
       <c r="I25" s="9"/>
       <c r="J25" s="9"/>
       <c r="K25" s="9"/>
@@ -5008,7 +5143,9 @@
       <c r="G26" s="21">
         <v>1</v>
       </c>
-      <c r="H26" s="9"/>
+      <c r="H26" s="9">
+        <v>1</v>
+      </c>
       <c r="I26" s="9"/>
       <c r="J26" s="9"/>
       <c r="K26" s="9"/>
@@ -5039,7 +5176,9 @@
       <c r="G27" s="21">
         <v>1</v>
       </c>
-      <c r="H27" s="9"/>
+      <c r="H27" s="9">
+        <v>1</v>
+      </c>
       <c r="I27" s="9"/>
       <c r="J27" s="9"/>
       <c r="K27" s="9"/>
@@ -5103,7 +5242,9 @@
       <c r="G29" s="21">
         <v>1</v>
       </c>
-      <c r="H29" s="9"/>
+      <c r="H29" s="9">
+        <v>1</v>
+      </c>
       <c r="I29" s="9"/>
       <c r="J29" s="9"/>
       <c r="K29" s="9"/>
@@ -5136,7 +5277,9 @@
       <c r="G30" s="21">
         <v>1</v>
       </c>
-      <c r="H30" s="9"/>
+      <c r="H30" s="9">
+        <v>1</v>
+      </c>
       <c r="I30" s="9"/>
       <c r="J30" s="9"/>
       <c r="K30" s="9"/>
@@ -5194,7 +5337,9 @@
       <c r="G32" s="21">
         <v>1</v>
       </c>
-      <c r="H32" s="9"/>
+      <c r="H32" s="9">
+        <v>1</v>
+      </c>
       <c r="I32" s="9"/>
       <c r="J32" s="9"/>
       <c r="K32" s="9"/>
@@ -5225,7 +5370,9 @@
       <c r="G33" s="21">
         <v>1</v>
       </c>
-      <c r="H33" s="9"/>
+      <c r="H33" s="9">
+        <v>1</v>
+      </c>
       <c r="I33" s="9"/>
       <c r="J33" s="9"/>
       <c r="K33" s="9"/>
@@ -5258,7 +5405,9 @@
       <c r="G34" s="21">
         <v>1</v>
       </c>
-      <c r="H34" s="9"/>
+      <c r="H34" s="9">
+        <v>1</v>
+      </c>
       <c r="I34" s="9"/>
       <c r="J34" s="9"/>
       <c r="K34" s="9"/>
@@ -5291,7 +5440,9 @@
       <c r="G35" s="21">
         <v>1</v>
       </c>
-      <c r="H35" s="9"/>
+      <c r="H35" s="9">
+        <v>1</v>
+      </c>
       <c r="I35" s="9"/>
       <c r="J35" s="9"/>
       <c r="K35" s="9"/>
@@ -5357,7 +5508,9 @@
       <c r="G37" s="21">
         <v>1</v>
       </c>
-      <c r="H37" s="9"/>
+      <c r="H37" s="9">
+        <v>1</v>
+      </c>
       <c r="I37" s="9"/>
       <c r="J37" s="9"/>
       <c r="K37" s="9"/>
@@ -5388,7 +5541,9 @@
       <c r="G38" s="21">
         <v>1</v>
       </c>
-      <c r="H38" s="9"/>
+      <c r="H38" s="9">
+        <v>1</v>
+      </c>
       <c r="I38" s="9"/>
       <c r="J38" s="9"/>
       <c r="K38" s="9"/>
@@ -5421,7 +5576,9 @@
       <c r="G39" s="21">
         <v>1</v>
       </c>
-      <c r="H39" s="9"/>
+      <c r="H39" s="9">
+        <v>1</v>
+      </c>
       <c r="I39" s="9"/>
       <c r="J39" s="9"/>
       <c r="K39" s="9"/>
@@ -5454,7 +5611,9 @@
       <c r="G40" s="21">
         <v>1</v>
       </c>
-      <c r="H40" s="9"/>
+      <c r="H40" s="9">
+        <v>1</v>
+      </c>
       <c r="I40" s="9"/>
       <c r="J40" s="9"/>
       <c r="K40" s="9"/>
@@ -5487,7 +5646,9 @@
       <c r="G41" s="21">
         <v>1</v>
       </c>
-      <c r="H41" s="9"/>
+      <c r="H41" s="9">
+        <v>1</v>
+      </c>
       <c r="I41" s="9"/>
       <c r="J41" s="9"/>
       <c r="K41" s="9"/>
@@ -5520,7 +5681,9 @@
       <c r="G42" s="21">
         <v>1</v>
       </c>
-      <c r="H42" s="9"/>
+      <c r="H42" s="9">
+        <v>1</v>
+      </c>
       <c r="I42" s="9"/>
       <c r="J42" s="9"/>
       <c r="K42" s="9"/>
@@ -5553,7 +5716,9 @@
       <c r="G43" s="21">
         <v>1</v>
       </c>
-      <c r="H43" s="9"/>
+      <c r="H43" s="9">
+        <v>1</v>
+      </c>
       <c r="I43" s="9"/>
       <c r="J43" s="9"/>
       <c r="K43" s="9"/>
@@ -5586,7 +5751,9 @@
       <c r="G44" s="21">
         <v>1</v>
       </c>
-      <c r="H44" s="9"/>
+      <c r="H44" s="9">
+        <v>1</v>
+      </c>
       <c r="I44" s="9"/>
       <c r="J44" s="9"/>
       <c r="K44" s="9"/>
@@ -5619,7 +5786,9 @@
       <c r="G45" s="21">
         <v>1</v>
       </c>
-      <c r="H45" s="9"/>
+      <c r="H45" s="9">
+        <v>1</v>
+      </c>
       <c r="I45" s="9"/>
       <c r="J45" s="9"/>
       <c r="K45" s="9"/>
@@ -5652,7 +5821,9 @@
       <c r="G46" s="21">
         <v>1</v>
       </c>
-      <c r="H46" s="9"/>
+      <c r="H46" s="9">
+        <v>1</v>
+      </c>
       <c r="I46" s="9"/>
       <c r="J46" s="9"/>
       <c r="K46" s="9"/>
@@ -5685,7 +5856,9 @@
       <c r="G47" s="21">
         <v>1</v>
       </c>
-      <c r="H47" s="9"/>
+      <c r="H47" s="9">
+        <v>1</v>
+      </c>
       <c r="I47" s="9"/>
       <c r="J47" s="9"/>
       <c r="K47" s="9"/>
@@ -5718,7 +5891,9 @@
       <c r="G48" s="21">
         <v>1</v>
       </c>
-      <c r="H48" s="9"/>
+      <c r="H48" s="9">
+        <v>1</v>
+      </c>
       <c r="I48" s="9"/>
       <c r="J48" s="9"/>
       <c r="K48" s="9"/>
@@ -5751,7 +5926,9 @@
       <c r="G49" s="21">
         <v>1</v>
       </c>
-      <c r="H49" s="9"/>
+      <c r="H49" s="9">
+        <v>1</v>
+      </c>
       <c r="I49" s="9"/>
       <c r="J49" s="9"/>
       <c r="K49" s="9"/>
@@ -5784,7 +5961,9 @@
       <c r="G50" s="21">
         <v>1</v>
       </c>
-      <c r="H50" s="9"/>
+      <c r="H50" s="9">
+        <v>1</v>
+      </c>
       <c r="I50" s="9"/>
       <c r="J50" s="9"/>
       <c r="K50" s="9"/>
@@ -5817,7 +5996,9 @@
       <c r="G51" s="21">
         <v>1</v>
       </c>
-      <c r="H51" s="9"/>
+      <c r="H51" s="9">
+        <v>1</v>
+      </c>
       <c r="I51" s="9"/>
       <c r="J51" s="9"/>
       <c r="K51" s="9"/>
@@ -5850,7 +6031,9 @@
       <c r="G52" s="21">
         <v>1</v>
       </c>
-      <c r="H52" s="9"/>
+      <c r="H52" s="9">
+        <v>1</v>
+      </c>
       <c r="I52" s="9"/>
       <c r="J52" s="9"/>
       <c r="K52" s="9"/>
@@ -5883,7 +6066,9 @@
       <c r="G53" s="21">
         <v>1</v>
       </c>
-      <c r="H53" s="9"/>
+      <c r="H53" s="9">
+        <v>1</v>
+      </c>
       <c r="I53" s="9"/>
       <c r="J53" s="9"/>
       <c r="K53" s="9"/>
@@ -5893,5 +6078,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>